--- a/docs/LoL/LolSpells.xlsx
+++ b/docs/LoL/LolSpells.xlsx
@@ -11,6 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spells!$A$1:$AG$861</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spells!$A$1:$AK$861</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="1927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1924">
   <si>
     <t>Champions</t>
   </si>
@@ -5792,15 +5793,6 @@
   </si>
   <si>
     <t>Stranglethorns</t>
-  </si>
-  <si>
-    <t>HardCC</t>
-  </si>
-  <si>
-    <t>SoftCC</t>
-  </si>
-  <si>
-    <t>Dash</t>
   </si>
 </sst>
 </file>
@@ -20567,6 +20559,9 @@
       <c r="D789" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="M789">
+        <v>1</v>
+      </c>
     </row>
     <row r="790" ht="14.25">
       <c r="A790" s="1" t="s">
@@ -20581,6 +20576,9 @@
       <c r="D790" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="J790">
+        <v>1</v>
+      </c>
       <c r="AF790">
         <v>1</v>
       </c>
@@ -21838,6 +21836,7 @@
       <c r="M862" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AK861"/>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
@@ -21845,7 +21844,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{C680E480-AB28-4934-8E1D-0A14EB04BB29}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{2D3AF7C2-61F6-46F2-88EA-0E4DD36D8AB7}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -21878,103 +21877,103 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1924</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1925</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>1926</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>34</v>
@@ -22016,7 +22015,7 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="AJ3">
         <v>1</v>
       </c>
       <c r="AM3">
@@ -22039,19 +22038,13 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="AI4">
-        <v>1</v>
-      </c>
-      <c r="AJ4">
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
         <v>1</v>
       </c>
     </row>
@@ -22071,9 +22064,6 @@
       <c r="W5">
         <v>1</v>
       </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -22088,7 +22078,10 @@
       <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="AE6">
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
         <v>1</v>
       </c>
       <c r="AN6">
@@ -22136,6 +22129,9 @@
       <c r="D9" t="s">
         <v>46</v>
       </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
       <c r="AN9">
         <v>1</v>
       </c>
@@ -22153,16 +22149,13 @@
       <c r="D10" t="s">
         <v>49</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="AI10">
-        <v>1</v>
-      </c>
-      <c r="AJ10">
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>1</v>
+      </c>
+      <c r="AG10">
         <v>1</v>
       </c>
     </row>
@@ -22182,10 +22175,10 @@
       <c r="W11">
         <v>1</v>
       </c>
-      <c r="Z11">
-        <v>1</v>
-      </c>
-      <c r="AE11">
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AJ11">
         <v>1</v>
       </c>
       <c r="AM11">
@@ -22205,6 +22198,9 @@
       <c r="D12" t="s">
         <v>40</v>
       </c>
+      <c r="AK12">
+        <v>1</v>
+      </c>
       <c r="AN12">
         <v>1</v>
       </c>
@@ -22222,10 +22218,7 @@
       <c r="D13" t="s">
         <v>43</v>
       </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
+      <c r="M13">
         <v>1</v>
       </c>
     </row>
@@ -22242,6 +22235,9 @@
       <c r="D14" t="s">
         <v>46</v>
       </c>
+      <c r="AK14">
+        <v>1</v>
+      </c>
       <c r="AN14">
         <v>1</v>
       </c>
@@ -22259,19 +22255,16 @@
       <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="W15">
-        <v>2</v>
-      </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>1</v>
-      </c>
-      <c r="AI15">
-        <v>1</v>
-      </c>
-      <c r="AJ15">
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
         <v>1</v>
       </c>
     </row>
@@ -22288,16 +22281,13 @@
       <c r="D16" t="s">
         <v>52</v>
       </c>
-      <c r="W16">
-        <v>2</v>
-      </c>
-      <c r="Y16">
-        <v>1</v>
-      </c>
-      <c r="AA16">
-        <v>1</v>
-      </c>
-      <c r="AG16">
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
         <v>1</v>
       </c>
     </row>
@@ -22314,6 +22304,9 @@
       <c r="D17" t="s">
         <v>40</v>
       </c>
+      <c r="AK17">
+        <v>1</v>
+      </c>
       <c r="AN17">
         <v>1</v>
       </c>
@@ -22331,6 +22324,9 @@
       <c r="D18" t="s">
         <v>43</v>
       </c>
+      <c r="AK18">
+        <v>1</v>
+      </c>
       <c r="AN18">
         <v>1</v>
       </c>
@@ -22348,6 +22344,9 @@
       <c r="D19" t="s">
         <v>46</v>
       </c>
+      <c r="AK19">
+        <v>1</v>
+      </c>
       <c r="AN19">
         <v>1</v>
       </c>
@@ -22365,13 +22364,10 @@
       <c r="D20" t="s">
         <v>49</v>
       </c>
-      <c r="W20">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>1</v>
-      </c>
-      <c r="AE20">
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="AB20">
         <v>1</v>
       </c>
     </row>
@@ -22388,13 +22384,13 @@
       <c r="D21" t="s">
         <v>52</v>
       </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AF21">
+        <v>1</v>
+      </c>
       <c r="AG21">
-        <v>1</v>
-      </c>
-      <c r="AI21">
-        <v>1</v>
-      </c>
-      <c r="AJ21">
         <v>1</v>
       </c>
     </row>
@@ -22426,12 +22422,9 @@
         <v>43</v>
       </c>
       <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="J23">
         <v>1</v>
       </c>
     </row>
@@ -22449,18 +22442,12 @@
         <v>46</v>
       </c>
       <c r="E24">
-        <v>2</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="W24">
-        <v>1</v>
-      </c>
-      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="X24">
         <v>1</v>
       </c>
     </row>
@@ -22477,10 +22464,7 @@
       <c r="D25" t="s">
         <v>49</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="K25">
+      <c r="J25">
         <v>1</v>
       </c>
     </row>
@@ -22497,6 +22481,9 @@
       <c r="D26" t="s">
         <v>52</v>
       </c>
+      <c r="AI26">
+        <v>1</v>
+      </c>
       <c r="AL26">
         <v>1</v>
       </c>
@@ -22514,10 +22501,7 @@
       <c r="D27" t="s">
         <v>40</v>
       </c>
-      <c r="W27">
-        <v>1</v>
-      </c>
-      <c r="Y27">
+      <c r="V27">
         <v>1</v>
       </c>
     </row>
@@ -22562,16 +22546,10 @@
       <c r="D30" t="s">
         <v>49</v>
       </c>
-      <c r="N30">
-        <v>1</v>
-      </c>
-      <c r="O30">
-        <v>1</v>
-      </c>
-      <c r="W30">
-        <v>1</v>
-      </c>
-      <c r="Y30">
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="V30">
         <v>1</v>
       </c>
     </row>
@@ -22588,13 +22566,10 @@
       <c r="D31" t="s">
         <v>52</v>
       </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="AD31">
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="AA31">
         <v>1</v>
       </c>
     </row>
@@ -22625,19 +22600,16 @@
       <c r="D33" t="s">
         <v>43</v>
       </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="W33">
-        <v>1</v>
-      </c>
-      <c r="X33">
-        <v>1</v>
-      </c>
-      <c r="AI33">
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="AF33">
+        <v>1</v>
+      </c>
+      <c r="AG33">
         <v>1</v>
       </c>
       <c r="AJ33">
@@ -22688,10 +22660,7 @@
       <c r="D36" t="s">
         <v>52</v>
       </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="K36">
+      <c r="J36">
         <v>1</v>
       </c>
     </row>
@@ -22722,10 +22691,7 @@
       <c r="D38" t="s">
         <v>43</v>
       </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="K38">
+      <c r="J38">
         <v>1</v>
       </c>
     </row>
@@ -22770,10 +22736,7 @@
       <c r="D41" t="s">
         <v>52</v>
       </c>
-      <c r="N41">
-        <v>1</v>
-      </c>
-      <c r="O41">
+      <c r="M41">
         <v>1</v>
       </c>
     </row>
@@ -22790,10 +22753,7 @@
       <c r="D42" t="s">
         <v>40</v>
       </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="K42">
+      <c r="J42">
         <v>1</v>
       </c>
     </row>
@@ -22838,6 +22798,9 @@
       <c r="D45" t="s">
         <v>49</v>
       </c>
+      <c r="AK45">
+        <v>1</v>
+      </c>
       <c r="AN45">
         <v>1</v>
       </c>
@@ -22869,16 +22832,13 @@
       <c r="D47" t="s">
         <v>40</v>
       </c>
-      <c r="E47">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="N47">
-        <v>1</v>
-      </c>
-      <c r="O47">
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="AJ47">
         <v>1</v>
       </c>
       <c r="AM47">
@@ -22954,10 +22914,7 @@
       <c r="D52" t="s">
         <v>40</v>
       </c>
-      <c r="N52">
-        <v>1</v>
-      </c>
-      <c r="O52">
+      <c r="M52">
         <v>1</v>
       </c>
     </row>
@@ -22988,10 +22945,10 @@
       <c r="D54" t="s">
         <v>46</v>
       </c>
-      <c r="AI54">
-        <v>1</v>
-      </c>
-      <c r="AJ54">
+      <c r="AF54">
+        <v>1</v>
+      </c>
+      <c r="AG54">
         <v>1</v>
       </c>
     </row>
@@ -23008,6 +22965,9 @@
       <c r="D55" t="s">
         <v>49</v>
       </c>
+      <c r="AJ55">
+        <v>1</v>
+      </c>
       <c r="AM55">
         <v>1</v>
       </c>
@@ -23025,13 +22985,10 @@
       <c r="D56" t="s">
         <v>52</v>
       </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
-      <c r="AI56">
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="AF56">
         <v>1</v>
       </c>
     </row>
@@ -23062,10 +23019,10 @@
       <c r="D58" t="s">
         <v>43</v>
       </c>
-      <c r="AI58">
-        <v>1</v>
-      </c>
-      <c r="AJ58">
+      <c r="AF58">
+        <v>1</v>
+      </c>
+      <c r="AG58">
         <v>1</v>
       </c>
     </row>
@@ -23082,13 +23039,10 @@
       <c r="D59" t="s">
         <v>46</v>
       </c>
-      <c r="W59">
-        <v>1</v>
-      </c>
-      <c r="Y59">
-        <v>1</v>
-      </c>
-      <c r="AE59">
+      <c r="V59">
+        <v>1</v>
+      </c>
+      <c r="AB59">
         <v>1</v>
       </c>
     </row>
@@ -23105,13 +23059,10 @@
       <c r="D60" t="s">
         <v>49</v>
       </c>
-      <c r="N60">
-        <v>1</v>
-      </c>
-      <c r="R60">
-        <v>1</v>
-      </c>
-      <c r="AF60">
+      <c r="P60">
+        <v>1</v>
+      </c>
+      <c r="AC60">
         <v>1</v>
       </c>
     </row>
@@ -23129,18 +23080,12 @@
         <v>52</v>
       </c>
       <c r="E61">
-        <v>2</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-      <c r="K61">
-        <v>1</v>
-      </c>
-      <c r="N61">
-        <v>1</v>
-      </c>
-      <c r="O61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="M61">
         <v>1</v>
       </c>
     </row>
@@ -23185,13 +23130,13 @@
       <c r="D64" t="s">
         <v>46</v>
       </c>
-      <c r="W64">
-        <v>1</v>
-      </c>
-      <c r="Y64">
-        <v>1</v>
-      </c>
-      <c r="AE64">
+      <c r="V64">
+        <v>1</v>
+      </c>
+      <c r="AB64">
+        <v>1</v>
+      </c>
+      <c r="AK64">
         <v>1</v>
       </c>
       <c r="AN64">
@@ -23211,16 +23156,10 @@
       <c r="D65" t="s">
         <v>49</v>
       </c>
-      <c r="N65">
-        <v>1</v>
-      </c>
-      <c r="O65">
-        <v>1</v>
-      </c>
-      <c r="W65">
-        <v>1</v>
-      </c>
-      <c r="Y65">
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="V65">
         <v>1</v>
       </c>
     </row>
@@ -23237,19 +23176,16 @@
       <c r="D66" t="s">
         <v>52</v>
       </c>
-      <c r="N66">
-        <v>1</v>
-      </c>
-      <c r="O66">
-        <v>1</v>
-      </c>
-      <c r="W66">
-        <v>2</v>
-      </c>
-      <c r="X66">
-        <v>1</v>
-      </c>
-      <c r="Y66">
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="U66">
+        <v>1</v>
+      </c>
+      <c r="V66">
+        <v>1</v>
+      </c>
+      <c r="AK66">
         <v>1</v>
       </c>
       <c r="AN66">
@@ -23283,10 +23219,7 @@
       <c r="D68" t="s">
         <v>43</v>
       </c>
-      <c r="N68">
-        <v>1</v>
-      </c>
-      <c r="O68">
+      <c r="M68">
         <v>1</v>
       </c>
     </row>
@@ -23303,6 +23236,9 @@
       <c r="D69" t="s">
         <v>46</v>
       </c>
+      <c r="AJ69">
+        <v>1</v>
+      </c>
       <c r="AM69">
         <v>1</v>
       </c>
@@ -23320,10 +23256,7 @@
       <c r="D70" t="s">
         <v>49</v>
       </c>
-      <c r="W70">
-        <v>1</v>
-      </c>
-      <c r="AA70">
+      <c r="X70">
         <v>1</v>
       </c>
     </row>
@@ -23343,9 +23276,6 @@
       <c r="E71">
         <v>1</v>
       </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
@@ -23360,10 +23290,10 @@
       <c r="D72" t="s">
         <v>40</v>
       </c>
-      <c r="N72">
-        <v>1</v>
-      </c>
-      <c r="O72">
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="AK72">
         <v>1</v>
       </c>
       <c r="AN72">
@@ -23383,22 +23313,16 @@
       <c r="D73" t="s">
         <v>43</v>
       </c>
-      <c r="E73">
-        <v>1</v>
-      </c>
-      <c r="K73">
-        <v>1</v>
-      </c>
-      <c r="N73">
-        <v>1</v>
-      </c>
-      <c r="O73">
-        <v>1</v>
-      </c>
-      <c r="AI73">
-        <v>1</v>
-      </c>
-      <c r="AJ73">
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="AF73">
+        <v>1</v>
+      </c>
+      <c r="AG73">
         <v>1</v>
       </c>
     </row>
@@ -23415,6 +23339,12 @@
       <c r="D74" t="s">
         <v>46</v>
       </c>
+      <c r="AJ74">
+        <v>1</v>
+      </c>
+      <c r="AK74">
+        <v>1</v>
+      </c>
       <c r="AM74">
         <v>1</v>
       </c>
@@ -23435,10 +23365,7 @@
       <c r="D75" t="s">
         <v>49</v>
       </c>
-      <c r="W75">
-        <v>1</v>
-      </c>
-      <c r="X75">
+      <c r="U75">
         <v>1</v>
       </c>
     </row>
@@ -23455,13 +23382,10 @@
       <c r="D76" t="s">
         <v>52</v>
       </c>
-      <c r="E76">
-        <v>1</v>
-      </c>
-      <c r="J76">
-        <v>1</v>
-      </c>
-      <c r="AH76">
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="AE76">
         <v>1</v>
       </c>
     </row>
@@ -23478,7 +23402,7 @@
       <c r="D77" t="s">
         <v>40</v>
       </c>
-      <c r="AE77">
+      <c r="AB77">
         <v>1</v>
       </c>
     </row>
@@ -23495,10 +23419,7 @@
       <c r="D78" t="s">
         <v>43</v>
       </c>
-      <c r="W78">
-        <v>1</v>
-      </c>
-      <c r="Y78">
+      <c r="V78">
         <v>1</v>
       </c>
     </row>
@@ -23518,13 +23439,7 @@
       <c r="E79">
         <v>1</v>
       </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-      <c r="N79">
-        <v>1</v>
-      </c>
-      <c r="O79">
+      <c r="M79">
         <v>1</v>
       </c>
     </row>
@@ -23541,7 +23456,7 @@
       <c r="D80" t="s">
         <v>49</v>
       </c>
-      <c r="AG80">
+      <c r="AD80">
         <v>1</v>
       </c>
     </row>
@@ -23558,16 +23473,16 @@
       <c r="D81" t="s">
         <v>52</v>
       </c>
-      <c r="W81">
-        <v>1</v>
-      </c>
-      <c r="AA81">
-        <v>1</v>
-      </c>
-      <c r="AE81">
-        <v>1</v>
-      </c>
-      <c r="AG81">
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="AB81">
+        <v>1</v>
+      </c>
+      <c r="AD81">
+        <v>1</v>
+      </c>
+      <c r="AK81">
         <v>1</v>
       </c>
       <c r="AN81">
@@ -23602,18 +23517,15 @@
         <v>43</v>
       </c>
       <c r="E83">
-        <v>2</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="K83">
-        <v>1</v>
-      </c>
-      <c r="AI83">
-        <v>1</v>
-      </c>
-      <c r="AJ83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="AF83">
+        <v>1</v>
+      </c>
+      <c r="AG83">
         <v>1</v>
       </c>
     </row>
@@ -23647,9 +23559,6 @@
       <c r="E85">
         <v>1</v>
       </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
@@ -23664,10 +23573,7 @@
       <c r="D86" t="s">
         <v>52</v>
       </c>
-      <c r="N86">
-        <v>1</v>
-      </c>
-      <c r="T86">
+      <c r="R86">
         <v>1</v>
       </c>
     </row>
@@ -23698,16 +23604,13 @@
       <c r="D88" t="s">
         <v>43</v>
       </c>
-      <c r="E88">
-        <v>1</v>
-      </c>
-      <c r="K88">
-        <v>1</v>
-      </c>
-      <c r="AI88">
-        <v>1</v>
-      </c>
-      <c r="AJ88">
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="AF88">
+        <v>1</v>
+      </c>
+      <c r="AG88">
         <v>1</v>
       </c>
     </row>
@@ -23752,10 +23655,7 @@
       <c r="D91" t="s">
         <v>52</v>
       </c>
-      <c r="N91">
-        <v>1</v>
-      </c>
-      <c r="O91">
+      <c r="M91">
         <v>1</v>
       </c>
     </row>
@@ -23772,10 +23672,7 @@
       <c r="D92" t="s">
         <v>40</v>
       </c>
-      <c r="E92">
-        <v>1</v>
-      </c>
-      <c r="K92">
+      <c r="J92">
         <v>1</v>
       </c>
     </row>
@@ -23792,16 +23689,13 @@
       <c r="D93" t="s">
         <v>43</v>
       </c>
-      <c r="N93">
-        <v>1</v>
-      </c>
-      <c r="O93">
-        <v>1</v>
-      </c>
-      <c r="AI93">
-        <v>1</v>
-      </c>
-      <c r="AJ93">
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="AF93">
+        <v>1</v>
+      </c>
+      <c r="AG93">
         <v>1</v>
       </c>
     </row>
@@ -23818,10 +23712,7 @@
       <c r="D94" t="s">
         <v>46</v>
       </c>
-      <c r="W94">
-        <v>1</v>
-      </c>
-      <c r="AA94">
+      <c r="X94">
         <v>1</v>
       </c>
     </row>
@@ -23838,6 +23729,9 @@
       <c r="D95" t="s">
         <v>49</v>
       </c>
+      <c r="AK95">
+        <v>1</v>
+      </c>
       <c r="AN95">
         <v>1</v>
       </c>
@@ -23858,13 +23752,7 @@
       <c r="E96">
         <v>1</v>
       </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-      <c r="N96">
-        <v>1</v>
-      </c>
-      <c r="O96">
+      <c r="M96">
         <v>1</v>
       </c>
     </row>
@@ -23895,16 +23783,10 @@
       <c r="D98" t="s">
         <v>43</v>
       </c>
-      <c r="E98">
-        <v>1</v>
-      </c>
-      <c r="K98">
-        <v>1</v>
-      </c>
-      <c r="W98">
-        <v>1</v>
-      </c>
-      <c r="AB98">
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="Y98">
         <v>1</v>
       </c>
     </row>
@@ -23924,10 +23806,10 @@
       <c r="W99">
         <v>1</v>
       </c>
-      <c r="Z99">
-        <v>1</v>
-      </c>
-      <c r="AG99">
+      <c r="AD99">
+        <v>1</v>
+      </c>
+      <c r="AK99">
         <v>1</v>
       </c>
       <c r="AN99">
@@ -23948,18 +23830,12 @@
         <v>49</v>
       </c>
       <c r="E100">
-        <v>2</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-      <c r="K100">
-        <v>1</v>
-      </c>
-      <c r="N100">
-        <v>1</v>
-      </c>
-      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="M100">
         <v>1</v>
       </c>
     </row>
@@ -23976,13 +23852,10 @@
       <c r="D101" t="s">
         <v>52</v>
       </c>
-      <c r="W101">
-        <v>1</v>
-      </c>
-      <c r="X101">
-        <v>1</v>
-      </c>
-      <c r="AI101">
+      <c r="U101">
+        <v>1</v>
+      </c>
+      <c r="AF101">
         <v>1</v>
       </c>
     </row>
@@ -24027,10 +23900,10 @@
       <c r="D104" t="s">
         <v>46</v>
       </c>
-      <c r="E104">
-        <v>1</v>
-      </c>
-      <c r="H104">
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="AJ104">
         <v>1</v>
       </c>
       <c r="AM104">
@@ -24050,22 +23923,16 @@
       <c r="D105" t="s">
         <v>49</v>
       </c>
-      <c r="N105">
-        <v>1</v>
-      </c>
-      <c r="O105">
-        <v>1</v>
-      </c>
-      <c r="W105">
-        <v>1</v>
-      </c>
-      <c r="Y105">
-        <v>1</v>
-      </c>
-      <c r="AI105">
-        <v>1</v>
-      </c>
-      <c r="AJ105">
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="V105">
+        <v>1</v>
+      </c>
+      <c r="AF105">
+        <v>1</v>
+      </c>
+      <c r="AG105">
         <v>1</v>
       </c>
     </row>
@@ -24082,7 +23949,7 @@
       <c r="D106" t="s">
         <v>52</v>
       </c>
-      <c r="AI106">
+      <c r="AF106">
         <v>1</v>
       </c>
     </row>
@@ -24113,6 +23980,9 @@
       <c r="D108" t="s">
         <v>43</v>
       </c>
+      <c r="AK108">
+        <v>1</v>
+      </c>
       <c r="AN108">
         <v>1</v>
       </c>
@@ -24130,10 +24000,7 @@
       <c r="D109" t="s">
         <v>46</v>
       </c>
-      <c r="N109">
-        <v>1</v>
-      </c>
-      <c r="O109">
+      <c r="M109">
         <v>1</v>
       </c>
     </row>
@@ -24151,24 +24018,18 @@
         <v>49</v>
       </c>
       <c r="E110">
-        <v>2</v>
-      </c>
-      <c r="F110">
-        <v>1</v>
-      </c>
-      <c r="K110">
-        <v>1</v>
-      </c>
-      <c r="W110">
-        <v>2</v>
-      </c>
-      <c r="Y110">
-        <v>1</v>
-      </c>
-      <c r="AC110">
-        <v>1</v>
-      </c>
-      <c r="AI110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="V110">
+        <v>1</v>
+      </c>
+      <c r="Z110">
+        <v>1</v>
+      </c>
+      <c r="AF110">
         <v>1</v>
       </c>
     </row>
@@ -24188,16 +24049,10 @@
       <c r="E111">
         <v>1</v>
       </c>
-      <c r="F111">
-        <v>1</v>
-      </c>
-      <c r="W111">
-        <v>1</v>
-      </c>
-      <c r="AB111">
-        <v>1</v>
-      </c>
-      <c r="AH111">
+      <c r="Y111">
+        <v>1</v>
+      </c>
+      <c r="AE111">
         <v>1</v>
       </c>
     </row>
@@ -24214,6 +24069,9 @@
       <c r="D112" t="s">
         <v>40</v>
       </c>
+      <c r="AK112">
+        <v>1</v>
+      </c>
       <c r="AN112">
         <v>1</v>
       </c>
@@ -24231,6 +24089,9 @@
       <c r="D113" t="s">
         <v>43</v>
       </c>
+      <c r="AK113">
+        <v>1</v>
+      </c>
       <c r="AN113">
         <v>1</v>
       </c>
@@ -24248,13 +24109,10 @@
       <c r="D114" t="s">
         <v>46</v>
       </c>
-      <c r="N114">
-        <v>2</v>
+      <c r="M114">
+        <v>1</v>
       </c>
       <c r="O114">
-        <v>1</v>
-      </c>
-      <c r="Q114">
         <v>1</v>
       </c>
     </row>
@@ -24285,16 +24143,10 @@
       <c r="D116" t="s">
         <v>52</v>
       </c>
-      <c r="E116">
-        <v>1</v>
-      </c>
-      <c r="K116">
-        <v>1</v>
-      </c>
-      <c r="N116">
-        <v>1</v>
-      </c>
-      <c r="O116">
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="M116">
         <v>1</v>
       </c>
     </row>
@@ -24328,13 +24180,7 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118">
-        <v>1</v>
-      </c>
-      <c r="N118">
-        <v>1</v>
-      </c>
-      <c r="O118">
+      <c r="M118">
         <v>1</v>
       </c>
     </row>
@@ -24351,10 +24197,7 @@
       <c r="D119" t="s">
         <v>46</v>
       </c>
-      <c r="N119">
-        <v>1</v>
-      </c>
-      <c r="T119">
+      <c r="R119">
         <v>1</v>
       </c>
     </row>
@@ -24371,10 +24214,7 @@
       <c r="D120" t="s">
         <v>49</v>
       </c>
-      <c r="N120">
-        <v>1</v>
-      </c>
-      <c r="O120">
+      <c r="M120">
         <v>1</v>
       </c>
     </row>
@@ -24436,9 +24276,6 @@
       <c r="W124">
         <v>1</v>
       </c>
-      <c r="Z124">
-        <v>1</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
@@ -24467,7 +24304,10 @@
       <c r="D126" t="s">
         <v>52</v>
       </c>
-      <c r="AI126">
+      <c r="AF126">
+        <v>1</v>
+      </c>
+      <c r="AG126">
         <v>1</v>
       </c>
       <c r="AJ126">
@@ -24518,10 +24358,7 @@
       <c r="D129" t="s">
         <v>46</v>
       </c>
-      <c r="N129">
-        <v>1</v>
-      </c>
-      <c r="O129">
+      <c r="M129">
         <v>1</v>
       </c>
     </row>
@@ -24541,13 +24378,7 @@
       <c r="E130">
         <v>1</v>
       </c>
-      <c r="F130">
-        <v>1</v>
-      </c>
-      <c r="N130">
-        <v>1</v>
-      </c>
-      <c r="O130">
+      <c r="M130">
         <v>1</v>
       </c>
     </row>
@@ -24620,10 +24451,7 @@
       <c r="D135" t="s">
         <v>49</v>
       </c>
-      <c r="W135">
-        <v>1</v>
-      </c>
-      <c r="AA135">
+      <c r="X135">
         <v>1</v>
       </c>
     </row>
@@ -24643,13 +24471,7 @@
       <c r="E136">
         <v>1</v>
       </c>
-      <c r="F136">
-        <v>1</v>
-      </c>
-      <c r="N136">
-        <v>1</v>
-      </c>
-      <c r="O136">
+      <c r="M136">
         <v>1</v>
       </c>
     </row>
@@ -24680,16 +24502,13 @@
       <c r="D138" t="s">
         <v>43</v>
       </c>
-      <c r="N138">
-        <v>1</v>
-      </c>
-      <c r="O138">
-        <v>1</v>
-      </c>
-      <c r="AI138">
-        <v>1</v>
-      </c>
-      <c r="AJ138">
+      <c r="M138">
+        <v>1</v>
+      </c>
+      <c r="AF138">
+        <v>1</v>
+      </c>
+      <c r="AG138">
         <v>1</v>
       </c>
     </row>
@@ -24734,6 +24553,9 @@
       <c r="D141" t="s">
         <v>52</v>
       </c>
+      <c r="AK141">
+        <v>1</v>
+      </c>
       <c r="AN141">
         <v>1</v>
       </c>
@@ -24779,6 +24601,9 @@
       <c r="D144" t="s">
         <v>46</v>
       </c>
+      <c r="AK144">
+        <v>1</v>
+      </c>
       <c r="AN144">
         <v>1</v>
       </c>
@@ -24799,13 +24624,7 @@
       <c r="E145">
         <v>1</v>
       </c>
-      <c r="F145">
-        <v>1</v>
-      </c>
-      <c r="N145">
-        <v>1</v>
-      </c>
-      <c r="O145">
+      <c r="M145">
         <v>1</v>
       </c>
     </row>
@@ -24822,10 +24641,10 @@
       <c r="D146" t="s">
         <v>52</v>
       </c>
+      <c r="AC146">
+        <v>1</v>
+      </c>
       <c r="AF146">
-        <v>1</v>
-      </c>
-      <c r="AI146">
         <v>1</v>
       </c>
     </row>
@@ -24842,6 +24661,9 @@
       <c r="D147" t="s">
         <v>40</v>
       </c>
+      <c r="AK147">
+        <v>1</v>
+      </c>
       <c r="AN147">
         <v>1</v>
       </c>
@@ -24859,16 +24681,13 @@
       <c r="D148" t="s">
         <v>43</v>
       </c>
-      <c r="N148">
-        <v>1</v>
-      </c>
-      <c r="O148">
-        <v>1</v>
-      </c>
-      <c r="AI148">
-        <v>1</v>
-      </c>
-      <c r="AJ148">
+      <c r="M148">
+        <v>1</v>
+      </c>
+      <c r="AF148">
+        <v>1</v>
+      </c>
+      <c r="AG148">
         <v>1</v>
       </c>
     </row>
@@ -24885,19 +24704,13 @@
       <c r="D149" t="s">
         <v>46</v>
       </c>
-      <c r="E149">
-        <v>1</v>
-      </c>
-      <c r="K149">
-        <v>1</v>
-      </c>
-      <c r="N149">
-        <v>1</v>
-      </c>
-      <c r="O149">
-        <v>1</v>
-      </c>
-      <c r="AG149">
+      <c r="J149">
+        <v>1</v>
+      </c>
+      <c r="M149">
+        <v>1</v>
+      </c>
+      <c r="AD149">
         <v>1</v>
       </c>
     </row>
@@ -24914,13 +24727,10 @@
       <c r="D150" t="s">
         <v>49</v>
       </c>
-      <c r="W150">
-        <v>1</v>
-      </c>
-      <c r="Y150">
-        <v>1</v>
-      </c>
-      <c r="AD150">
+      <c r="V150">
+        <v>1</v>
+      </c>
+      <c r="AA150">
         <v>1</v>
       </c>
     </row>
@@ -24937,13 +24747,10 @@
       <c r="D151" t="s">
         <v>52</v>
       </c>
-      <c r="W151">
-        <v>1</v>
-      </c>
-      <c r="X151">
-        <v>1</v>
-      </c>
-      <c r="AH151">
+      <c r="U151">
+        <v>1</v>
+      </c>
+      <c r="AE151">
         <v>1</v>
       </c>
     </row>
@@ -24960,6 +24767,9 @@
       <c r="D152" t="s">
         <v>40</v>
       </c>
+      <c r="AK152">
+        <v>1</v>
+      </c>
       <c r="AN152">
         <v>1</v>
       </c>
@@ -24977,10 +24787,7 @@
       <c r="D153" t="s">
         <v>43</v>
       </c>
-      <c r="W153">
-        <v>1</v>
-      </c>
-      <c r="AB153">
+      <c r="Y153">
         <v>1</v>
       </c>
     </row>
@@ -24997,10 +24804,10 @@
       <c r="D154" t="s">
         <v>46</v>
       </c>
-      <c r="AI154">
-        <v>1</v>
-      </c>
-      <c r="AJ154">
+      <c r="AF154">
+        <v>1</v>
+      </c>
+      <c r="AG154">
         <v>1</v>
       </c>
     </row>
@@ -25017,22 +24824,19 @@
       <c r="D155" t="s">
         <v>49</v>
       </c>
-      <c r="E155">
-        <v>1</v>
-      </c>
-      <c r="K155">
-        <v>1</v>
-      </c>
-      <c r="AD155">
-        <v>1</v>
-      </c>
-      <c r="AH155">
-        <v>1</v>
-      </c>
-      <c r="AI155">
-        <v>1</v>
-      </c>
-      <c r="AJ155">
+      <c r="J155">
+        <v>1</v>
+      </c>
+      <c r="AA155">
+        <v>1</v>
+      </c>
+      <c r="AE155">
+        <v>1</v>
+      </c>
+      <c r="AF155">
+        <v>1</v>
+      </c>
+      <c r="AG155">
         <v>1</v>
       </c>
     </row>
@@ -25077,7 +24881,10 @@
       <c r="D158" t="s">
         <v>43</v>
       </c>
-      <c r="AI158">
+      <c r="AF158">
+        <v>1</v>
+      </c>
+      <c r="AG158">
         <v>1</v>
       </c>
       <c r="AJ158">
@@ -25100,16 +24907,10 @@
       <c r="D159" t="s">
         <v>46</v>
       </c>
-      <c r="E159">
-        <v>1</v>
-      </c>
-      <c r="G159">
-        <v>1</v>
-      </c>
-      <c r="N159">
-        <v>1</v>
-      </c>
-      <c r="O159">
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="M159">
         <v>1</v>
       </c>
     </row>
@@ -25126,10 +24927,10 @@
       <c r="D160" t="s">
         <v>49</v>
       </c>
-      <c r="W160">
-        <v>1</v>
-      </c>
-      <c r="AB160">
+      <c r="Y160">
+        <v>1</v>
+      </c>
+      <c r="AK160">
         <v>1</v>
       </c>
       <c r="AN160">
@@ -25149,10 +24950,10 @@
       <c r="D161" t="s">
         <v>52</v>
       </c>
-      <c r="AD161">
-        <v>1</v>
-      </c>
-      <c r="AH161">
+      <c r="AA161">
+        <v>1</v>
+      </c>
+      <c r="AE161">
         <v>1</v>
       </c>
     </row>
@@ -25183,10 +24984,10 @@
       <c r="D163" t="s">
         <v>43</v>
       </c>
-      <c r="AI163">
-        <v>1</v>
-      </c>
-      <c r="AJ163">
+      <c r="AF163">
+        <v>1</v>
+      </c>
+      <c r="AG163">
         <v>1</v>
       </c>
     </row>
@@ -25203,7 +25004,7 @@
       <c r="D164" t="s">
         <v>46</v>
       </c>
-      <c r="AI164">
+      <c r="AF164">
         <v>1</v>
       </c>
     </row>
@@ -25220,7 +25021,7 @@
       <c r="D165" t="s">
         <v>49</v>
       </c>
-      <c r="AD165">
+      <c r="AA165">
         <v>1</v>
       </c>
     </row>
@@ -25265,16 +25066,10 @@
       <c r="D168" t="s">
         <v>43</v>
       </c>
-      <c r="E168">
-        <v>1</v>
-      </c>
-      <c r="G168">
-        <v>1</v>
-      </c>
-      <c r="N168">
-        <v>1</v>
-      </c>
-      <c r="O168">
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="M168">
         <v>1</v>
       </c>
     </row>
@@ -25319,13 +25114,10 @@
       <c r="D171" t="s">
         <v>52</v>
       </c>
-      <c r="N171">
-        <v>1</v>
-      </c>
-      <c r="O171">
-        <v>1</v>
-      </c>
-      <c r="AD171">
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="AA171">
         <v>1</v>
       </c>
     </row>
@@ -25342,6 +25134,9 @@
       <c r="D172" t="s">
         <v>40</v>
       </c>
+      <c r="AK172">
+        <v>1</v>
+      </c>
       <c r="AN172">
         <v>1</v>
       </c>
@@ -25362,9 +25157,6 @@
       <c r="W173">
         <v>1</v>
       </c>
-      <c r="Z173">
-        <v>1</v>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
@@ -25379,25 +25171,19 @@
       <c r="D174" t="s">
         <v>46</v>
       </c>
-      <c r="E174">
-        <v>1</v>
-      </c>
-      <c r="K174">
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="M174">
         <v>1</v>
       </c>
       <c r="N174">
-        <v>2</v>
-      </c>
-      <c r="O174">
-        <v>1</v>
-      </c>
-      <c r="P174">
-        <v>1</v>
-      </c>
-      <c r="AH174">
-        <v>1</v>
-      </c>
-      <c r="AI174">
+        <v>1</v>
+      </c>
+      <c r="AE174">
+        <v>1</v>
+      </c>
+      <c r="AF174">
         <v>1</v>
       </c>
     </row>
@@ -25414,10 +25200,7 @@
       <c r="D175" t="s">
         <v>49</v>
       </c>
-      <c r="N175">
-        <v>1</v>
-      </c>
-      <c r="O175">
+      <c r="M175">
         <v>1</v>
       </c>
     </row>
@@ -25434,6 +25217,9 @@
       <c r="D176" t="s">
         <v>52</v>
       </c>
+      <c r="AK176">
+        <v>1</v>
+      </c>
       <c r="AN176">
         <v>1</v>
       </c>
@@ -25465,10 +25251,7 @@
       <c r="D178" t="s">
         <v>43</v>
       </c>
-      <c r="W178">
-        <v>1</v>
-      </c>
-      <c r="AA178">
+      <c r="X178">
         <v>1</v>
       </c>
     </row>
@@ -25499,19 +25282,13 @@
       <c r="D180" t="s">
         <v>49</v>
       </c>
-      <c r="N180">
-        <v>1</v>
-      </c>
-      <c r="O180">
+      <c r="M180">
         <v>1</v>
       </c>
       <c r="W180">
         <v>1</v>
       </c>
-      <c r="Z180">
-        <v>1</v>
-      </c>
-      <c r="AH180">
+      <c r="AE180">
         <v>1</v>
       </c>
     </row>
@@ -25531,16 +25308,10 @@
       <c r="E181">
         <v>1</v>
       </c>
-      <c r="F181">
-        <v>1</v>
-      </c>
-      <c r="N181">
-        <v>1</v>
-      </c>
-      <c r="O181">
-        <v>1</v>
-      </c>
-      <c r="AI181">
+      <c r="M181">
+        <v>1</v>
+      </c>
+      <c r="AF181">
         <v>1</v>
       </c>
     </row>
@@ -25585,16 +25356,10 @@
       <c r="D184" t="s">
         <v>46</v>
       </c>
-      <c r="E184">
-        <v>1</v>
-      </c>
-      <c r="G184">
-        <v>1</v>
-      </c>
-      <c r="N184">
-        <v>1</v>
-      </c>
-      <c r="O184">
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="M184">
         <v>1</v>
       </c>
     </row>
@@ -25614,16 +25379,10 @@
       <c r="E185">
         <v>1</v>
       </c>
-      <c r="F185">
-        <v>1</v>
-      </c>
-      <c r="W185">
-        <v>1</v>
-      </c>
-      <c r="Y185">
-        <v>1</v>
-      </c>
-      <c r="AI185">
+      <c r="V185">
+        <v>1</v>
+      </c>
+      <c r="AF185">
         <v>1</v>
       </c>
     </row>
@@ -25643,16 +25402,10 @@
       <c r="E186">
         <v>1</v>
       </c>
-      <c r="F186">
-        <v>1</v>
-      </c>
-      <c r="W186">
-        <v>1</v>
-      </c>
-      <c r="AA186">
-        <v>1</v>
-      </c>
-      <c r="AH186">
+      <c r="X186">
+        <v>1</v>
+      </c>
+      <c r="AE186">
         <v>1</v>
       </c>
     </row>
@@ -25669,6 +25422,9 @@
       <c r="D187" t="s">
         <v>40</v>
       </c>
+      <c r="AK187">
+        <v>1</v>
+      </c>
       <c r="AN187">
         <v>1</v>
       </c>
@@ -25714,10 +25470,7 @@
       <c r="D190" t="s">
         <v>49</v>
       </c>
-      <c r="N190">
-        <v>1</v>
-      </c>
-      <c r="O190">
+      <c r="M190">
         <v>1</v>
       </c>
     </row>
@@ -25734,10 +25487,7 @@
       <c r="D191" t="s">
         <v>52</v>
       </c>
-      <c r="N191">
-        <v>1</v>
-      </c>
-      <c r="O191">
+      <c r="M191">
         <v>1</v>
       </c>
     </row>
@@ -25768,10 +25518,10 @@
       <c r="D193" t="s">
         <v>43</v>
       </c>
-      <c r="N193">
-        <v>1</v>
-      </c>
-      <c r="T193">
+      <c r="R193">
+        <v>1</v>
+      </c>
+      <c r="AK193">
         <v>1</v>
       </c>
       <c r="AN193">
@@ -25819,7 +25569,7 @@
       <c r="D196" t="s">
         <v>52</v>
       </c>
-      <c r="AG196">
+      <c r="AD196">
         <v>1</v>
       </c>
     </row>
@@ -25836,6 +25586,9 @@
       <c r="D197" t="s">
         <v>40</v>
       </c>
+      <c r="AK197">
+        <v>1</v>
+      </c>
       <c r="AN197">
         <v>1</v>
       </c>
@@ -25853,16 +25606,13 @@
       <c r="D198" t="s">
         <v>43</v>
       </c>
-      <c r="N198">
-        <v>1</v>
-      </c>
-      <c r="O198">
-        <v>1</v>
-      </c>
-      <c r="AI198">
-        <v>1</v>
-      </c>
-      <c r="AJ198">
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="AF198">
+        <v>1</v>
+      </c>
+      <c r="AG198">
         <v>1</v>
       </c>
     </row>
@@ -25879,10 +25629,7 @@
       <c r="D199" t="s">
         <v>46</v>
       </c>
-      <c r="E199">
-        <v>1</v>
-      </c>
-      <c r="K199">
+      <c r="J199">
         <v>1</v>
       </c>
     </row>
@@ -25899,16 +25646,10 @@
       <c r="D200" t="s">
         <v>49</v>
       </c>
-      <c r="N200">
-        <v>1</v>
-      </c>
-      <c r="O200">
+      <c r="M200">
         <v>1</v>
       </c>
       <c r="W200">
-        <v>1</v>
-      </c>
-      <c r="Z200">
         <v>1</v>
       </c>
     </row>
@@ -25926,12 +25667,9 @@
         <v>52</v>
       </c>
       <c r="E201">
-        <v>2</v>
-      </c>
-      <c r="F201">
-        <v>1</v>
-      </c>
-      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="J201">
         <v>1</v>
       </c>
     </row>
@@ -25962,10 +25700,7 @@
       <c r="D203" t="s">
         <v>43</v>
       </c>
-      <c r="N203">
-        <v>1</v>
-      </c>
-      <c r="O203">
+      <c r="M203">
         <v>1</v>
       </c>
     </row>
@@ -25997,24 +25732,18 @@
         <v>49</v>
       </c>
       <c r="E205">
-        <v>2</v>
-      </c>
-      <c r="F205">
-        <v>1</v>
-      </c>
-      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="J205">
         <v>1</v>
       </c>
       <c r="W205">
         <v>1</v>
       </c>
-      <c r="Z205">
-        <v>1</v>
-      </c>
-      <c r="AI205">
-        <v>1</v>
-      </c>
-      <c r="AJ205">
+      <c r="AF205">
+        <v>1</v>
+      </c>
+      <c r="AG205">
         <v>1</v>
       </c>
     </row>
@@ -26034,9 +25763,6 @@
       <c r="E206">
         <v>1</v>
       </c>
-      <c r="F206">
-        <v>1</v>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
@@ -26051,6 +25777,9 @@
       <c r="D207" t="s">
         <v>40</v>
       </c>
+      <c r="AJ207">
+        <v>1</v>
+      </c>
       <c r="AM207">
         <v>1</v>
       </c>
@@ -26082,13 +25811,10 @@
       <c r="D209" t="s">
         <v>46</v>
       </c>
-      <c r="N209">
-        <v>2</v>
-      </c>
-      <c r="O209">
-        <v>1</v>
-      </c>
-      <c r="S209">
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="Q209">
         <v>1</v>
       </c>
     </row>
@@ -26108,9 +25834,6 @@
       <c r="W210">
         <v>1</v>
       </c>
-      <c r="Z210">
-        <v>1</v>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
@@ -26125,13 +25848,10 @@
       <c r="D211" t="s">
         <v>52</v>
       </c>
-      <c r="W211">
-        <v>1</v>
-      </c>
-      <c r="Y211">
-        <v>1</v>
-      </c>
-      <c r="AI211">
+      <c r="V211">
+        <v>1</v>
+      </c>
+      <c r="AF211">
         <v>1</v>
       </c>
     </row>
@@ -26176,7 +25896,7 @@
       <c r="D214" t="s">
         <v>46</v>
       </c>
-      <c r="AH214">
+      <c r="AE214">
         <v>1</v>
       </c>
     </row>
@@ -26196,9 +25916,6 @@
       <c r="W215">
         <v>1</v>
       </c>
-      <c r="Z215">
-        <v>1</v>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
@@ -26213,10 +25930,10 @@
       <c r="D216" t="s">
         <v>52</v>
       </c>
-      <c r="N216">
-        <v>1</v>
-      </c>
-      <c r="O216">
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="AJ216">
         <v>1</v>
       </c>
       <c r="AM216">
@@ -26279,18 +25996,12 @@
         <v>49</v>
       </c>
       <c r="E220">
-        <v>2</v>
-      </c>
-      <c r="F220">
-        <v>1</v>
-      </c>
-      <c r="K220">
-        <v>1</v>
-      </c>
-      <c r="W220">
-        <v>1</v>
-      </c>
-      <c r="AB220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="Y220">
         <v>1</v>
       </c>
     </row>
@@ -26307,22 +26018,13 @@
       <c r="D221" t="s">
         <v>52</v>
       </c>
-      <c r="E221">
-        <v>1</v>
-      </c>
-      <c r="G221">
-        <v>1</v>
-      </c>
-      <c r="N221">
-        <v>1</v>
-      </c>
-      <c r="O221">
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="M221">
         <v>1</v>
       </c>
       <c r="W221">
-        <v>1</v>
-      </c>
-      <c r="Z221">
         <v>1</v>
       </c>
     </row>
@@ -26339,6 +26041,9 @@
       <c r="D222" t="s">
         <v>40</v>
       </c>
+      <c r="AK222">
+        <v>1</v>
+      </c>
       <c r="AN222">
         <v>1</v>
       </c>
@@ -26356,6 +26061,9 @@
       <c r="D223" t="s">
         <v>43</v>
       </c>
+      <c r="AJ223">
+        <v>1</v>
+      </c>
       <c r="AM223">
         <v>1</v>
       </c>
@@ -26373,10 +26081,10 @@
       <c r="D224" t="s">
         <v>46</v>
       </c>
-      <c r="AI224">
-        <v>1</v>
-      </c>
-      <c r="AJ224">
+      <c r="AF224">
+        <v>1</v>
+      </c>
+      <c r="AG224">
         <v>1</v>
       </c>
     </row>
@@ -26393,16 +26101,10 @@
       <c r="D225" t="s">
         <v>49</v>
       </c>
-      <c r="E225">
-        <v>1</v>
-      </c>
-      <c r="K225">
-        <v>1</v>
-      </c>
-      <c r="N225">
-        <v>1</v>
-      </c>
-      <c r="O225">
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="M225">
         <v>1</v>
       </c>
     </row>
@@ -26419,16 +26121,10 @@
       <c r="D226" t="s">
         <v>52</v>
       </c>
-      <c r="E226">
-        <v>1</v>
-      </c>
-      <c r="K226">
-        <v>1</v>
-      </c>
-      <c r="N226">
-        <v>1</v>
-      </c>
-      <c r="O226">
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="M226">
         <v>1</v>
       </c>
     </row>
@@ -26459,19 +26155,16 @@
       <c r="D228" t="s">
         <v>43</v>
       </c>
-      <c r="N228">
-        <v>1</v>
-      </c>
-      <c r="O228">
+      <c r="M228">
+        <v>1</v>
+      </c>
+      <c r="AD228">
+        <v>1</v>
+      </c>
+      <c r="AF228">
         <v>1</v>
       </c>
       <c r="AG228">
-        <v>1</v>
-      </c>
-      <c r="AI228">
-        <v>1</v>
-      </c>
-      <c r="AJ228">
         <v>1</v>
       </c>
     </row>
@@ -26488,6 +26181,9 @@
       <c r="D229" t="s">
         <v>46</v>
       </c>
+      <c r="AK229">
+        <v>1</v>
+      </c>
       <c r="AN229">
         <v>1</v>
       </c>
@@ -26506,7 +26202,7 @@
         <v>49</v>
       </c>
       <c r="E230">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F230">
         <v>1</v>
@@ -26514,13 +26210,10 @@
       <c r="G230">
         <v>1</v>
       </c>
-      <c r="H230">
-        <v>1</v>
-      </c>
-      <c r="AI230">
-        <v>1</v>
-      </c>
-      <c r="AJ230">
+      <c r="AF230">
+        <v>1</v>
+      </c>
+      <c r="AG230">
         <v>1</v>
       </c>
     </row>
@@ -26537,13 +26230,10 @@
       <c r="D231" t="s">
         <v>52</v>
       </c>
-      <c r="N231">
-        <v>1</v>
-      </c>
-      <c r="O231">
-        <v>1</v>
-      </c>
-      <c r="AI231">
+      <c r="M231">
+        <v>1</v>
+      </c>
+      <c r="AF231">
         <v>1</v>
       </c>
     </row>
@@ -26588,10 +26278,7 @@
       <c r="D234" t="s">
         <v>46</v>
       </c>
-      <c r="W234">
-        <v>1</v>
-      </c>
-      <c r="AB234">
+      <c r="Y234">
         <v>1</v>
       </c>
     </row>
@@ -26608,16 +26295,13 @@
       <c r="D235" t="s">
         <v>49</v>
       </c>
-      <c r="N235">
-        <v>1</v>
-      </c>
-      <c r="O235">
-        <v>1</v>
-      </c>
-      <c r="AI235">
-        <v>1</v>
-      </c>
-      <c r="AJ235">
+      <c r="M235">
+        <v>1</v>
+      </c>
+      <c r="AF235">
+        <v>1</v>
+      </c>
+      <c r="AG235">
         <v>1</v>
       </c>
     </row>
@@ -26662,10 +26346,7 @@
       <c r="D238" t="s">
         <v>43</v>
       </c>
-      <c r="W238">
-        <v>1</v>
-      </c>
-      <c r="AA238">
+      <c r="X238">
         <v>1</v>
       </c>
     </row>
@@ -26696,10 +26377,7 @@
       <c r="D240" t="s">
         <v>49</v>
       </c>
-      <c r="E240">
-        <v>1</v>
-      </c>
-      <c r="K240">
+      <c r="J240">
         <v>1</v>
       </c>
     </row>
@@ -26716,13 +26394,10 @@
       <c r="D241" t="s">
         <v>52</v>
       </c>
-      <c r="N241">
-        <v>1</v>
-      </c>
-      <c r="O241">
-        <v>1</v>
-      </c>
-      <c r="AI241">
+      <c r="M241">
+        <v>1</v>
+      </c>
+      <c r="AF241">
         <v>1</v>
       </c>
     </row>
@@ -26753,22 +26428,16 @@
       <c r="D243" t="s">
         <v>43</v>
       </c>
-      <c r="E243">
-        <v>1</v>
-      </c>
-      <c r="H243">
-        <v>1</v>
-      </c>
-      <c r="W243">
-        <v>1</v>
-      </c>
-      <c r="X243">
-        <v>1</v>
-      </c>
-      <c r="AI243">
-        <v>1</v>
-      </c>
-      <c r="AJ243">
+      <c r="G243">
+        <v>1</v>
+      </c>
+      <c r="U243">
+        <v>1</v>
+      </c>
+      <c r="AF243">
+        <v>1</v>
+      </c>
+      <c r="AG243">
         <v>1</v>
       </c>
     </row>
@@ -26785,6 +26454,9 @@
       <c r="D244" t="s">
         <v>46</v>
       </c>
+      <c r="AJ244">
+        <v>1</v>
+      </c>
       <c r="AM244">
         <v>1</v>
       </c>
@@ -26802,10 +26474,7 @@
       <c r="D245" t="s">
         <v>49</v>
       </c>
-      <c r="N245">
-        <v>1</v>
-      </c>
-      <c r="O245">
+      <c r="M245">
         <v>1</v>
       </c>
     </row>
@@ -26825,9 +26494,6 @@
       <c r="E246">
         <v>1</v>
       </c>
-      <c r="F246">
-        <v>1</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
@@ -26842,6 +26508,9 @@
       <c r="D247" t="s">
         <v>40</v>
       </c>
+      <c r="AK247">
+        <v>1</v>
+      </c>
       <c r="AN247">
         <v>1</v>
       </c>
@@ -26862,9 +26531,6 @@
       <c r="E248">
         <v>1</v>
       </c>
-      <c r="F248">
-        <v>1</v>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
@@ -26879,10 +26545,10 @@
       <c r="D249" t="s">
         <v>46</v>
       </c>
-      <c r="N249">
-        <v>1</v>
-      </c>
-      <c r="O249">
+      <c r="M249">
+        <v>1</v>
+      </c>
+      <c r="AK249">
         <v>1</v>
       </c>
       <c r="AN249">
@@ -26919,9 +26585,6 @@
       <c r="E251">
         <v>1</v>
       </c>
-      <c r="F251">
-        <v>1</v>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
@@ -26953,13 +26616,7 @@
       <c r="E253">
         <v>1</v>
       </c>
-      <c r="F253">
-        <v>1</v>
-      </c>
-      <c r="W253">
-        <v>1</v>
-      </c>
-      <c r="X253">
+      <c r="U253">
         <v>1</v>
       </c>
     </row>
@@ -26976,10 +26633,7 @@
       <c r="D254" t="s">
         <v>46</v>
       </c>
-      <c r="N254">
-        <v>1</v>
-      </c>
-      <c r="O254">
+      <c r="M254">
         <v>1</v>
       </c>
     </row>
@@ -27013,13 +26667,7 @@
       <c r="E256">
         <v>1</v>
       </c>
-      <c r="F256">
-        <v>1</v>
-      </c>
-      <c r="W256">
-        <v>1</v>
-      </c>
-      <c r="AA256">
+      <c r="X256">
         <v>1</v>
       </c>
     </row>
@@ -27050,10 +26698,7 @@
       <c r="D258" t="s">
         <v>43</v>
       </c>
-      <c r="W258">
-        <v>1</v>
-      </c>
-      <c r="AA258">
+      <c r="X258">
         <v>1</v>
       </c>
     </row>
@@ -27084,13 +26729,10 @@
       <c r="D260" t="s">
         <v>49</v>
       </c>
-      <c r="E260">
-        <v>1</v>
-      </c>
-      <c r="K260">
-        <v>1</v>
-      </c>
-      <c r="AK260">
+      <c r="J260">
+        <v>1</v>
+      </c>
+      <c r="AH260">
         <v>1</v>
       </c>
     </row>
@@ -27121,6 +26763,9 @@
       <c r="D262" t="s">
         <v>40</v>
       </c>
+      <c r="AK262">
+        <v>1</v>
+      </c>
       <c r="AN262">
         <v>1</v>
       </c>
@@ -27138,22 +26783,16 @@
       <c r="D263" t="s">
         <v>43</v>
       </c>
-      <c r="N263">
-        <v>1</v>
-      </c>
-      <c r="O263">
-        <v>1</v>
-      </c>
-      <c r="W263">
-        <v>1</v>
-      </c>
-      <c r="AA263">
-        <v>1</v>
-      </c>
-      <c r="AI263">
-        <v>1</v>
-      </c>
-      <c r="AJ263">
+      <c r="M263">
+        <v>1</v>
+      </c>
+      <c r="X263">
+        <v>1</v>
+      </c>
+      <c r="AF263">
+        <v>1</v>
+      </c>
+      <c r="AG263">
         <v>1</v>
       </c>
     </row>
@@ -27185,12 +26824,12 @@
         <v>49</v>
       </c>
       <c r="E265">
-        <v>2</v>
-      </c>
-      <c r="F265">
-        <v>1</v>
-      </c>
-      <c r="H265">
+        <v>1</v>
+      </c>
+      <c r="G265">
+        <v>1</v>
+      </c>
+      <c r="AK265">
         <v>1</v>
       </c>
       <c r="AN265">
@@ -27224,7 +26863,13 @@
       <c r="D267" t="s">
         <v>40</v>
       </c>
-      <c r="AG267">
+      <c r="AD267">
+        <v>1</v>
+      </c>
+      <c r="AJ267">
+        <v>1</v>
+      </c>
+      <c r="AK267">
         <v>1</v>
       </c>
       <c r="AM267">
@@ -27261,13 +26906,10 @@
       <c r="D269" t="s">
         <v>46</v>
       </c>
-      <c r="E269">
-        <v>1</v>
-      </c>
-      <c r="H269">
-        <v>1</v>
-      </c>
-      <c r="AI269">
+      <c r="G269">
+        <v>1</v>
+      </c>
+      <c r="AF269">
         <v>1</v>
       </c>
     </row>
@@ -27284,10 +26926,10 @@
       <c r="D270" t="s">
         <v>49</v>
       </c>
-      <c r="N270">
-        <v>1</v>
-      </c>
-      <c r="O270">
+      <c r="M270">
+        <v>1</v>
+      </c>
+      <c r="AJ270">
         <v>1</v>
       </c>
       <c r="AM270">
@@ -27307,16 +26949,16 @@
       <c r="D271" t="s">
         <v>52</v>
       </c>
-      <c r="N271">
-        <v>1</v>
-      </c>
-      <c r="O271">
-        <v>1</v>
-      </c>
-      <c r="AG271">
-        <v>1</v>
-      </c>
-      <c r="AI271">
+      <c r="M271">
+        <v>1</v>
+      </c>
+      <c r="AD271">
+        <v>1</v>
+      </c>
+      <c r="AF271">
+        <v>1</v>
+      </c>
+      <c r="AJ271">
         <v>1</v>
       </c>
       <c r="AM271">
@@ -27336,7 +26978,7 @@
       <c r="D272" t="s">
         <v>40</v>
       </c>
-      <c r="AE272">
+      <c r="AB272">
         <v>1</v>
       </c>
     </row>
@@ -27367,16 +27009,13 @@
       <c r="D274" t="s">
         <v>46</v>
       </c>
-      <c r="N274">
-        <v>1</v>
-      </c>
-      <c r="O274">
-        <v>1</v>
-      </c>
-      <c r="AI274">
-        <v>1</v>
-      </c>
-      <c r="AJ274">
+      <c r="M274">
+        <v>1</v>
+      </c>
+      <c r="AF274">
+        <v>1</v>
+      </c>
+      <c r="AG274">
         <v>1</v>
       </c>
     </row>
@@ -27393,10 +27032,7 @@
       <c r="D275" t="s">
         <v>49</v>
       </c>
-      <c r="E275">
-        <v>1</v>
-      </c>
-      <c r="H275">
+      <c r="G275">
         <v>1</v>
       </c>
     </row>
@@ -27442,18 +27078,12 @@
         <v>43</v>
       </c>
       <c r="E278">
-        <v>2</v>
-      </c>
-      <c r="F278">
-        <v>1</v>
-      </c>
-      <c r="K278">
-        <v>1</v>
-      </c>
-      <c r="N278">
-        <v>1</v>
-      </c>
-      <c r="O278">
+        <v>1</v>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="M278">
         <v>1</v>
       </c>
     </row>
@@ -27471,18 +27101,12 @@
         <v>46</v>
       </c>
       <c r="E279">
-        <v>2</v>
-      </c>
-      <c r="F279">
-        <v>1</v>
-      </c>
-      <c r="K279">
-        <v>1</v>
-      </c>
-      <c r="W279">
-        <v>1</v>
-      </c>
-      <c r="Y279">
+        <v>1</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="V279">
         <v>1</v>
       </c>
     </row>
@@ -27500,12 +27124,9 @@
         <v>49</v>
       </c>
       <c r="W280">
-        <v>2</v>
-      </c>
-      <c r="Z280">
-        <v>1</v>
-      </c>
-      <c r="AA280">
+        <v>1</v>
+      </c>
+      <c r="X280">
         <v>1</v>
       </c>
     </row>
@@ -27523,21 +27144,18 @@
         <v>52</v>
       </c>
       <c r="E281">
-        <v>3</v>
-      </c>
-      <c r="F281">
-        <v>1</v>
-      </c>
-      <c r="H281">
-        <v>1</v>
-      </c>
-      <c r="K281">
-        <v>1</v>
-      </c>
-      <c r="AD281">
-        <v>1</v>
-      </c>
-      <c r="AH281">
+        <v>1</v>
+      </c>
+      <c r="G281">
+        <v>1</v>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="AA281">
+        <v>1</v>
+      </c>
+      <c r="AE281">
         <v>1</v>
       </c>
     </row>
@@ -27582,10 +27200,10 @@
       <c r="D284" t="s">
         <v>46</v>
       </c>
-      <c r="AI284">
-        <v>1</v>
-      </c>
-      <c r="AJ284">
+      <c r="AF284">
+        <v>1</v>
+      </c>
+      <c r="AG284">
         <v>1</v>
       </c>
     </row>
@@ -27602,6 +27220,9 @@
       <c r="D285" t="s">
         <v>49</v>
       </c>
+      <c r="AK285">
+        <v>1</v>
+      </c>
       <c r="AN285">
         <v>1</v>
       </c>
@@ -27622,9 +27243,6 @@
       <c r="W286">
         <v>1</v>
       </c>
-      <c r="Z286">
-        <v>1</v>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
@@ -27639,10 +27257,7 @@
       <c r="D287" t="s">
         <v>40</v>
       </c>
-      <c r="W287">
-        <v>1</v>
-      </c>
-      <c r="Y287">
+      <c r="V287">
         <v>1</v>
       </c>
     </row>
@@ -27659,10 +27274,10 @@
       <c r="D288" t="s">
         <v>43</v>
       </c>
-      <c r="AI288">
-        <v>1</v>
-      </c>
-      <c r="AJ288">
+      <c r="AF288">
+        <v>1</v>
+      </c>
+      <c r="AG288">
         <v>1</v>
       </c>
     </row>
@@ -27679,6 +27294,9 @@
       <c r="D289" t="s">
         <v>46</v>
       </c>
+      <c r="AJ289">
+        <v>1</v>
+      </c>
       <c r="AM289">
         <v>1</v>
       </c>
@@ -27696,10 +27314,7 @@
       <c r="D290" t="s">
         <v>49</v>
       </c>
-      <c r="N290">
-        <v>1</v>
-      </c>
-      <c r="O290">
+      <c r="M290">
         <v>1</v>
       </c>
     </row>
@@ -27719,19 +27334,13 @@
       <c r="E291">
         <v>1</v>
       </c>
-      <c r="F291">
+      <c r="U291">
         <v>1</v>
       </c>
       <c r="W291">
-        <v>2</v>
-      </c>
-      <c r="X291">
-        <v>1</v>
-      </c>
-      <c r="Z291">
-        <v>1</v>
-      </c>
-      <c r="AH291">
+        <v>1</v>
+      </c>
+      <c r="AE291">
         <v>1</v>
       </c>
     </row>
@@ -27762,16 +27371,13 @@
       <c r="D293" t="s">
         <v>43</v>
       </c>
-      <c r="N293">
-        <v>1</v>
-      </c>
-      <c r="O293">
-        <v>1</v>
-      </c>
-      <c r="AI293">
-        <v>1</v>
-      </c>
-      <c r="AJ293">
+      <c r="M293">
+        <v>1</v>
+      </c>
+      <c r="AF293">
+        <v>1</v>
+      </c>
+      <c r="AG293">
         <v>1</v>
       </c>
     </row>
@@ -27788,10 +27394,7 @@
       <c r="D294" t="s">
         <v>46</v>
       </c>
-      <c r="E294">
-        <v>1</v>
-      </c>
-      <c r="H294">
+      <c r="G294">
         <v>1</v>
       </c>
     </row>
@@ -27808,6 +27411,9 @@
       <c r="D295" t="s">
         <v>49</v>
       </c>
+      <c r="AK295">
+        <v>1</v>
+      </c>
       <c r="AN295">
         <v>1</v>
       </c>
@@ -27825,10 +27431,7 @@
       <c r="D296" t="s">
         <v>52</v>
       </c>
-      <c r="E296">
-        <v>1</v>
-      </c>
-      <c r="H296">
+      <c r="G296">
         <v>1</v>
       </c>
     </row>
@@ -27845,7 +27448,7 @@
       <c r="D297" t="s">
         <v>40</v>
       </c>
-      <c r="AH297">
+      <c r="AE297">
         <v>1</v>
       </c>
     </row>
@@ -27876,10 +27479,7 @@
       <c r="D299" t="s">
         <v>46</v>
       </c>
-      <c r="N299">
-        <v>1</v>
-      </c>
-      <c r="O299">
+      <c r="M299">
         <v>1</v>
       </c>
     </row>
@@ -27966,10 +27566,7 @@
       <c r="D305" t="s">
         <v>49</v>
       </c>
-      <c r="N305">
-        <v>1</v>
-      </c>
-      <c r="O305">
+      <c r="M305">
         <v>1</v>
       </c>
     </row>
@@ -27986,7 +27583,7 @@
       <c r="D306" t="s">
         <v>52</v>
       </c>
-      <c r="AD306">
+      <c r="AA306">
         <v>1</v>
       </c>
     </row>
@@ -28003,7 +27600,7 @@
       <c r="D307" t="s">
         <v>40</v>
       </c>
-      <c r="AE307">
+      <c r="AB307">
         <v>1</v>
       </c>
     </row>
@@ -28034,6 +27631,9 @@
       <c r="D309" t="s">
         <v>46</v>
       </c>
+      <c r="AK309">
+        <v>1</v>
+      </c>
       <c r="AN309">
         <v>1</v>
       </c>
@@ -28051,7 +27651,7 @@
       <c r="D310" t="s">
         <v>49</v>
       </c>
-      <c r="AD310">
+      <c r="AA310">
         <v>1</v>
       </c>
     </row>
@@ -28082,6 +27682,9 @@
       <c r="D312" t="s">
         <v>40</v>
       </c>
+      <c r="AK312">
+        <v>1</v>
+      </c>
       <c r="AN312">
         <v>1</v>
       </c>
@@ -28099,16 +27702,13 @@
       <c r="D313" t="s">
         <v>43</v>
       </c>
-      <c r="N313">
-        <v>1</v>
-      </c>
-      <c r="O313">
-        <v>1</v>
-      </c>
-      <c r="AI313">
-        <v>1</v>
-      </c>
-      <c r="AJ313">
+      <c r="M313">
+        <v>1</v>
+      </c>
+      <c r="AF313">
+        <v>1</v>
+      </c>
+      <c r="AG313">
         <v>1</v>
       </c>
     </row>
@@ -28125,6 +27725,9 @@
       <c r="D314" t="s">
         <v>46</v>
       </c>
+      <c r="AK314">
+        <v>1</v>
+      </c>
       <c r="AN314">
         <v>1</v>
       </c>
@@ -28142,7 +27745,7 @@
       <c r="D315" t="s">
         <v>49</v>
       </c>
-      <c r="AG315">
+      <c r="AD315">
         <v>1</v>
       </c>
     </row>
@@ -28159,7 +27762,7 @@
       <c r="D316" t="s">
         <v>52</v>
       </c>
-      <c r="AH316">
+      <c r="AE316">
         <v>1</v>
       </c>
     </row>
@@ -28193,9 +27796,6 @@
       <c r="W318">
         <v>1</v>
       </c>
-      <c r="Z318">
-        <v>1</v>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
@@ -28213,13 +27813,7 @@
       <c r="E319">
         <v>1</v>
       </c>
-      <c r="F319">
-        <v>1</v>
-      </c>
-      <c r="N319">
-        <v>1</v>
-      </c>
-      <c r="O319">
+      <c r="M319">
         <v>1</v>
       </c>
     </row>
@@ -28250,16 +27844,13 @@
       <c r="D321" t="s">
         <v>52</v>
       </c>
-      <c r="W321">
-        <v>2</v>
-      </c>
-      <c r="Y321">
-        <v>1</v>
-      </c>
-      <c r="AA321">
-        <v>1</v>
-      </c>
-      <c r="AH321">
+      <c r="V321">
+        <v>1</v>
+      </c>
+      <c r="X321">
+        <v>1</v>
+      </c>
+      <c r="AE321">
         <v>1</v>
       </c>
     </row>
@@ -28276,10 +27867,7 @@
       <c r="D322" t="s">
         <v>40</v>
       </c>
-      <c r="E322">
-        <v>1</v>
-      </c>
-      <c r="K322">
+      <c r="J322">
         <v>1</v>
       </c>
     </row>
@@ -28296,10 +27884,10 @@
       <c r="D323" t="s">
         <v>43</v>
       </c>
-      <c r="AI323">
-        <v>1</v>
-      </c>
-      <c r="AJ323">
+      <c r="AF323">
+        <v>1</v>
+      </c>
+      <c r="AG323">
         <v>1</v>
       </c>
     </row>
@@ -28330,6 +27918,9 @@
       <c r="D325" t="s">
         <v>49</v>
       </c>
+      <c r="AK325">
+        <v>1</v>
+      </c>
       <c r="AN325">
         <v>1</v>
       </c>
@@ -28361,10 +27952,7 @@
       <c r="D327" t="s">
         <v>40</v>
       </c>
-      <c r="N327">
-        <v>1</v>
-      </c>
-      <c r="O327">
+      <c r="M327">
         <v>1</v>
       </c>
     </row>
@@ -28395,16 +27983,13 @@
       <c r="D329" t="s">
         <v>46</v>
       </c>
-      <c r="N329">
-        <v>1</v>
-      </c>
-      <c r="O329">
-        <v>1</v>
-      </c>
-      <c r="AI329">
-        <v>1</v>
-      </c>
-      <c r="AJ329">
+      <c r="M329">
+        <v>1</v>
+      </c>
+      <c r="AF329">
+        <v>1</v>
+      </c>
+      <c r="AG329">
         <v>1</v>
       </c>
     </row>
@@ -28424,10 +28009,7 @@
       <c r="W330">
         <v>1</v>
       </c>
-      <c r="Z330">
-        <v>1</v>
-      </c>
-      <c r="AE330">
+      <c r="AB330">
         <v>1</v>
       </c>
     </row>
@@ -28444,6 +28026,9 @@
       <c r="D331" t="s">
         <v>52</v>
       </c>
+      <c r="AK331">
+        <v>1</v>
+      </c>
       <c r="AN331">
         <v>1</v>
       </c>
@@ -28478,9 +28063,6 @@
       <c r="W333">
         <v>1</v>
       </c>
-      <c r="Z333">
-        <v>1</v>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
@@ -28495,10 +28077,7 @@
       <c r="D334" t="s">
         <v>46</v>
       </c>
-      <c r="N334">
-        <v>1</v>
-      </c>
-      <c r="O334">
+      <c r="M334">
         <v>1</v>
       </c>
     </row>
@@ -28515,13 +28094,10 @@
       <c r="D335" t="s">
         <v>49</v>
       </c>
-      <c r="N335">
-        <v>1</v>
-      </c>
-      <c r="O335">
-        <v>1</v>
-      </c>
-      <c r="AG335">
+      <c r="M335">
+        <v>1</v>
+      </c>
+      <c r="AD335">
         <v>1</v>
       </c>
     </row>
@@ -28538,7 +28114,7 @@
       <c r="D336" t="s">
         <v>52</v>
       </c>
-      <c r="AH336">
+      <c r="AE336">
         <v>1</v>
       </c>
     </row>
@@ -28555,7 +28131,10 @@
       <c r="D337" t="s">
         <v>773</v>
       </c>
-      <c r="AH337">
+      <c r="AE337">
+        <v>1</v>
+      </c>
+      <c r="AK337">
         <v>1</v>
       </c>
       <c r="AN337">
@@ -28578,22 +28157,16 @@
       <c r="E338">
         <v>1</v>
       </c>
-      <c r="F338">
-        <v>1</v>
-      </c>
-      <c r="N338">
-        <v>1</v>
-      </c>
-      <c r="O338">
-        <v>1</v>
-      </c>
-      <c r="W338">
-        <v>1</v>
-      </c>
-      <c r="Y338">
-        <v>1</v>
-      </c>
-      <c r="AI338">
+      <c r="M338">
+        <v>1</v>
+      </c>
+      <c r="V338">
+        <v>1</v>
+      </c>
+      <c r="AF338">
+        <v>1</v>
+      </c>
+      <c r="AJ338">
         <v>1</v>
       </c>
       <c r="AM338">
@@ -28627,10 +28200,10 @@
       <c r="D340" t="s">
         <v>49</v>
       </c>
-      <c r="W340">
-        <v>1</v>
-      </c>
-      <c r="X340">
+      <c r="U340">
+        <v>1</v>
+      </c>
+      <c r="AK340">
         <v>1</v>
       </c>
       <c r="AN340">
@@ -28653,16 +28226,13 @@
       <c r="E341">
         <v>1</v>
       </c>
-      <c r="F341">
-        <v>1</v>
-      </c>
-      <c r="W341">
-        <v>1</v>
-      </c>
-      <c r="X341">
-        <v>1</v>
-      </c>
-      <c r="AI341">
+      <c r="U341">
+        <v>1</v>
+      </c>
+      <c r="AF341">
+        <v>1</v>
+      </c>
+      <c r="AK341">
         <v>1</v>
       </c>
       <c r="AN341">
@@ -28682,7 +28252,7 @@
       <c r="D342" t="s">
         <v>40</v>
       </c>
-      <c r="AH342">
+      <c r="AE342">
         <v>1</v>
       </c>
     </row>
@@ -28699,10 +28269,10 @@
       <c r="D343" t="s">
         <v>43</v>
       </c>
-      <c r="AI343">
-        <v>1</v>
-      </c>
-      <c r="AJ343">
+      <c r="AF343">
+        <v>1</v>
+      </c>
+      <c r="AG343">
         <v>1</v>
       </c>
     </row>
@@ -28733,10 +28303,7 @@
       <c r="D345" t="s">
         <v>49</v>
       </c>
-      <c r="N345">
-        <v>1</v>
-      </c>
-      <c r="O345">
+      <c r="M345">
         <v>1</v>
       </c>
     </row>
@@ -28753,7 +28320,7 @@
       <c r="D346" t="s">
         <v>52</v>
       </c>
-      <c r="AG346">
+      <c r="AD346">
         <v>1</v>
       </c>
     </row>
@@ -28801,10 +28368,7 @@
       <c r="W349">
         <v>1</v>
       </c>
-      <c r="Z349">
-        <v>1</v>
-      </c>
-      <c r="AD349">
+      <c r="AA349">
         <v>1</v>
       </c>
     </row>
@@ -28821,22 +28385,16 @@
       <c r="D350" t="s">
         <v>49</v>
       </c>
-      <c r="E350">
-        <v>1</v>
-      </c>
-      <c r="H350">
-        <v>1</v>
-      </c>
-      <c r="N350">
-        <v>1</v>
-      </c>
-      <c r="O350">
-        <v>1</v>
-      </c>
-      <c r="AI350">
-        <v>1</v>
-      </c>
-      <c r="AJ350">
+      <c r="G350">
+        <v>1</v>
+      </c>
+      <c r="M350">
+        <v>1</v>
+      </c>
+      <c r="AF350">
+        <v>1</v>
+      </c>
+      <c r="AG350">
         <v>1</v>
       </c>
     </row>
@@ -28853,31 +28411,22 @@
       <c r="D351" t="s">
         <v>52</v>
       </c>
-      <c r="E351">
-        <v>1</v>
-      </c>
-      <c r="H351">
-        <v>1</v>
-      </c>
-      <c r="N351">
-        <v>1</v>
-      </c>
-      <c r="O351">
+      <c r="G351">
+        <v>1</v>
+      </c>
+      <c r="M351">
         <v>1</v>
       </c>
       <c r="W351">
         <v>1</v>
       </c>
-      <c r="Z351">
-        <v>1</v>
-      </c>
-      <c r="AD351">
-        <v>1</v>
-      </c>
-      <c r="AI351">
-        <v>1</v>
-      </c>
-      <c r="AJ351">
+      <c r="AA351">
+        <v>1</v>
+      </c>
+      <c r="AF351">
+        <v>1</v>
+      </c>
+      <c r="AG351">
         <v>1</v>
       </c>
     </row>
@@ -28908,19 +28457,16 @@
       <c r="D353" t="s">
         <v>43</v>
       </c>
-      <c r="W353">
-        <v>1</v>
-      </c>
-      <c r="X353">
+      <c r="U353">
+        <v>1</v>
+      </c>
+      <c r="AD353">
+        <v>1</v>
+      </c>
+      <c r="AF353">
         <v>1</v>
       </c>
       <c r="AG353">
-        <v>1</v>
-      </c>
-      <c r="AI353">
-        <v>1</v>
-      </c>
-      <c r="AJ353">
         <v>1</v>
       </c>
     </row>
@@ -28937,10 +28483,7 @@
       <c r="D354" t="s">
         <v>46</v>
       </c>
-      <c r="W354">
-        <v>1</v>
-      </c>
-      <c r="AA354">
+      <c r="X354">
         <v>1</v>
       </c>
     </row>
@@ -28957,10 +28500,7 @@
       <c r="D355" t="s">
         <v>49</v>
       </c>
-      <c r="N355">
-        <v>1</v>
-      </c>
-      <c r="O355">
+      <c r="M355">
         <v>1</v>
       </c>
     </row>
@@ -28978,12 +28518,9 @@
         <v>52</v>
       </c>
       <c r="E356">
-        <v>2</v>
-      </c>
-      <c r="F356">
-        <v>1</v>
-      </c>
-      <c r="H356">
+        <v>1</v>
+      </c>
+      <c r="G356">
         <v>1</v>
       </c>
     </row>
@@ -29014,10 +28551,7 @@
       <c r="D358" t="s">
         <v>43</v>
       </c>
-      <c r="E358">
-        <v>1</v>
-      </c>
-      <c r="K358">
+      <c r="J358">
         <v>1</v>
       </c>
     </row>
@@ -29048,16 +28582,10 @@
       <c r="D360" t="s">
         <v>49</v>
       </c>
-      <c r="E360">
-        <v>1</v>
-      </c>
-      <c r="H360">
-        <v>1</v>
-      </c>
-      <c r="W360">
-        <v>1</v>
-      </c>
-      <c r="X360">
+      <c r="G360">
+        <v>1</v>
+      </c>
+      <c r="U360">
         <v>1</v>
       </c>
     </row>
@@ -29074,16 +28602,10 @@
       <c r="D361" t="s">
         <v>52</v>
       </c>
-      <c r="E361">
-        <v>1</v>
-      </c>
-      <c r="K361">
-        <v>1</v>
-      </c>
-      <c r="N361">
-        <v>1</v>
-      </c>
-      <c r="O361">
+      <c r="J361">
+        <v>1</v>
+      </c>
+      <c r="M361">
         <v>1</v>
       </c>
     </row>
@@ -29114,6 +28636,9 @@
       <c r="D363" t="s">
         <v>43</v>
       </c>
+      <c r="AK363">
+        <v>1</v>
+      </c>
       <c r="AN363">
         <v>1</v>
       </c>
@@ -29134,9 +28659,6 @@
       <c r="W364">
         <v>1</v>
       </c>
-      <c r="Z364">
-        <v>1</v>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="s">
@@ -29151,16 +28673,13 @@
       <c r="D365" t="s">
         <v>49</v>
       </c>
-      <c r="N365">
-        <v>1</v>
-      </c>
-      <c r="O365">
-        <v>1</v>
-      </c>
-      <c r="AI365">
-        <v>1</v>
-      </c>
-      <c r="AJ365">
+      <c r="M365">
+        <v>1</v>
+      </c>
+      <c r="AF365">
+        <v>1</v>
+      </c>
+      <c r="AG365">
         <v>1</v>
       </c>
     </row>
@@ -29177,19 +28696,13 @@
       <c r="D366" t="s">
         <v>52</v>
       </c>
-      <c r="E366">
-        <v>1</v>
-      </c>
-      <c r="I366">
-        <v>1</v>
-      </c>
-      <c r="N366">
-        <v>2</v>
-      </c>
-      <c r="O366">
-        <v>1</v>
-      </c>
-      <c r="U366">
+      <c r="H366">
+        <v>1</v>
+      </c>
+      <c r="M366">
+        <v>1</v>
+      </c>
+      <c r="S366">
         <v>1</v>
       </c>
     </row>
@@ -29220,16 +28733,13 @@
       <c r="D368" t="s">
         <v>43</v>
       </c>
-      <c r="N368">
-        <v>1</v>
-      </c>
-      <c r="O368">
-        <v>1</v>
-      </c>
-      <c r="AI368">
-        <v>1</v>
-      </c>
-      <c r="AJ368">
+      <c r="M368">
+        <v>1</v>
+      </c>
+      <c r="AF368">
+        <v>1</v>
+      </c>
+      <c r="AG368">
         <v>1</v>
       </c>
     </row>
@@ -29246,10 +28756,7 @@
       <c r="D369" t="s">
         <v>46</v>
       </c>
-      <c r="E369">
-        <v>1</v>
-      </c>
-      <c r="H369">
+      <c r="G369">
         <v>1</v>
       </c>
     </row>
@@ -29266,7 +28773,7 @@
       <c r="D370" t="s">
         <v>49</v>
       </c>
-      <c r="AD370">
+      <c r="AA370">
         <v>1</v>
       </c>
     </row>
@@ -29283,19 +28790,13 @@
       <c r="D371" t="s">
         <v>52</v>
       </c>
-      <c r="E371">
-        <v>1</v>
-      </c>
-      <c r="K371">
-        <v>1</v>
-      </c>
-      <c r="N371">
-        <v>1</v>
-      </c>
-      <c r="O371">
-        <v>1</v>
-      </c>
-      <c r="AH371">
+      <c r="J371">
+        <v>1</v>
+      </c>
+      <c r="M371">
+        <v>1</v>
+      </c>
+      <c r="AE371">
         <v>1</v>
       </c>
     </row>
@@ -29340,10 +28841,13 @@
       <c r="D374" t="s">
         <v>46</v>
       </c>
-      <c r="AI374">
-        <v>1</v>
-      </c>
-      <c r="AJ374">
+      <c r="AF374">
+        <v>1</v>
+      </c>
+      <c r="AG374">
+        <v>1</v>
+      </c>
+      <c r="AK374">
         <v>1</v>
       </c>
       <c r="AN374">
@@ -29366,9 +28870,6 @@
       <c r="W375">
         <v>1</v>
       </c>
-      <c r="Z375">
-        <v>1</v>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="s">
@@ -29383,10 +28884,10 @@
       <c r="D376" t="s">
         <v>52</v>
       </c>
-      <c r="AI376">
-        <v>1</v>
-      </c>
-      <c r="AJ376">
+      <c r="AF376">
+        <v>1</v>
+      </c>
+      <c r="AG376">
         <v>1</v>
       </c>
     </row>
@@ -29417,10 +28918,7 @@
       <c r="D378" t="s">
         <v>43</v>
       </c>
-      <c r="N378">
-        <v>1</v>
-      </c>
-      <c r="O378">
+      <c r="M378">
         <v>1</v>
       </c>
     </row>
@@ -29437,10 +28935,10 @@
       <c r="D379" t="s">
         <v>46</v>
       </c>
-      <c r="E379">
-        <v>1</v>
-      </c>
-      <c r="M379">
+      <c r="L379">
+        <v>1</v>
+      </c>
+      <c r="AK379">
         <v>1</v>
       </c>
       <c r="AN379">
@@ -29477,13 +28975,7 @@
       <c r="E381">
         <v>1</v>
       </c>
-      <c r="F381">
-        <v>1</v>
-      </c>
-      <c r="N381">
-        <v>1</v>
-      </c>
-      <c r="O381">
+      <c r="M381">
         <v>1</v>
       </c>
     </row>
@@ -29514,16 +29006,13 @@
       <c r="D383" t="s">
         <v>43</v>
       </c>
-      <c r="E383">
-        <v>1</v>
-      </c>
-      <c r="H383">
-        <v>1</v>
-      </c>
-      <c r="AI383">
-        <v>1</v>
-      </c>
-      <c r="AJ383">
+      <c r="G383">
+        <v>1</v>
+      </c>
+      <c r="AF383">
+        <v>1</v>
+      </c>
+      <c r="AG383">
         <v>1</v>
       </c>
     </row>
@@ -29554,10 +29043,7 @@
       <c r="D385" t="s">
         <v>49</v>
       </c>
-      <c r="N385">
-        <v>1</v>
-      </c>
-      <c r="O385">
+      <c r="M385">
         <v>1</v>
       </c>
     </row>
@@ -29602,10 +29088,10 @@
       <c r="D388" t="s">
         <v>43</v>
       </c>
-      <c r="N388">
-        <v>1</v>
-      </c>
-      <c r="O388">
+      <c r="M388">
+        <v>1</v>
+      </c>
+      <c r="AK388">
         <v>1</v>
       </c>
       <c r="AN388">
@@ -29642,9 +29128,6 @@
       <c r="N390">
         <v>1</v>
       </c>
-      <c r="P390">
-        <v>1</v>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="s">
@@ -29662,13 +29145,7 @@
       <c r="E391">
         <v>1</v>
       </c>
-      <c r="F391">
-        <v>1</v>
-      </c>
       <c r="W391">
-        <v>1</v>
-      </c>
-      <c r="Z391">
         <v>1</v>
       </c>
     </row>
@@ -29699,10 +29176,7 @@
       <c r="D393" t="s">
         <v>43</v>
       </c>
-      <c r="N393">
-        <v>1</v>
-      </c>
-      <c r="T393">
+      <c r="R393">
         <v>1</v>
       </c>
     </row>
@@ -29747,10 +29221,7 @@
       <c r="D396" t="s">
         <v>52</v>
       </c>
-      <c r="E396">
-        <v>1</v>
-      </c>
-      <c r="L396">
+      <c r="K396">
         <v>1</v>
       </c>
     </row>
@@ -29784,13 +29255,7 @@
       <c r="E398">
         <v>1</v>
       </c>
-      <c r="F398">
-        <v>1</v>
-      </c>
-      <c r="N398">
-        <v>1</v>
-      </c>
-      <c r="O398">
+      <c r="M398">
         <v>1</v>
       </c>
     </row>
@@ -29807,19 +29272,13 @@
       <c r="D399" t="s">
         <v>46</v>
       </c>
-      <c r="E399">
-        <v>1</v>
-      </c>
-      <c r="H399">
-        <v>1</v>
-      </c>
-      <c r="W399">
-        <v>1</v>
-      </c>
-      <c r="AA399">
-        <v>1</v>
-      </c>
-      <c r="AH399">
+      <c r="G399">
+        <v>1</v>
+      </c>
+      <c r="X399">
+        <v>1</v>
+      </c>
+      <c r="AE399">
         <v>1</v>
       </c>
     </row>
@@ -29836,10 +29295,7 @@
       <c r="D400" t="s">
         <v>49</v>
       </c>
-      <c r="N400">
-        <v>1</v>
-      </c>
-      <c r="O400">
+      <c r="M400">
         <v>1</v>
       </c>
     </row>
@@ -29856,10 +29312,10 @@
       <c r="D401" t="s">
         <v>52</v>
       </c>
-      <c r="E401">
-        <v>1</v>
-      </c>
-      <c r="H401">
+      <c r="G401">
+        <v>1</v>
+      </c>
+      <c r="AK401">
         <v>1</v>
       </c>
       <c r="AN401">
@@ -29893,10 +29349,10 @@
       <c r="D403" t="s">
         <v>43</v>
       </c>
-      <c r="AD403">
-        <v>1</v>
-      </c>
-      <c r="AH403">
+      <c r="AA403">
+        <v>1</v>
+      </c>
+      <c r="AE403">
         <v>1</v>
       </c>
     </row>
@@ -29941,7 +29397,10 @@
       <c r="D406" t="s">
         <v>52</v>
       </c>
-      <c r="AE406">
+      <c r="AB406">
+        <v>1</v>
+      </c>
+      <c r="AK406">
         <v>1</v>
       </c>
       <c r="AN406">
@@ -29990,7 +29449,7 @@
         <v>46</v>
       </c>
       <c r="E409">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F409">
         <v>1</v>
@@ -30001,28 +29460,28 @@
       <c r="H409">
         <v>1</v>
       </c>
-      <c r="I409">
-        <v>1</v>
-      </c>
-      <c r="K409">
+      <c r="J409">
+        <v>1</v>
+      </c>
+      <c r="L409">
         <v>1</v>
       </c>
       <c r="M409">
         <v>1</v>
       </c>
       <c r="N409">
-        <v>4</v>
-      </c>
-      <c r="O409">
-        <v>1</v>
-      </c>
-      <c r="P409">
-        <v>1</v>
-      </c>
-      <c r="U409">
-        <v>1</v>
-      </c>
-      <c r="V409">
+        <v>1</v>
+      </c>
+      <c r="S409">
+        <v>1</v>
+      </c>
+      <c r="T409">
+        <v>1</v>
+      </c>
+      <c r="AI409">
+        <v>1</v>
+      </c>
+      <c r="AK409">
         <v>1</v>
       </c>
       <c r="AL409">
@@ -30045,16 +29504,10 @@
       <c r="D410" t="s">
         <v>49</v>
       </c>
-      <c r="E410">
-        <v>1</v>
-      </c>
-      <c r="H410">
-        <v>1</v>
-      </c>
-      <c r="N410">
-        <v>1</v>
-      </c>
-      <c r="O410">
+      <c r="G410">
+        <v>1</v>
+      </c>
+      <c r="M410">
         <v>1</v>
       </c>
     </row>
@@ -30102,19 +29555,13 @@
       <c r="E413">
         <v>1</v>
       </c>
-      <c r="F413">
-        <v>1</v>
-      </c>
-      <c r="N413">
-        <v>1</v>
-      </c>
-      <c r="O413">
-        <v>1</v>
-      </c>
-      <c r="AI413">
-        <v>1</v>
-      </c>
-      <c r="AJ413">
+      <c r="M413">
+        <v>1</v>
+      </c>
+      <c r="AF413">
+        <v>1</v>
+      </c>
+      <c r="AG413">
         <v>1</v>
       </c>
     </row>
@@ -30145,6 +29592,12 @@
       <c r="D415" t="s">
         <v>49</v>
       </c>
+      <c r="AJ415">
+        <v>1</v>
+      </c>
+      <c r="AK415">
+        <v>1</v>
+      </c>
       <c r="AM415">
         <v>1</v>
       </c>
@@ -30207,6 +29660,9 @@
       <c r="D419" t="s">
         <v>46</v>
       </c>
+      <c r="AK419">
+        <v>1</v>
+      </c>
       <c r="AN419">
         <v>1</v>
       </c>
@@ -30224,10 +29680,7 @@
       <c r="D420" t="s">
         <v>49</v>
       </c>
-      <c r="N420">
-        <v>1</v>
-      </c>
-      <c r="O420">
+      <c r="M420">
         <v>1</v>
       </c>
     </row>
@@ -30258,6 +29711,9 @@
       <c r="D422" t="s">
         <v>40</v>
       </c>
+      <c r="AK422">
+        <v>1</v>
+      </c>
       <c r="AN422">
         <v>1</v>
       </c>
@@ -30306,9 +29762,6 @@
       <c r="E425">
         <v>1</v>
       </c>
-      <c r="F425">
-        <v>1</v>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="s">
@@ -30323,10 +29776,7 @@
       <c r="D426" t="s">
         <v>52</v>
       </c>
-      <c r="N426">
-        <v>1</v>
-      </c>
-      <c r="O426">
+      <c r="M426">
         <v>1</v>
       </c>
     </row>
@@ -30357,16 +29807,13 @@
       <c r="D428" t="s">
         <v>43</v>
       </c>
-      <c r="E428">
-        <v>1</v>
-      </c>
-      <c r="H428">
-        <v>1</v>
-      </c>
-      <c r="AI428">
-        <v>1</v>
-      </c>
-      <c r="AJ428">
+      <c r="G428">
+        <v>1</v>
+      </c>
+      <c r="AF428">
+        <v>1</v>
+      </c>
+      <c r="AG428">
         <v>1</v>
       </c>
     </row>
@@ -30411,16 +29858,13 @@
       <c r="D431" t="s">
         <v>52</v>
       </c>
-      <c r="E431">
-        <v>1</v>
-      </c>
-      <c r="K431">
-        <v>1</v>
-      </c>
-      <c r="N431">
-        <v>1</v>
-      </c>
-      <c r="O431">
+      <c r="J431">
+        <v>1</v>
+      </c>
+      <c r="M431">
+        <v>1</v>
+      </c>
+      <c r="AK431">
         <v>1</v>
       </c>
       <c r="AN431">
@@ -30468,7 +29912,10 @@
       <c r="D434" t="s">
         <v>46</v>
       </c>
-      <c r="AH434">
+      <c r="AE434">
+        <v>1</v>
+      </c>
+      <c r="AK434">
         <v>1</v>
       </c>
       <c r="AN434">
@@ -30488,10 +29935,7 @@
       <c r="D435" t="s">
         <v>49</v>
       </c>
-      <c r="W435">
-        <v>1</v>
-      </c>
-      <c r="Y435">
+      <c r="V435">
         <v>1</v>
       </c>
     </row>
@@ -30508,19 +29952,13 @@
       <c r="D436" t="s">
         <v>52</v>
       </c>
-      <c r="N436">
-        <v>1</v>
-      </c>
-      <c r="O436">
-        <v>1</v>
-      </c>
-      <c r="W436">
-        <v>1</v>
-      </c>
-      <c r="AA436">
-        <v>1</v>
-      </c>
-      <c r="AE436">
+      <c r="M436">
+        <v>1</v>
+      </c>
+      <c r="X436">
+        <v>1</v>
+      </c>
+      <c r="AB436">
         <v>1</v>
       </c>
     </row>
@@ -30537,6 +29975,9 @@
       <c r="D437" t="s">
         <v>40</v>
       </c>
+      <c r="AK437">
+        <v>1</v>
+      </c>
       <c r="AN437">
         <v>1</v>
       </c>
@@ -30555,12 +29996,9 @@
         <v>43</v>
       </c>
       <c r="E438">
-        <v>2</v>
-      </c>
-      <c r="F438">
-        <v>1</v>
-      </c>
-      <c r="K438">
+        <v>1</v>
+      </c>
+      <c r="J438">
         <v>1</v>
       </c>
     </row>
@@ -30591,10 +30029,7 @@
       <c r="D440" t="s">
         <v>49</v>
       </c>
-      <c r="N440">
-        <v>1</v>
-      </c>
-      <c r="O440">
+      <c r="M440">
         <v>1</v>
       </c>
     </row>
@@ -30614,13 +30049,7 @@
       <c r="E441">
         <v>1</v>
       </c>
-      <c r="F441">
-        <v>1</v>
-      </c>
-      <c r="N441">
-        <v>1</v>
-      </c>
-      <c r="O441">
+      <c r="M441">
         <v>1</v>
       </c>
     </row>
@@ -30665,13 +30094,10 @@
       <c r="D444" t="s">
         <v>46</v>
       </c>
+      <c r="M444">
+        <v>1</v>
+      </c>
       <c r="N444">
-        <v>2</v>
-      </c>
-      <c r="O444">
-        <v>1</v>
-      </c>
-      <c r="P444">
         <v>1</v>
       </c>
     </row>
@@ -30716,10 +30142,7 @@
       <c r="D447" t="s">
         <v>40</v>
       </c>
-      <c r="E447">
-        <v>1</v>
-      </c>
-      <c r="H447">
+      <c r="G447">
         <v>1</v>
       </c>
     </row>
@@ -30737,27 +30160,21 @@
         <v>43</v>
       </c>
       <c r="E448">
-        <v>2</v>
-      </c>
-      <c r="F448">
-        <v>1</v>
-      </c>
-      <c r="K448">
-        <v>1</v>
-      </c>
-      <c r="W448">
-        <v>2</v>
-      </c>
-      <c r="X448">
-        <v>1</v>
-      </c>
-      <c r="AC448">
-        <v>1</v>
-      </c>
-      <c r="AI448">
-        <v>1</v>
-      </c>
-      <c r="AJ448">
+        <v>1</v>
+      </c>
+      <c r="J448">
+        <v>1</v>
+      </c>
+      <c r="U448">
+        <v>1</v>
+      </c>
+      <c r="Z448">
+        <v>1</v>
+      </c>
+      <c r="AF448">
+        <v>1</v>
+      </c>
+      <c r="AG448">
         <v>1</v>
       </c>
     </row>
@@ -30788,10 +30205,7 @@
       <c r="D450" t="s">
         <v>49</v>
       </c>
-      <c r="N450">
-        <v>1</v>
-      </c>
-      <c r="O450">
+      <c r="M450">
         <v>1</v>
       </c>
     </row>
@@ -30809,12 +30223,9 @@
         <v>52</v>
       </c>
       <c r="E451">
-        <v>2</v>
-      </c>
-      <c r="F451">
-        <v>1</v>
-      </c>
-      <c r="K451">
+        <v>1</v>
+      </c>
+      <c r="J451">
         <v>1</v>
       </c>
     </row>
@@ -30859,6 +30270,9 @@
       <c r="D454" t="s">
         <v>46</v>
       </c>
+      <c r="AK454">
+        <v>1</v>
+      </c>
       <c r="AN454">
         <v>1</v>
       </c>
@@ -30876,10 +30290,7 @@
       <c r="D455" t="s">
         <v>49</v>
       </c>
-      <c r="E455">
-        <v>1</v>
-      </c>
-      <c r="H455">
+      <c r="G455">
         <v>1</v>
       </c>
     </row>
@@ -30897,12 +30308,9 @@
         <v>52</v>
       </c>
       <c r="E456">
-        <v>2</v>
-      </c>
-      <c r="F456">
-        <v>1</v>
-      </c>
-      <c r="K456">
+        <v>1</v>
+      </c>
+      <c r="J456">
         <v>1</v>
       </c>
     </row>
@@ -30919,6 +30327,9 @@
       <c r="D457" t="s">
         <v>40</v>
       </c>
+      <c r="AK457">
+        <v>1</v>
+      </c>
       <c r="AN457">
         <v>1</v>
       </c>
@@ -30936,10 +30347,10 @@
       <c r="D458" t="s">
         <v>43</v>
       </c>
-      <c r="AI458">
-        <v>1</v>
-      </c>
-      <c r="AJ458">
+      <c r="AF458">
+        <v>1</v>
+      </c>
+      <c r="AG458">
         <v>1</v>
       </c>
     </row>
@@ -30956,10 +30367,7 @@
       <c r="D459" t="s">
         <v>46</v>
       </c>
-      <c r="W459">
-        <v>1</v>
-      </c>
-      <c r="Y459">
+      <c r="V459">
         <v>1</v>
       </c>
     </row>
@@ -31032,6 +30440,9 @@
       <c r="D464" t="s">
         <v>46</v>
       </c>
+      <c r="AH464">
+        <v>1</v>
+      </c>
       <c r="AK464">
         <v>1</v>
       </c>
@@ -31052,10 +30463,10 @@
       <c r="D465" t="s">
         <v>49</v>
       </c>
-      <c r="W465">
-        <v>1</v>
-      </c>
-      <c r="AA465">
+      <c r="X465">
+        <v>1</v>
+      </c>
+      <c r="AJ465">
         <v>1</v>
       </c>
       <c r="AM465">
@@ -31078,13 +30489,7 @@
       <c r="E466">
         <v>1</v>
       </c>
-      <c r="F466">
-        <v>1</v>
-      </c>
-      <c r="N466">
-        <v>1</v>
-      </c>
-      <c r="O466">
+      <c r="M466">
         <v>1</v>
       </c>
     </row>
@@ -31143,16 +30548,13 @@
       <c r="D470" t="s">
         <v>49</v>
       </c>
-      <c r="E470">
-        <v>1</v>
-      </c>
-      <c r="G470">
-        <v>1</v>
-      </c>
-      <c r="N470">
-        <v>1</v>
-      </c>
-      <c r="O470">
+      <c r="F470">
+        <v>1</v>
+      </c>
+      <c r="M470">
+        <v>1</v>
+      </c>
+      <c r="AK470">
         <v>1</v>
       </c>
       <c r="AN470">
@@ -31172,16 +30574,10 @@
       <c r="D471" t="s">
         <v>52</v>
       </c>
-      <c r="N471">
-        <v>1</v>
-      </c>
-      <c r="S471">
-        <v>1</v>
-      </c>
-      <c r="W471">
-        <v>1</v>
-      </c>
-      <c r="AA471">
+      <c r="Q471">
+        <v>1</v>
+      </c>
+      <c r="X471">
         <v>1</v>
       </c>
     </row>
@@ -31198,6 +30594,9 @@
       <c r="D472" t="s">
         <v>40</v>
       </c>
+      <c r="AK472">
+        <v>1</v>
+      </c>
       <c r="AN472">
         <v>1</v>
       </c>
@@ -31230,12 +30629,12 @@
         <v>46</v>
       </c>
       <c r="E474">
-        <v>2</v>
-      </c>
-      <c r="F474">
-        <v>1</v>
-      </c>
-      <c r="K474">
+        <v>1</v>
+      </c>
+      <c r="J474">
+        <v>1</v>
+      </c>
+      <c r="AK474">
         <v>1</v>
       </c>
       <c r="AN474">
@@ -31255,19 +30654,16 @@
       <c r="D475" t="s">
         <v>49</v>
       </c>
-      <c r="E475">
-        <v>1</v>
-      </c>
-      <c r="H475">
-        <v>1</v>
-      </c>
-      <c r="N475">
-        <v>1</v>
-      </c>
-      <c r="O475">
-        <v>1</v>
-      </c>
-      <c r="AI475">
+      <c r="G475">
+        <v>1</v>
+      </c>
+      <c r="M475">
+        <v>1</v>
+      </c>
+      <c r="AF475">
+        <v>1</v>
+      </c>
+      <c r="AG475">
         <v>1</v>
       </c>
       <c r="AJ475">
@@ -31290,10 +30686,7 @@
       <c r="D476" t="s">
         <v>52</v>
       </c>
-      <c r="N476">
-        <v>1</v>
-      </c>
-      <c r="O476">
+      <c r="M476">
         <v>1</v>
       </c>
     </row>
@@ -31324,10 +30717,7 @@
       <c r="D478" t="s">
         <v>43</v>
       </c>
-      <c r="N478">
-        <v>1</v>
-      </c>
-      <c r="O478">
+      <c r="M478">
         <v>1</v>
       </c>
     </row>
@@ -31372,6 +30762,9 @@
       <c r="D481" t="s">
         <v>52</v>
       </c>
+      <c r="AK481">
+        <v>1</v>
+      </c>
       <c r="AN481">
         <v>1</v>
       </c>
@@ -31417,10 +30810,10 @@
       <c r="D484" t="s">
         <v>46</v>
       </c>
-      <c r="N484">
-        <v>1</v>
-      </c>
-      <c r="O484">
+      <c r="M484">
+        <v>1</v>
+      </c>
+      <c r="AK484">
         <v>1</v>
       </c>
       <c r="AN484">
@@ -31455,12 +30848,9 @@
         <v>52</v>
       </c>
       <c r="E486">
-        <v>2</v>
-      </c>
-      <c r="F486">
-        <v>1</v>
-      </c>
-      <c r="K486">
+        <v>1</v>
+      </c>
+      <c r="J486">
         <v>1</v>
       </c>
     </row>
@@ -31491,10 +30881,7 @@
       <c r="D488" t="s">
         <v>43</v>
       </c>
-      <c r="N488">
-        <v>1</v>
-      </c>
-      <c r="O488">
+      <c r="M488">
         <v>1</v>
       </c>
     </row>
@@ -31526,18 +30913,12 @@
         <v>49</v>
       </c>
       <c r="E490">
-        <v>2</v>
-      </c>
-      <c r="F490">
-        <v>1</v>
-      </c>
-      <c r="K490">
-        <v>1</v>
-      </c>
-      <c r="W490">
-        <v>1</v>
-      </c>
-      <c r="Y490">
+        <v>1</v>
+      </c>
+      <c r="J490">
+        <v>1</v>
+      </c>
+      <c r="V490">
         <v>1</v>
       </c>
     </row>
@@ -31555,24 +30936,15 @@
         <v>52</v>
       </c>
       <c r="E491">
-        <v>2</v>
-      </c>
-      <c r="F491">
-        <v>1</v>
-      </c>
-      <c r="K491">
-        <v>1</v>
-      </c>
-      <c r="N491">
-        <v>1</v>
-      </c>
-      <c r="O491">
-        <v>1</v>
-      </c>
-      <c r="W491">
-        <v>1</v>
-      </c>
-      <c r="Y491">
+        <v>1</v>
+      </c>
+      <c r="J491">
+        <v>1</v>
+      </c>
+      <c r="M491">
+        <v>1</v>
+      </c>
+      <c r="V491">
         <v>1</v>
       </c>
     </row>
@@ -31617,16 +30989,10 @@
       <c r="D494" t="s">
         <v>46</v>
       </c>
-      <c r="E494">
-        <v>1</v>
-      </c>
-      <c r="K494">
-        <v>1</v>
-      </c>
-      <c r="W494">
-        <v>1</v>
-      </c>
-      <c r="AA494">
+      <c r="J494">
+        <v>1</v>
+      </c>
+      <c r="X494">
         <v>1</v>
       </c>
     </row>
@@ -31643,7 +31009,10 @@
       <c r="D495" t="s">
         <v>49</v>
       </c>
-      <c r="AH495">
+      <c r="AE495">
+        <v>1</v>
+      </c>
+      <c r="AK495">
         <v>1</v>
       </c>
       <c r="AN495">
@@ -31663,13 +31032,10 @@
       <c r="D496" t="s">
         <v>52</v>
       </c>
-      <c r="N496">
-        <v>1</v>
-      </c>
-      <c r="O496">
-        <v>1</v>
-      </c>
-      <c r="AH496">
+      <c r="M496">
+        <v>1</v>
+      </c>
+      <c r="AE496">
         <v>1</v>
       </c>
     </row>
@@ -31700,10 +31066,7 @@
       <c r="D498" t="s">
         <v>43</v>
       </c>
-      <c r="N498">
-        <v>1</v>
-      </c>
-      <c r="O498">
+      <c r="M498">
         <v>1</v>
       </c>
     </row>
@@ -31723,16 +31086,13 @@
       <c r="E499">
         <v>1</v>
       </c>
-      <c r="F499">
-        <v>1</v>
-      </c>
-      <c r="N499">
-        <v>2</v>
+      <c r="M499">
+        <v>1</v>
       </c>
       <c r="O499">
         <v>1</v>
       </c>
-      <c r="Q499">
+      <c r="AK499">
         <v>1</v>
       </c>
       <c r="AN499">
@@ -31753,18 +31113,12 @@
         <v>49</v>
       </c>
       <c r="E500">
-        <v>2</v>
-      </c>
-      <c r="F500">
-        <v>1</v>
-      </c>
-      <c r="K500">
-        <v>1</v>
-      </c>
-      <c r="W500">
-        <v>1</v>
-      </c>
-      <c r="AA500">
+        <v>1</v>
+      </c>
+      <c r="J500">
+        <v>1</v>
+      </c>
+      <c r="X500">
         <v>1</v>
       </c>
     </row>
@@ -31784,10 +31138,7 @@
       <c r="E501">
         <v>1</v>
       </c>
-      <c r="F501">
-        <v>1</v>
-      </c>
-      <c r="AI501">
+      <c r="AF501">
         <v>1</v>
       </c>
     </row>
@@ -31821,19 +31172,13 @@
       <c r="E503">
         <v>1</v>
       </c>
-      <c r="F503">
-        <v>1</v>
-      </c>
-      <c r="N503">
-        <v>1</v>
-      </c>
-      <c r="O503">
-        <v>1</v>
-      </c>
-      <c r="AI503">
-        <v>1</v>
-      </c>
-      <c r="AJ503">
+      <c r="M503">
+        <v>1</v>
+      </c>
+      <c r="AF503">
+        <v>1</v>
+      </c>
+      <c r="AG503">
         <v>1</v>
       </c>
     </row>
@@ -31850,6 +31195,9 @@
       <c r="D504" t="s">
         <v>46</v>
       </c>
+      <c r="AK504">
+        <v>1</v>
+      </c>
       <c r="AN504">
         <v>1</v>
       </c>
@@ -31867,16 +31215,10 @@
       <c r="D505" t="s">
         <v>49</v>
       </c>
-      <c r="E505">
-        <v>1</v>
-      </c>
-      <c r="K505">
-        <v>1</v>
-      </c>
-      <c r="W505">
-        <v>1</v>
-      </c>
-      <c r="Y505">
+      <c r="J505">
+        <v>1</v>
+      </c>
+      <c r="V505">
         <v>1</v>
       </c>
     </row>
@@ -31893,7 +31235,7 @@
       <c r="D506" t="s">
         <v>52</v>
       </c>
-      <c r="AF506">
+      <c r="AC506">
         <v>1</v>
       </c>
     </row>
@@ -31924,22 +31266,16 @@
       <c r="D508" t="s">
         <v>43</v>
       </c>
-      <c r="E508">
-        <v>1</v>
-      </c>
-      <c r="K508">
-        <v>1</v>
-      </c>
-      <c r="N508">
-        <v>1</v>
-      </c>
-      <c r="O508">
-        <v>1</v>
-      </c>
-      <c r="AI508">
-        <v>1</v>
-      </c>
-      <c r="AJ508">
+      <c r="J508">
+        <v>1</v>
+      </c>
+      <c r="M508">
+        <v>1</v>
+      </c>
+      <c r="AF508">
+        <v>1</v>
+      </c>
+      <c r="AG508">
         <v>1</v>
       </c>
     </row>
@@ -31959,7 +31295,7 @@
       <c r="W509">
         <v>1</v>
       </c>
-      <c r="Z509">
+      <c r="AK509">
         <v>1</v>
       </c>
       <c r="AN509">
@@ -31979,10 +31315,7 @@
       <c r="D510" t="s">
         <v>49</v>
       </c>
-      <c r="W510">
-        <v>1</v>
-      </c>
-      <c r="AA510">
+      <c r="X510">
         <v>1</v>
       </c>
     </row>
@@ -32000,12 +31333,9 @@
         <v>52</v>
       </c>
       <c r="E511">
-        <v>2</v>
-      </c>
-      <c r="F511">
-        <v>1</v>
-      </c>
-      <c r="K511">
+        <v>1</v>
+      </c>
+      <c r="J511">
         <v>1</v>
       </c>
     </row>
@@ -32036,16 +31366,13 @@
       <c r="D513" t="s">
         <v>43</v>
       </c>
-      <c r="N513">
-        <v>1</v>
-      </c>
-      <c r="S513">
-        <v>1</v>
-      </c>
-      <c r="AI513">
-        <v>1</v>
-      </c>
-      <c r="AJ513">
+      <c r="Q513">
+        <v>1</v>
+      </c>
+      <c r="AF513">
+        <v>1</v>
+      </c>
+      <c r="AG513">
         <v>1</v>
       </c>
     </row>
@@ -32062,6 +31389,9 @@
       <c r="D514" t="s">
         <v>46</v>
       </c>
+      <c r="AK514">
+        <v>1</v>
+      </c>
       <c r="AN514">
         <v>1</v>
       </c>
@@ -32082,19 +31412,10 @@
       <c r="E515">
         <v>1</v>
       </c>
-      <c r="F515">
-        <v>1</v>
-      </c>
-      <c r="N515">
-        <v>1</v>
-      </c>
-      <c r="O515">
-        <v>1</v>
-      </c>
-      <c r="W515">
-        <v>1</v>
-      </c>
-      <c r="AA515">
+      <c r="M515">
+        <v>1</v>
+      </c>
+      <c r="X515">
         <v>1</v>
       </c>
     </row>
@@ -32111,6 +31432,9 @@
       <c r="D516" t="s">
         <v>52</v>
       </c>
+      <c r="AK516">
+        <v>1</v>
+      </c>
       <c r="AN516">
         <v>1</v>
       </c>
@@ -32142,10 +31466,10 @@
       <c r="D518" t="s">
         <v>43</v>
       </c>
-      <c r="AI518">
-        <v>1</v>
-      </c>
-      <c r="AJ518">
+      <c r="AF518">
+        <v>1</v>
+      </c>
+      <c r="AG518">
         <v>1</v>
       </c>
     </row>
@@ -32165,13 +31489,7 @@
       <c r="E519">
         <v>1</v>
       </c>
-      <c r="F519">
-        <v>1</v>
-      </c>
       <c r="W519">
-        <v>1</v>
-      </c>
-      <c r="Z519">
         <v>1</v>
       </c>
     </row>
@@ -32188,10 +31506,7 @@
       <c r="D520" t="s">
         <v>49</v>
       </c>
-      <c r="W520">
-        <v>1</v>
-      </c>
-      <c r="AA520">
+      <c r="X520">
         <v>1</v>
       </c>
     </row>
@@ -32208,16 +31523,13 @@
       <c r="D521" t="s">
         <v>52</v>
       </c>
-      <c r="E521">
-        <v>1</v>
-      </c>
-      <c r="G521">
-        <v>1</v>
-      </c>
-      <c r="N521">
-        <v>1</v>
-      </c>
-      <c r="O521">
+      <c r="F521">
+        <v>1</v>
+      </c>
+      <c r="M521">
+        <v>1</v>
+      </c>
+      <c r="AK521">
         <v>1</v>
       </c>
       <c r="AN521">
@@ -32252,24 +31564,18 @@
         <v>43</v>
       </c>
       <c r="E523">
-        <v>2</v>
-      </c>
-      <c r="F523">
-        <v>1</v>
-      </c>
-      <c r="K523">
-        <v>1</v>
-      </c>
-      <c r="N523">
-        <v>1</v>
-      </c>
-      <c r="O523">
-        <v>1</v>
-      </c>
-      <c r="AI523">
-        <v>1</v>
-      </c>
-      <c r="AJ523">
+        <v>1</v>
+      </c>
+      <c r="J523">
+        <v>1</v>
+      </c>
+      <c r="M523">
+        <v>1</v>
+      </c>
+      <c r="AF523">
+        <v>1</v>
+      </c>
+      <c r="AG523">
         <v>1</v>
       </c>
     </row>
@@ -32300,10 +31606,7 @@
       <c r="D525" t="s">
         <v>49</v>
       </c>
-      <c r="E525">
-        <v>1</v>
-      </c>
-      <c r="G525">
+      <c r="F525">
         <v>1</v>
       </c>
     </row>
@@ -32323,19 +31626,10 @@
       <c r="E526">
         <v>1</v>
       </c>
-      <c r="F526">
-        <v>1</v>
-      </c>
-      <c r="N526">
-        <v>1</v>
-      </c>
-      <c r="O526">
+      <c r="M526">
         <v>1</v>
       </c>
       <c r="W526">
-        <v>1</v>
-      </c>
-      <c r="Z526">
         <v>1</v>
       </c>
     </row>
@@ -32366,10 +31660,10 @@
       <c r="D528" t="s">
         <v>43</v>
       </c>
-      <c r="AI528">
-        <v>1</v>
-      </c>
-      <c r="AJ528">
+      <c r="AF528">
+        <v>1</v>
+      </c>
+      <c r="AG528">
         <v>1</v>
       </c>
     </row>
@@ -32389,7 +31683,7 @@
       <c r="E529">
         <v>1</v>
       </c>
-      <c r="F529">
+      <c r="AK529">
         <v>1</v>
       </c>
       <c r="AN529">
@@ -32409,13 +31703,10 @@
       <c r="D530" t="s">
         <v>49</v>
       </c>
-      <c r="W530">
-        <v>2</v>
-      </c>
-      <c r="X530">
-        <v>1</v>
-      </c>
-      <c r="Y530">
+      <c r="U530">
+        <v>1</v>
+      </c>
+      <c r="V530">
         <v>1</v>
       </c>
     </row>
@@ -32432,13 +31723,10 @@
       <c r="D531" t="s">
         <v>52</v>
       </c>
-      <c r="W531">
-        <v>1</v>
-      </c>
-      <c r="AA531">
-        <v>1</v>
-      </c>
-      <c r="AH531">
+      <c r="X531">
+        <v>1</v>
+      </c>
+      <c r="AE531">
         <v>1</v>
       </c>
     </row>
@@ -32469,10 +31757,7 @@
       <c r="D533" t="s">
         <v>43</v>
       </c>
-      <c r="E533">
-        <v>1</v>
-      </c>
-      <c r="K533">
+      <c r="J533">
         <v>1</v>
       </c>
     </row>
@@ -32490,18 +31775,15 @@
         <v>46</v>
       </c>
       <c r="E534">
-        <v>2</v>
-      </c>
-      <c r="F534">
-        <v>1</v>
-      </c>
-      <c r="K534">
+        <v>1</v>
+      </c>
+      <c r="J534">
         <v>1</v>
       </c>
       <c r="W534">
         <v>1</v>
       </c>
-      <c r="Z534">
+      <c r="AK534">
         <v>1</v>
       </c>
       <c r="AN534">
@@ -32521,6 +31803,9 @@
       <c r="D535" t="s">
         <v>49</v>
       </c>
+      <c r="AK535">
+        <v>1</v>
+      </c>
       <c r="AN535">
         <v>1</v>
       </c>
@@ -32541,13 +31826,7 @@
       <c r="E536">
         <v>1</v>
       </c>
-      <c r="F536">
-        <v>1</v>
-      </c>
-      <c r="N536">
-        <v>1</v>
-      </c>
-      <c r="R536">
+      <c r="P536">
         <v>1</v>
       </c>
     </row>
@@ -32579,21 +31858,18 @@
         <v>43</v>
       </c>
       <c r="E538">
-        <v>3</v>
-      </c>
-      <c r="F538">
-        <v>1</v>
-      </c>
-      <c r="H538">
-        <v>1</v>
-      </c>
-      <c r="K538">
-        <v>1</v>
-      </c>
-      <c r="AI538">
-        <v>1</v>
-      </c>
-      <c r="AJ538">
+        <v>1</v>
+      </c>
+      <c r="G538">
+        <v>1</v>
+      </c>
+      <c r="J538">
+        <v>1</v>
+      </c>
+      <c r="AF538">
+        <v>1</v>
+      </c>
+      <c r="AG538">
         <v>1</v>
       </c>
     </row>
@@ -32610,7 +31886,10 @@
       <c r="D539" t="s">
         <v>46</v>
       </c>
-      <c r="AE539">
+      <c r="AB539">
+        <v>1</v>
+      </c>
+      <c r="AK539">
         <v>1</v>
       </c>
       <c r="AN539">
@@ -32630,13 +31909,10 @@
       <c r="D540" t="s">
         <v>49</v>
       </c>
-      <c r="N540">
-        <v>1</v>
-      </c>
-      <c r="O540">
-        <v>1</v>
-      </c>
-      <c r="AI540">
+      <c r="M540">
+        <v>1</v>
+      </c>
+      <c r="AF540">
         <v>1</v>
       </c>
     </row>
@@ -32653,10 +31929,7 @@
       <c r="D541" t="s">
         <v>52</v>
       </c>
-      <c r="E541">
-        <v>1</v>
-      </c>
-      <c r="G541">
+      <c r="F541">
         <v>1</v>
       </c>
     </row>
@@ -32701,10 +31974,7 @@
       <c r="D544" t="s">
         <v>46</v>
       </c>
-      <c r="E544">
-        <v>1</v>
-      </c>
-      <c r="K544">
+      <c r="J544">
         <v>1</v>
       </c>
     </row>
@@ -32724,9 +31994,6 @@
       <c r="W545">
         <v>1</v>
       </c>
-      <c r="Z545">
-        <v>1</v>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="s">
@@ -32755,10 +32022,10 @@
       <c r="D547" t="s">
         <v>40</v>
       </c>
-      <c r="W547">
-        <v>1</v>
-      </c>
-      <c r="AA547">
+      <c r="X547">
+        <v>1</v>
+      </c>
+      <c r="AK547">
         <v>1</v>
       </c>
       <c r="AN547">
@@ -32806,22 +32073,16 @@
       <c r="D550" t="s">
         <v>49</v>
       </c>
-      <c r="E550">
-        <v>1</v>
-      </c>
-      <c r="H550">
-        <v>1</v>
-      </c>
-      <c r="N550">
-        <v>1</v>
-      </c>
-      <c r="O550">
-        <v>1</v>
-      </c>
-      <c r="AI550">
-        <v>1</v>
-      </c>
-      <c r="AJ550">
+      <c r="G550">
+        <v>1</v>
+      </c>
+      <c r="M550">
+        <v>1</v>
+      </c>
+      <c r="AF550">
+        <v>1</v>
+      </c>
+      <c r="AG550">
         <v>1</v>
       </c>
     </row>
@@ -32838,6 +32099,9 @@
       <c r="D551" t="s">
         <v>52</v>
       </c>
+      <c r="AK551">
+        <v>1</v>
+      </c>
       <c r="AN551">
         <v>1</v>
       </c>
@@ -32872,13 +32136,10 @@
       <c r="E553">
         <v>1</v>
       </c>
-      <c r="F553">
-        <v>1</v>
-      </c>
-      <c r="W553">
-        <v>1</v>
-      </c>
-      <c r="Y553">
+      <c r="V553">
+        <v>1</v>
+      </c>
+      <c r="AJ553">
         <v>1</v>
       </c>
       <c r="AM553">
@@ -32898,10 +32159,7 @@
       <c r="D554" t="s">
         <v>46</v>
       </c>
-      <c r="E554">
-        <v>1</v>
-      </c>
-      <c r="K554">
+      <c r="J554">
         <v>1</v>
       </c>
     </row>
@@ -32918,10 +32176,7 @@
       <c r="D555" t="s">
         <v>49</v>
       </c>
-      <c r="W555">
-        <v>1</v>
-      </c>
-      <c r="Y555">
+      <c r="V555">
         <v>1</v>
       </c>
     </row>
@@ -32980,6 +32235,9 @@
       <c r="D559" t="s">
         <v>46</v>
       </c>
+      <c r="AK559">
+        <v>1</v>
+      </c>
       <c r="AN559">
         <v>1</v>
       </c>
@@ -32997,13 +32255,13 @@
       <c r="D560" t="s">
         <v>49</v>
       </c>
-      <c r="N560">
-        <v>1</v>
-      </c>
-      <c r="O560">
-        <v>1</v>
-      </c>
-      <c r="AI560">
+      <c r="M560">
+        <v>1</v>
+      </c>
+      <c r="AF560">
+        <v>1</v>
+      </c>
+      <c r="AG560">
         <v>1</v>
       </c>
       <c r="AJ560">
@@ -33026,10 +32284,7 @@
       <c r="D561" t="s">
         <v>52</v>
       </c>
-      <c r="N561">
-        <v>1</v>
-      </c>
-      <c r="O561">
+      <c r="M561">
         <v>1</v>
       </c>
     </row>
@@ -33060,10 +32315,13 @@
       <c r="D563" t="s">
         <v>43</v>
       </c>
-      <c r="AI563">
-        <v>1</v>
-      </c>
-      <c r="AJ563">
+      <c r="AF563">
+        <v>1</v>
+      </c>
+      <c r="AG563">
+        <v>1</v>
+      </c>
+      <c r="AK563">
         <v>1</v>
       </c>
       <c r="AN563">
@@ -33083,16 +32341,10 @@
       <c r="D564" t="s">
         <v>46</v>
       </c>
-      <c r="E564">
-        <v>1</v>
-      </c>
-      <c r="H564">
-        <v>1</v>
-      </c>
-      <c r="N564">
-        <v>1</v>
-      </c>
-      <c r="O564">
+      <c r="G564">
+        <v>1</v>
+      </c>
+      <c r="M564">
         <v>1</v>
       </c>
     </row>
@@ -33123,7 +32375,7 @@
       <c r="D566" t="s">
         <v>52</v>
       </c>
-      <c r="AH566">
+      <c r="AE566">
         <v>1</v>
       </c>
     </row>
@@ -33143,13 +32395,10 @@
       <c r="E567">
         <v>1</v>
       </c>
-      <c r="F567">
-        <v>1</v>
-      </c>
-      <c r="W567">
-        <v>1</v>
-      </c>
-      <c r="AB567">
+      <c r="Y567">
+        <v>1</v>
+      </c>
+      <c r="AK567">
         <v>1</v>
       </c>
       <c r="AN567">
@@ -33169,10 +32418,10 @@
       <c r="D568" t="s">
         <v>43</v>
       </c>
-      <c r="AI568">
-        <v>1</v>
-      </c>
-      <c r="AJ568">
+      <c r="AF568">
+        <v>1</v>
+      </c>
+      <c r="AG568">
         <v>1</v>
       </c>
     </row>
@@ -33189,6 +32438,9 @@
       <c r="D569" t="s">
         <v>46</v>
       </c>
+      <c r="AI569">
+        <v>1</v>
+      </c>
       <c r="AL569">
         <v>1</v>
       </c>
@@ -33206,13 +32458,10 @@
       <c r="D570" t="s">
         <v>49</v>
       </c>
-      <c r="W570">
-        <v>1</v>
-      </c>
-      <c r="AA570">
-        <v>1</v>
-      </c>
-      <c r="AE570">
+      <c r="X570">
+        <v>1</v>
+      </c>
+      <c r="AB570">
         <v>1</v>
       </c>
     </row>
@@ -33260,16 +32509,10 @@
       <c r="E573">
         <v>1</v>
       </c>
-      <c r="F573">
-        <v>1</v>
-      </c>
       <c r="W573">
         <v>1</v>
       </c>
-      <c r="Z573">
-        <v>1</v>
-      </c>
-      <c r="AI573">
+      <c r="AF573">
         <v>1</v>
       </c>
     </row>
@@ -33286,10 +32529,7 @@
       <c r="D574" t="s">
         <v>46</v>
       </c>
-      <c r="N574">
-        <v>1</v>
-      </c>
-      <c r="O574">
+      <c r="M574">
         <v>1</v>
       </c>
     </row>
@@ -33306,10 +32546,7 @@
       <c r="D575" t="s">
         <v>49</v>
       </c>
-      <c r="E575">
-        <v>1</v>
-      </c>
-      <c r="K575">
+      <c r="J575">
         <v>1</v>
       </c>
     </row>
@@ -33326,16 +32563,10 @@
       <c r="D576" t="s">
         <v>52</v>
       </c>
-      <c r="E576">
-        <v>1</v>
-      </c>
-      <c r="K576">
-        <v>1</v>
-      </c>
-      <c r="N576">
-        <v>1</v>
-      </c>
-      <c r="O576">
+      <c r="J576">
+        <v>1</v>
+      </c>
+      <c r="M576">
         <v>1</v>
       </c>
     </row>
@@ -33352,6 +32583,9 @@
       <c r="D577" t="s">
         <v>40</v>
       </c>
+      <c r="AK577">
+        <v>1</v>
+      </c>
       <c r="AN577">
         <v>1</v>
       </c>
@@ -33369,10 +32603,7 @@
       <c r="D578" t="s">
         <v>43</v>
       </c>
-      <c r="N578">
-        <v>1</v>
-      </c>
-      <c r="O578">
+      <c r="M578">
         <v>1</v>
       </c>
     </row>
@@ -33389,16 +32620,13 @@
       <c r="D579" t="s">
         <v>46</v>
       </c>
-      <c r="E579">
-        <v>1</v>
-      </c>
-      <c r="H579">
-        <v>1</v>
-      </c>
-      <c r="AI579">
-        <v>1</v>
-      </c>
-      <c r="AJ579">
+      <c r="G579">
+        <v>1</v>
+      </c>
+      <c r="AF579">
+        <v>1</v>
+      </c>
+      <c r="AG579">
         <v>1</v>
       </c>
     </row>
@@ -33415,6 +32643,9 @@
       <c r="D580" t="s">
         <v>49</v>
       </c>
+      <c r="AK580">
+        <v>1</v>
+      </c>
       <c r="AN580">
         <v>1</v>
       </c>
@@ -33474,6 +32705,9 @@
       <c r="D584" t="s">
         <v>46</v>
       </c>
+      <c r="AK584">
+        <v>1</v>
+      </c>
       <c r="AN584">
         <v>1</v>
       </c>
@@ -33491,19 +32725,13 @@
       <c r="D585" t="s">
         <v>49</v>
       </c>
-      <c r="E585">
-        <v>2</v>
-      </c>
-      <c r="H585">
-        <v>1</v>
-      </c>
-      <c r="K585">
-        <v>1</v>
-      </c>
-      <c r="N585">
-        <v>1</v>
-      </c>
-      <c r="O585">
+      <c r="G585">
+        <v>1</v>
+      </c>
+      <c r="J585">
+        <v>1</v>
+      </c>
+      <c r="M585">
         <v>1</v>
       </c>
     </row>
@@ -33520,16 +32748,10 @@
       <c r="D586" t="s">
         <v>52</v>
       </c>
-      <c r="E586">
-        <v>1</v>
-      </c>
-      <c r="G586">
-        <v>1</v>
-      </c>
-      <c r="N586">
-        <v>1</v>
-      </c>
-      <c r="O586">
+      <c r="F586">
+        <v>1</v>
+      </c>
+      <c r="M586">
         <v>1</v>
       </c>
     </row>
@@ -33560,6 +32782,9 @@
       <c r="D588" t="s">
         <v>43</v>
       </c>
+      <c r="AK588">
+        <v>1</v>
+      </c>
       <c r="AN588">
         <v>1</v>
       </c>
@@ -33592,18 +32817,12 @@
         <v>49</v>
       </c>
       <c r="E590">
-        <v>2</v>
-      </c>
-      <c r="F590">
-        <v>1</v>
-      </c>
-      <c r="K590">
-        <v>1</v>
-      </c>
-      <c r="N590">
-        <v>1</v>
-      </c>
-      <c r="O590">
+        <v>1</v>
+      </c>
+      <c r="J590">
+        <v>1</v>
+      </c>
+      <c r="M590">
         <v>1</v>
       </c>
     </row>
@@ -33623,19 +32842,10 @@
       <c r="E591">
         <v>1</v>
       </c>
-      <c r="F591">
-        <v>1</v>
-      </c>
-      <c r="N591">
-        <v>1</v>
-      </c>
-      <c r="O591">
-        <v>1</v>
-      </c>
-      <c r="W591">
-        <v>1</v>
-      </c>
-      <c r="AB591">
+      <c r="M591">
+        <v>1</v>
+      </c>
+      <c r="Y591">
         <v>1</v>
       </c>
     </row>
@@ -33680,10 +32890,7 @@
       <c r="D594" t="s">
         <v>46</v>
       </c>
-      <c r="E594">
-        <v>1</v>
-      </c>
-      <c r="G594">
+      <c r="F594">
         <v>1</v>
       </c>
     </row>
@@ -33700,10 +32907,7 @@
       <c r="D595" t="s">
         <v>49</v>
       </c>
-      <c r="N595">
-        <v>1</v>
-      </c>
-      <c r="O595">
+      <c r="M595">
         <v>1</v>
       </c>
     </row>
@@ -33720,19 +32924,13 @@
       <c r="D596" t="s">
         <v>52</v>
       </c>
-      <c r="E596">
-        <v>1</v>
-      </c>
-      <c r="G596">
-        <v>1</v>
-      </c>
-      <c r="N596">
-        <v>1</v>
-      </c>
-      <c r="O596">
-        <v>1</v>
-      </c>
-      <c r="AH596">
+      <c r="F596">
+        <v>1</v>
+      </c>
+      <c r="M596">
+        <v>1</v>
+      </c>
+      <c r="AE596">
         <v>1</v>
       </c>
     </row>
@@ -33763,10 +32961,7 @@
       <c r="D598" t="s">
         <v>43</v>
       </c>
-      <c r="N598">
-        <v>1</v>
-      </c>
-      <c r="O598">
+      <c r="M598">
         <v>1</v>
       </c>
     </row>
@@ -33783,7 +32978,7 @@
       <c r="D599" t="s">
         <v>46</v>
       </c>
-      <c r="AK599">
+      <c r="AH599">
         <v>1</v>
       </c>
     </row>
@@ -33800,16 +32995,10 @@
       <c r="D600" t="s">
         <v>49</v>
       </c>
-      <c r="E600">
-        <v>1</v>
-      </c>
-      <c r="G600">
+      <c r="F600">
         <v>1</v>
       </c>
       <c r="W600">
-        <v>1</v>
-      </c>
-      <c r="Z600">
         <v>1</v>
       </c>
     </row>
@@ -33868,6 +33057,9 @@
       <c r="D604" t="s">
         <v>46</v>
       </c>
+      <c r="AK604">
+        <v>1</v>
+      </c>
       <c r="AN604">
         <v>1</v>
       </c>
@@ -33885,10 +33077,7 @@
       <c r="D605" t="s">
         <v>49</v>
       </c>
-      <c r="N605">
-        <v>1</v>
-      </c>
-      <c r="O605">
+      <c r="M605">
         <v>1</v>
       </c>
     </row>
@@ -33905,22 +33094,13 @@
       <c r="D606" t="s">
         <v>52</v>
       </c>
-      <c r="E606">
-        <v>1</v>
-      </c>
-      <c r="G606">
-        <v>1</v>
-      </c>
-      <c r="N606">
-        <v>1</v>
-      </c>
-      <c r="O606">
+      <c r="F606">
+        <v>1</v>
+      </c>
+      <c r="M606">
         <v>1</v>
       </c>
       <c r="W606">
-        <v>1</v>
-      </c>
-      <c r="Z606">
         <v>1</v>
       </c>
     </row>
@@ -33937,6 +33117,9 @@
       <c r="D607" t="s">
         <v>40</v>
       </c>
+      <c r="AK607">
+        <v>1</v>
+      </c>
       <c r="AN607">
         <v>1</v>
       </c>
@@ -33968,13 +33151,10 @@
       <c r="D609" t="s">
         <v>46</v>
       </c>
-      <c r="N609">
-        <v>2</v>
+      <c r="M609">
+        <v>1</v>
       </c>
       <c r="O609">
-        <v>1</v>
-      </c>
-      <c r="Q609">
         <v>1</v>
       </c>
     </row>
@@ -33992,12 +33172,9 @@
         <v>49</v>
       </c>
       <c r="E610">
-        <v>2</v>
-      </c>
-      <c r="F610">
-        <v>1</v>
-      </c>
-      <c r="H610">
+        <v>1</v>
+      </c>
+      <c r="G610">
         <v>1</v>
       </c>
     </row>
@@ -34014,6 +33191,9 @@
       <c r="D611" t="s">
         <v>52</v>
       </c>
+      <c r="AK611">
+        <v>1</v>
+      </c>
       <c r="AN611">
         <v>1</v>
       </c>
@@ -34046,18 +33226,12 @@
         <v>43</v>
       </c>
       <c r="E613">
-        <v>2</v>
-      </c>
-      <c r="F613">
-        <v>1</v>
-      </c>
-      <c r="K613">
-        <v>1</v>
-      </c>
-      <c r="N613">
-        <v>1</v>
-      </c>
-      <c r="O613">
+        <v>1</v>
+      </c>
+      <c r="J613">
+        <v>1</v>
+      </c>
+      <c r="M613">
         <v>1</v>
       </c>
     </row>
@@ -34088,16 +33262,13 @@
       <c r="D615" t="s">
         <v>49</v>
       </c>
-      <c r="N615">
-        <v>1</v>
-      </c>
-      <c r="O615">
-        <v>1</v>
-      </c>
-      <c r="AI615">
-        <v>1</v>
-      </c>
-      <c r="AJ615">
+      <c r="M615">
+        <v>1</v>
+      </c>
+      <c r="AF615">
+        <v>1</v>
+      </c>
+      <c r="AG615">
         <v>1</v>
       </c>
     </row>
@@ -34115,18 +33286,15 @@
         <v>52</v>
       </c>
       <c r="E616">
-        <v>2</v>
-      </c>
-      <c r="F616">
-        <v>1</v>
-      </c>
-      <c r="K616">
-        <v>1</v>
-      </c>
-      <c r="N616">
-        <v>1</v>
-      </c>
-      <c r="O616">
+        <v>1</v>
+      </c>
+      <c r="J616">
+        <v>1</v>
+      </c>
+      <c r="M616">
+        <v>1</v>
+      </c>
+      <c r="AK616">
         <v>1</v>
       </c>
       <c r="AN616">
@@ -34146,6 +33314,9 @@
       <c r="D617" t="s">
         <v>40</v>
       </c>
+      <c r="AK617">
+        <v>1</v>
+      </c>
       <c r="AN617">
         <v>1</v>
       </c>
@@ -34205,6 +33376,9 @@
       <c r="D621" t="s">
         <v>52</v>
       </c>
+      <c r="AK621">
+        <v>1</v>
+      </c>
       <c r="AN621">
         <v>1</v>
       </c>
@@ -34236,16 +33410,13 @@
       <c r="D623" t="s">
         <v>43</v>
       </c>
-      <c r="N623">
-        <v>1</v>
-      </c>
-      <c r="O623">
-        <v>1</v>
-      </c>
-      <c r="AI623">
-        <v>1</v>
-      </c>
-      <c r="AJ623">
+      <c r="M623">
+        <v>1</v>
+      </c>
+      <c r="AF623">
+        <v>1</v>
+      </c>
+      <c r="AG623">
         <v>1</v>
       </c>
     </row>
@@ -34262,10 +33433,7 @@
       <c r="D624" t="s">
         <v>46</v>
       </c>
-      <c r="N624">
-        <v>1</v>
-      </c>
-      <c r="O624">
+      <c r="M624">
         <v>1</v>
       </c>
     </row>
@@ -34282,13 +33450,10 @@
       <c r="D625" t="s">
         <v>49</v>
       </c>
-      <c r="E625">
-        <v>2</v>
+      <c r="J625">
+        <v>1</v>
       </c>
       <c r="K625">
-        <v>1</v>
-      </c>
-      <c r="L625">
         <v>1</v>
       </c>
     </row>
@@ -34305,10 +33470,10 @@
       <c r="D626" t="s">
         <v>52</v>
       </c>
-      <c r="E626">
-        <v>1</v>
-      </c>
-      <c r="L626">
+      <c r="K626">
+        <v>1</v>
+      </c>
+      <c r="AK626">
         <v>1</v>
       </c>
       <c r="AN626">
@@ -34342,7 +33507,7 @@
       <c r="D628" t="s">
         <v>43</v>
       </c>
-      <c r="AF628">
+      <c r="AC628">
         <v>1</v>
       </c>
     </row>
@@ -34359,10 +33524,7 @@
       <c r="D629" t="s">
         <v>46</v>
       </c>
-      <c r="N629">
-        <v>1</v>
-      </c>
-      <c r="O629">
+      <c r="M629">
         <v>1</v>
       </c>
     </row>
@@ -34379,6 +33541,9 @@
       <c r="D630" t="s">
         <v>1416</v>
       </c>
+      <c r="AK630">
+        <v>1</v>
+      </c>
       <c r="AN630">
         <v>1</v>
       </c>
@@ -34396,10 +33561,7 @@
       <c r="D631" t="s">
         <v>52</v>
       </c>
-      <c r="N631">
-        <v>1</v>
-      </c>
-      <c r="O631">
+      <c r="M631">
         <v>1</v>
       </c>
     </row>
@@ -34416,10 +33578,7 @@
       <c r="D632" t="s">
         <v>40</v>
       </c>
-      <c r="N632">
-        <v>1</v>
-      </c>
-      <c r="O632">
+      <c r="M632">
         <v>1</v>
       </c>
     </row>
@@ -34464,6 +33623,9 @@
       <c r="D635" t="s">
         <v>49</v>
       </c>
+      <c r="AK635">
+        <v>1</v>
+      </c>
       <c r="AN635">
         <v>1</v>
       </c>
@@ -34481,10 +33643,7 @@
       <c r="D636" t="s">
         <v>52</v>
       </c>
-      <c r="E636">
-        <v>1</v>
-      </c>
-      <c r="K636">
+      <c r="J636">
         <v>1</v>
       </c>
     </row>
@@ -34501,6 +33660,9 @@
       <c r="D637" t="s">
         <v>40</v>
       </c>
+      <c r="AK637">
+        <v>1</v>
+      </c>
       <c r="AN637">
         <v>1</v>
       </c>
@@ -34518,10 +33680,7 @@
       <c r="D638" t="s">
         <v>43</v>
       </c>
-      <c r="N638">
-        <v>1</v>
-      </c>
-      <c r="O638">
+      <c r="M638">
         <v>1</v>
       </c>
     </row>
@@ -34538,6 +33697,9 @@
       <c r="D639" t="s">
         <v>46</v>
       </c>
+      <c r="AK639">
+        <v>1</v>
+      </c>
       <c r="AN639">
         <v>1</v>
       </c>
@@ -34555,16 +33717,10 @@
       <c r="D640" t="s">
         <v>49</v>
       </c>
-      <c r="E640">
-        <v>1</v>
-      </c>
-      <c r="H640">
-        <v>1</v>
-      </c>
-      <c r="N640">
-        <v>1</v>
-      </c>
-      <c r="T640">
+      <c r="G640">
+        <v>1</v>
+      </c>
+      <c r="R640">
         <v>1</v>
       </c>
     </row>
@@ -34623,10 +33779,7 @@
       <c r="D644" t="s">
         <v>46</v>
       </c>
-      <c r="N644">
-        <v>1</v>
-      </c>
-      <c r="O644">
+      <c r="M644">
         <v>1</v>
       </c>
     </row>
@@ -34644,18 +33797,15 @@
         <v>49</v>
       </c>
       <c r="E645">
-        <v>2</v>
-      </c>
-      <c r="F645">
-        <v>1</v>
-      </c>
-      <c r="H645">
-        <v>1</v>
-      </c>
-      <c r="AI645">
-        <v>1</v>
-      </c>
-      <c r="AJ645">
+        <v>1</v>
+      </c>
+      <c r="G645">
+        <v>1</v>
+      </c>
+      <c r="AF645">
+        <v>1</v>
+      </c>
+      <c r="AG645">
         <v>1</v>
       </c>
     </row>
@@ -34672,10 +33822,7 @@
       <c r="D646" t="s">
         <v>52</v>
       </c>
-      <c r="N646">
-        <v>1</v>
-      </c>
-      <c r="O646">
+      <c r="M646">
         <v>1</v>
       </c>
     </row>
@@ -34706,10 +33853,7 @@
       <c r="D648" t="s">
         <v>43</v>
       </c>
-      <c r="N648">
-        <v>1</v>
-      </c>
-      <c r="O648">
+      <c r="M648">
         <v>1</v>
       </c>
     </row>
@@ -34726,10 +33870,7 @@
       <c r="D649" t="s">
         <v>46</v>
       </c>
-      <c r="W649">
-        <v>1</v>
-      </c>
-      <c r="AB649">
+      <c r="Y649">
         <v>1</v>
       </c>
     </row>
@@ -34747,27 +33888,21 @@
         <v>49</v>
       </c>
       <c r="E650">
-        <v>2</v>
-      </c>
-      <c r="F650">
-        <v>1</v>
-      </c>
-      <c r="K650">
+        <v>1</v>
+      </c>
+      <c r="J650">
+        <v>1</v>
+      </c>
+      <c r="U650">
         <v>1</v>
       </c>
       <c r="W650">
-        <v>2</v>
-      </c>
-      <c r="X650">
-        <v>1</v>
-      </c>
-      <c r="Z650">
-        <v>1</v>
-      </c>
-      <c r="AI650">
-        <v>1</v>
-      </c>
-      <c r="AJ650">
+        <v>1</v>
+      </c>
+      <c r="AF650">
+        <v>1</v>
+      </c>
+      <c r="AG650">
         <v>1</v>
       </c>
     </row>
@@ -34812,6 +33947,9 @@
       <c r="D653" t="s">
         <v>43</v>
       </c>
+      <c r="AJ653">
+        <v>1</v>
+      </c>
       <c r="AM653">
         <v>1</v>
       </c>
@@ -34829,10 +33967,7 @@
       <c r="D654" t="s">
         <v>46</v>
       </c>
-      <c r="N654">
-        <v>1</v>
-      </c>
-      <c r="O654">
+      <c r="M654">
         <v>1</v>
       </c>
     </row>
@@ -34850,18 +33985,12 @@
         <v>49</v>
       </c>
       <c r="E655">
-        <v>2</v>
-      </c>
-      <c r="F655">
-        <v>1</v>
-      </c>
-      <c r="K655">
-        <v>1</v>
-      </c>
-      <c r="N655">
-        <v>1</v>
-      </c>
-      <c r="O655">
+        <v>1</v>
+      </c>
+      <c r="J655">
+        <v>1</v>
+      </c>
+      <c r="M655">
         <v>1</v>
       </c>
     </row>
@@ -34878,7 +34007,7 @@
       <c r="D656" t="s">
         <v>52</v>
       </c>
-      <c r="AF656">
+      <c r="AC656">
         <v>1</v>
       </c>
     </row>
@@ -34909,22 +34038,16 @@
       <c r="D658" t="s">
         <v>43</v>
       </c>
-      <c r="E658">
-        <v>1</v>
-      </c>
-      <c r="K658">
-        <v>1</v>
-      </c>
-      <c r="N658">
-        <v>1</v>
-      </c>
-      <c r="O658">
-        <v>1</v>
-      </c>
-      <c r="AI658">
-        <v>1</v>
-      </c>
-      <c r="AJ658">
+      <c r="J658">
+        <v>1</v>
+      </c>
+      <c r="M658">
+        <v>1</v>
+      </c>
+      <c r="AF658">
+        <v>1</v>
+      </c>
+      <c r="AG658">
         <v>1</v>
       </c>
     </row>
@@ -34958,9 +34081,6 @@
       <c r="E660">
         <v>1</v>
       </c>
-      <c r="F660">
-        <v>1</v>
-      </c>
     </row>
     <row r="661">
       <c r="A661" t="s">
@@ -34975,13 +34095,13 @@
       <c r="D661" t="s">
         <v>52</v>
       </c>
-      <c r="E661">
-        <v>1</v>
-      </c>
-      <c r="L661">
-        <v>1</v>
-      </c>
-      <c r="AH661">
+      <c r="K661">
+        <v>1</v>
+      </c>
+      <c r="AE661">
+        <v>1</v>
+      </c>
+      <c r="AK661">
         <v>1</v>
       </c>
       <c r="AN661">
@@ -35001,6 +34121,9 @@
       <c r="D662" t="s">
         <v>40</v>
       </c>
+      <c r="AK662">
+        <v>1</v>
+      </c>
       <c r="AN662">
         <v>1</v>
       </c>
@@ -35018,16 +34141,13 @@
       <c r="D663" t="s">
         <v>43</v>
       </c>
-      <c r="N663">
-        <v>1</v>
-      </c>
-      <c r="O663">
-        <v>1</v>
-      </c>
-      <c r="AI663">
-        <v>1</v>
-      </c>
-      <c r="AJ663">
+      <c r="M663">
+        <v>1</v>
+      </c>
+      <c r="AF663">
+        <v>1</v>
+      </c>
+      <c r="AG663">
         <v>1</v>
       </c>
     </row>
@@ -35047,9 +34167,6 @@
       <c r="E664">
         <v>1</v>
       </c>
-      <c r="F664">
-        <v>1</v>
-      </c>
     </row>
     <row r="665">
       <c r="A665" t="s">
@@ -35064,16 +34181,10 @@
       <c r="D665" t="s">
         <v>49</v>
       </c>
-      <c r="E665">
-        <v>1</v>
-      </c>
-      <c r="K665">
-        <v>1</v>
-      </c>
-      <c r="N665">
-        <v>1</v>
-      </c>
-      <c r="O665">
+      <c r="J665">
+        <v>1</v>
+      </c>
+      <c r="M665">
         <v>1</v>
       </c>
     </row>
@@ -35093,13 +34204,7 @@
       <c r="E666">
         <v>1</v>
       </c>
-      <c r="F666">
-        <v>1</v>
-      </c>
       <c r="W666">
-        <v>1</v>
-      </c>
-      <c r="Z666">
         <v>1</v>
       </c>
     </row>
@@ -35130,10 +34235,7 @@
       <c r="D668" t="s">
         <v>43</v>
       </c>
-      <c r="W668">
-        <v>1</v>
-      </c>
-      <c r="AA668">
+      <c r="X668">
         <v>1</v>
       </c>
     </row>
@@ -35150,10 +34252,7 @@
       <c r="D669" t="s">
         <v>46</v>
       </c>
-      <c r="N669">
-        <v>1</v>
-      </c>
-      <c r="O669">
+      <c r="M669">
         <v>1</v>
       </c>
     </row>
@@ -35170,10 +34269,7 @@
       <c r="D670" t="s">
         <v>49</v>
       </c>
-      <c r="W670">
-        <v>1</v>
-      </c>
-      <c r="AC670">
+      <c r="Z670">
         <v>1</v>
       </c>
     </row>
@@ -35190,6 +34286,9 @@
       <c r="D671" t="s">
         <v>52</v>
       </c>
+      <c r="AK671">
+        <v>1</v>
+      </c>
       <c r="AN671">
         <v>1</v>
       </c>
@@ -35221,6 +34320,9 @@
       <c r="D673" t="s">
         <v>43</v>
       </c>
+      <c r="AJ673">
+        <v>1</v>
+      </c>
       <c r="AM673">
         <v>1</v>
       </c>
@@ -35252,10 +34354,7 @@
       <c r="D675" t="s">
         <v>49</v>
       </c>
-      <c r="E675">
-        <v>1</v>
-      </c>
-      <c r="K675">
+      <c r="J675">
         <v>1</v>
       </c>
     </row>
@@ -35272,7 +34371,7 @@
       <c r="D676" t="s">
         <v>52</v>
       </c>
-      <c r="AH676">
+      <c r="AE676">
         <v>1</v>
       </c>
     </row>
@@ -35303,13 +34402,10 @@
       <c r="D678" t="s">
         <v>43</v>
       </c>
-      <c r="N678">
-        <v>1</v>
-      </c>
-      <c r="V678">
-        <v>1</v>
-      </c>
-      <c r="AK678">
+      <c r="T678">
+        <v>1</v>
+      </c>
+      <c r="AH678">
         <v>1</v>
       </c>
     </row>
@@ -35326,6 +34422,9 @@
       <c r="D679" t="s">
         <v>46</v>
       </c>
+      <c r="AK679">
+        <v>1</v>
+      </c>
       <c r="AN679">
         <v>1</v>
       </c>
@@ -35357,10 +34456,10 @@
       <c r="D681" t="s">
         <v>52</v>
       </c>
-      <c r="N681">
-        <v>1</v>
-      </c>
-      <c r="O681">
+      <c r="M681">
+        <v>1</v>
+      </c>
+      <c r="AJ681">
         <v>1</v>
       </c>
       <c r="AM681">
@@ -35395,30 +34494,21 @@
         <v>43</v>
       </c>
       <c r="E683">
-        <v>2</v>
-      </c>
-      <c r="F683">
-        <v>1</v>
-      </c>
-      <c r="K683">
-        <v>1</v>
-      </c>
-      <c r="N683">
-        <v>1</v>
-      </c>
-      <c r="O683">
-        <v>1</v>
-      </c>
-      <c r="W683">
-        <v>1</v>
-      </c>
-      <c r="X683">
-        <v>1</v>
-      </c>
-      <c r="AI683">
-        <v>1</v>
-      </c>
-      <c r="AJ683">
+        <v>1</v>
+      </c>
+      <c r="J683">
+        <v>1</v>
+      </c>
+      <c r="M683">
+        <v>1</v>
+      </c>
+      <c r="U683">
+        <v>1</v>
+      </c>
+      <c r="AF683">
+        <v>1</v>
+      </c>
+      <c r="AG683">
         <v>1</v>
       </c>
     </row>
@@ -35435,10 +34525,7 @@
       <c r="D684" t="s">
         <v>46</v>
       </c>
-      <c r="W684">
-        <v>1</v>
-      </c>
-      <c r="X684">
+      <c r="U684">
         <v>1</v>
       </c>
     </row>
@@ -35458,13 +34545,7 @@
       <c r="E685">
         <v>1</v>
       </c>
-      <c r="F685">
-        <v>1</v>
-      </c>
-      <c r="N685">
-        <v>1</v>
-      </c>
-      <c r="O685">
+      <c r="M685">
         <v>1</v>
       </c>
     </row>
@@ -35481,10 +34562,7 @@
       <c r="D686" t="s">
         <v>52</v>
       </c>
-      <c r="N686">
-        <v>1</v>
-      </c>
-      <c r="O686">
+      <c r="M686">
         <v>1</v>
       </c>
     </row>
@@ -35529,19 +34607,13 @@
       <c r="D689" t="s">
         <v>46</v>
       </c>
-      <c r="N689">
-        <v>1</v>
-      </c>
-      <c r="O689">
+      <c r="M689">
         <v>1</v>
       </c>
       <c r="W689">
         <v>1</v>
       </c>
-      <c r="Z689">
-        <v>1</v>
-      </c>
-      <c r="AE689">
+      <c r="AB689">
         <v>1</v>
       </c>
     </row>
@@ -35573,12 +34645,9 @@
         <v>52</v>
       </c>
       <c r="E691">
-        <v>2</v>
-      </c>
-      <c r="F691">
-        <v>1</v>
-      </c>
-      <c r="K691">
+        <v>1</v>
+      </c>
+      <c r="J691">
         <v>1</v>
       </c>
     </row>
@@ -35609,10 +34678,7 @@
       <c r="D693" t="s">
         <v>43</v>
       </c>
-      <c r="N693">
-        <v>1</v>
-      </c>
-      <c r="O693">
+      <c r="M693">
         <v>1</v>
       </c>
     </row>
@@ -35629,6 +34695,9 @@
       <c r="D694" t="s">
         <v>46</v>
       </c>
+      <c r="AK694">
+        <v>1</v>
+      </c>
       <c r="AN694">
         <v>1</v>
       </c>
@@ -35649,13 +34718,7 @@
       <c r="E695">
         <v>1</v>
       </c>
-      <c r="F695">
-        <v>1</v>
-      </c>
-      <c r="N695">
-        <v>1</v>
-      </c>
-      <c r="O695">
+      <c r="M695">
         <v>1</v>
       </c>
     </row>
@@ -35714,10 +34777,7 @@
       <c r="D699" t="s">
         <v>46</v>
       </c>
-      <c r="N699">
-        <v>1</v>
-      </c>
-      <c r="O699">
+      <c r="M699">
         <v>1</v>
       </c>
     </row>
@@ -35737,9 +34797,6 @@
       <c r="W700">
         <v>1</v>
       </c>
-      <c r="Z700">
-        <v>1</v>
-      </c>
     </row>
     <row r="701">
       <c r="A701" t="s">
@@ -35796,16 +34853,10 @@
       <c r="D704" t="s">
         <v>46</v>
       </c>
-      <c r="E704">
-        <v>1</v>
-      </c>
-      <c r="K704">
-        <v>1</v>
-      </c>
-      <c r="N704">
-        <v>1</v>
-      </c>
-      <c r="O704">
+      <c r="J704">
+        <v>1</v>
+      </c>
+      <c r="M704">
         <v>1</v>
       </c>
     </row>
@@ -35864,6 +34915,9 @@
       <c r="D708" t="s">
         <v>43</v>
       </c>
+      <c r="AK708">
+        <v>1</v>
+      </c>
       <c r="AN708">
         <v>1</v>
       </c>
@@ -35881,10 +34935,7 @@
       <c r="D709" t="s">
         <v>46</v>
       </c>
-      <c r="N709">
-        <v>1</v>
-      </c>
-      <c r="O709">
+      <c r="M709">
         <v>1</v>
       </c>
     </row>
@@ -35971,16 +35022,13 @@
       <c r="D715" t="s">
         <v>49</v>
       </c>
-      <c r="E715">
-        <v>1</v>
-      </c>
-      <c r="K715">
-        <v>1</v>
-      </c>
-      <c r="W715">
-        <v>1</v>
-      </c>
-      <c r="AB715">
+      <c r="J715">
+        <v>1</v>
+      </c>
+      <c r="Y715">
+        <v>1</v>
+      </c>
+      <c r="AK715">
         <v>1</v>
       </c>
       <c r="AN715">
@@ -36000,10 +35048,7 @@
       <c r="D716" t="s">
         <v>52</v>
       </c>
-      <c r="N716">
-        <v>1</v>
-      </c>
-      <c r="O716">
+      <c r="M716">
         <v>1</v>
       </c>
     </row>
@@ -36034,10 +35079,7 @@
       <c r="D718" t="s">
         <v>43</v>
       </c>
-      <c r="N718">
-        <v>1</v>
-      </c>
-      <c r="O718">
+      <c r="M718">
         <v>1</v>
       </c>
     </row>
@@ -36069,18 +35111,12 @@
         <v>49</v>
       </c>
       <c r="E720">
-        <v>2</v>
-      </c>
-      <c r="F720">
-        <v>1</v>
-      </c>
-      <c r="K720">
-        <v>1</v>
-      </c>
-      <c r="W720">
-        <v>1</v>
-      </c>
-      <c r="Y720">
+        <v>1</v>
+      </c>
+      <c r="J720">
+        <v>1</v>
+      </c>
+      <c r="V720">
         <v>1</v>
       </c>
     </row>
@@ -36097,22 +35133,16 @@
       <c r="D721" t="s">
         <v>52</v>
       </c>
-      <c r="E721">
-        <v>1</v>
-      </c>
-      <c r="L721">
-        <v>1</v>
-      </c>
-      <c r="N721">
-        <v>1</v>
-      </c>
-      <c r="O721">
+      <c r="K721">
+        <v>1</v>
+      </c>
+      <c r="M721">
+        <v>1</v>
+      </c>
+      <c r="AC721">
         <v>1</v>
       </c>
       <c r="AF721">
-        <v>1</v>
-      </c>
-      <c r="AI721">
         <v>1</v>
       </c>
     </row>
@@ -36171,10 +35201,7 @@
       <c r="D725" t="s">
         <v>49</v>
       </c>
-      <c r="N725">
-        <v>1</v>
-      </c>
-      <c r="O725">
+      <c r="M725">
         <v>1</v>
       </c>
     </row>
@@ -36191,13 +35218,10 @@
       <c r="D726" t="s">
         <v>52</v>
       </c>
-      <c r="E726">
-        <v>1</v>
-      </c>
-      <c r="H726">
-        <v>1</v>
-      </c>
-      <c r="AI726">
+      <c r="G726">
+        <v>1</v>
+      </c>
+      <c r="AF726">
         <v>1</v>
       </c>
     </row>
@@ -36214,6 +35238,9 @@
       <c r="D727" t="s">
         <v>40</v>
       </c>
+      <c r="AK727">
+        <v>1</v>
+      </c>
       <c r="AN727">
         <v>1</v>
       </c>
@@ -36234,9 +35261,6 @@
       <c r="W728">
         <v>1</v>
       </c>
-      <c r="Z728">
-        <v>1</v>
-      </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
@@ -36266,12 +35290,9 @@
         <v>49</v>
       </c>
       <c r="E730">
-        <v>2</v>
-      </c>
-      <c r="F730">
-        <v>1</v>
-      </c>
-      <c r="K730">
+        <v>1</v>
+      </c>
+      <c r="J730">
         <v>1</v>
       </c>
     </row>
@@ -36316,10 +35337,10 @@
       <c r="D733" t="s">
         <v>43</v>
       </c>
-      <c r="AI733">
-        <v>1</v>
-      </c>
-      <c r="AJ733">
+      <c r="AF733">
+        <v>1</v>
+      </c>
+      <c r="AG733">
         <v>1</v>
       </c>
     </row>
@@ -36350,10 +35371,7 @@
       <c r="D735" t="s">
         <v>49</v>
       </c>
-      <c r="E735">
-        <v>1</v>
-      </c>
-      <c r="K735">
+      <c r="J735">
         <v>1</v>
       </c>
     </row>
@@ -36398,16 +35416,13 @@
       <c r="D738" t="s">
         <v>43</v>
       </c>
-      <c r="N738">
-        <v>1</v>
-      </c>
-      <c r="O738">
-        <v>1</v>
-      </c>
-      <c r="AI738">
-        <v>1</v>
-      </c>
-      <c r="AJ738">
+      <c r="M738">
+        <v>1</v>
+      </c>
+      <c r="AF738">
+        <v>1</v>
+      </c>
+      <c r="AG738">
         <v>1</v>
       </c>
     </row>
@@ -36424,6 +35439,9 @@
       <c r="D739" t="s">
         <v>46</v>
       </c>
+      <c r="AJ739">
+        <v>1</v>
+      </c>
       <c r="AM739">
         <v>1</v>
       </c>
@@ -36442,12 +35460,9 @@
         <v>49</v>
       </c>
       <c r="E740">
-        <v>2</v>
-      </c>
-      <c r="F740">
-        <v>1</v>
-      </c>
-      <c r="K740">
+        <v>1</v>
+      </c>
+      <c r="J740">
         <v>1</v>
       </c>
     </row>
@@ -36464,10 +35479,7 @@
       <c r="D741" t="s">
         <v>52</v>
       </c>
-      <c r="N741">
-        <v>1</v>
-      </c>
-      <c r="O741">
+      <c r="M741">
         <v>1</v>
       </c>
     </row>
@@ -36484,16 +35496,10 @@
       <c r="D742" t="s">
         <v>40</v>
       </c>
-      <c r="E742">
-        <v>1</v>
-      </c>
-      <c r="G742">
-        <v>1</v>
-      </c>
-      <c r="N742">
-        <v>1</v>
-      </c>
-      <c r="O742">
+      <c r="F742">
+        <v>1</v>
+      </c>
+      <c r="M742">
         <v>1</v>
       </c>
     </row>
@@ -36538,10 +35544,7 @@
       <c r="D745" t="s">
         <v>49</v>
       </c>
-      <c r="N745">
-        <v>1</v>
-      </c>
-      <c r="O745">
+      <c r="M745">
         <v>1</v>
       </c>
     </row>
@@ -36558,16 +35561,13 @@
       <c r="D746" t="s">
         <v>52</v>
       </c>
-      <c r="W746">
-        <v>1</v>
-      </c>
-      <c r="X746">
-        <v>1</v>
-      </c>
-      <c r="AE746">
-        <v>1</v>
-      </c>
-      <c r="AI746">
+      <c r="U746">
+        <v>1</v>
+      </c>
+      <c r="AB746">
+        <v>1</v>
+      </c>
+      <c r="AF746">
         <v>1</v>
       </c>
     </row>
@@ -36601,16 +35601,10 @@
       <c r="E748">
         <v>1</v>
       </c>
-      <c r="F748">
-        <v>1</v>
-      </c>
-      <c r="W748">
-        <v>1</v>
-      </c>
-      <c r="Y748">
-        <v>1</v>
-      </c>
-      <c r="AI748">
+      <c r="V748">
+        <v>1</v>
+      </c>
+      <c r="AF748">
         <v>1</v>
       </c>
     </row>
@@ -36641,6 +35635,9 @@
       <c r="D750" t="s">
         <v>49</v>
       </c>
+      <c r="AJ750">
+        <v>1</v>
+      </c>
       <c r="AM750">
         <v>1</v>
       </c>
@@ -36659,18 +35656,12 @@
         <v>52</v>
       </c>
       <c r="E751">
-        <v>2</v>
-      </c>
-      <c r="F751">
-        <v>1</v>
-      </c>
-      <c r="K751">
-        <v>1</v>
-      </c>
-      <c r="W751">
-        <v>1</v>
-      </c>
-      <c r="AA751">
+        <v>1</v>
+      </c>
+      <c r="J751">
+        <v>1</v>
+      </c>
+      <c r="X751">
         <v>1</v>
       </c>
     </row>
@@ -36687,10 +35678,13 @@
       <c r="D752" t="s">
         <v>40</v>
       </c>
+      <c r="AB752">
+        <v>1</v>
+      </c>
       <c r="AE752">
         <v>1</v>
       </c>
-      <c r="AH752">
+      <c r="AK752">
         <v>1</v>
       </c>
       <c r="AN752">
@@ -36724,22 +35718,16 @@
       <c r="D754" t="s">
         <v>46</v>
       </c>
-      <c r="E754">
-        <v>1</v>
-      </c>
-      <c r="K754">
-        <v>1</v>
-      </c>
-      <c r="W754">
-        <v>1</v>
-      </c>
-      <c r="Y754">
-        <v>1</v>
-      </c>
-      <c r="AI754">
-        <v>1</v>
-      </c>
-      <c r="AJ754">
+      <c r="J754">
+        <v>1</v>
+      </c>
+      <c r="V754">
+        <v>1</v>
+      </c>
+      <c r="AF754">
+        <v>1</v>
+      </c>
+      <c r="AG754">
         <v>1</v>
       </c>
     </row>
@@ -36756,6 +35744,9 @@
       <c r="D755" t="s">
         <v>49</v>
       </c>
+      <c r="AK755">
+        <v>1</v>
+      </c>
       <c r="AN755">
         <v>1</v>
       </c>
@@ -36776,16 +35767,10 @@
       <c r="E756">
         <v>1</v>
       </c>
-      <c r="F756">
-        <v>1</v>
-      </c>
-      <c r="N756">
-        <v>1</v>
-      </c>
-      <c r="O756">
-        <v>1</v>
-      </c>
-      <c r="AE756">
+      <c r="M756">
+        <v>1</v>
+      </c>
+      <c r="AB756">
         <v>1</v>
       </c>
     </row>
@@ -36802,10 +35787,7 @@
       <c r="D757" t="s">
         <v>40</v>
       </c>
-      <c r="N757">
-        <v>1</v>
-      </c>
-      <c r="O757">
+      <c r="M757">
         <v>1</v>
       </c>
     </row>
@@ -36822,6 +35804,9 @@
       <c r="D758" t="s">
         <v>43</v>
       </c>
+      <c r="AK758">
+        <v>1</v>
+      </c>
       <c r="AN758">
         <v>1</v>
       </c>
@@ -36839,16 +35824,10 @@
       <c r="D759" t="s">
         <v>46</v>
       </c>
-      <c r="E759">
-        <v>1</v>
-      </c>
-      <c r="K759">
-        <v>1</v>
-      </c>
-      <c r="N759">
-        <v>1</v>
-      </c>
-      <c r="O759">
+      <c r="J759">
+        <v>1</v>
+      </c>
+      <c r="M759">
         <v>1</v>
       </c>
     </row>
@@ -36907,6 +35886,9 @@
       <c r="D763" t="s">
         <v>43</v>
       </c>
+      <c r="AK763">
+        <v>1</v>
+      </c>
       <c r="AN763">
         <v>1</v>
       </c>
@@ -36924,13 +35906,13 @@
       <c r="D764" t="s">
         <v>46</v>
       </c>
-      <c r="N764">
-        <v>1</v>
-      </c>
-      <c r="O764">
-        <v>1</v>
-      </c>
-      <c r="AH764">
+      <c r="M764">
+        <v>1</v>
+      </c>
+      <c r="AE764">
+        <v>1</v>
+      </c>
+      <c r="AK764">
         <v>1</v>
       </c>
       <c r="AN764">
@@ -36950,16 +35932,13 @@
       <c r="D765" t="s">
         <v>49</v>
       </c>
-      <c r="N765">
-        <v>1</v>
-      </c>
-      <c r="O765">
-        <v>1</v>
-      </c>
-      <c r="AI765">
-        <v>1</v>
-      </c>
-      <c r="AJ765">
+      <c r="M765">
+        <v>1</v>
+      </c>
+      <c r="AF765">
+        <v>1</v>
+      </c>
+      <c r="AG765">
         <v>1</v>
       </c>
     </row>
@@ -37004,16 +35983,13 @@
       <c r="D768" t="s">
         <v>43</v>
       </c>
-      <c r="E768">
-        <v>1</v>
-      </c>
-      <c r="K768">
-        <v>1</v>
-      </c>
-      <c r="W768">
-        <v>1</v>
-      </c>
-      <c r="AB768">
+      <c r="J768">
+        <v>1</v>
+      </c>
+      <c r="Y768">
+        <v>1</v>
+      </c>
+      <c r="AK768">
         <v>1</v>
       </c>
       <c r="AN768">
@@ -37047,10 +36023,7 @@
       <c r="D770" t="s">
         <v>49</v>
       </c>
-      <c r="N770">
-        <v>1</v>
-      </c>
-      <c r="O770">
+      <c r="M770">
         <v>1</v>
       </c>
     </row>
@@ -37067,16 +36040,10 @@
       <c r="D771" t="s">
         <v>52</v>
       </c>
-      <c r="N771">
-        <v>1</v>
-      </c>
-      <c r="O771">
+      <c r="M771">
         <v>1</v>
       </c>
       <c r="W771">
-        <v>1</v>
-      </c>
-      <c r="Z771">
         <v>1</v>
       </c>
     </row>
@@ -37107,10 +36074,7 @@
       <c r="D773" t="s">
         <v>43</v>
       </c>
-      <c r="W773">
-        <v>1</v>
-      </c>
-      <c r="X773">
+      <c r="U773">
         <v>1</v>
       </c>
     </row>
@@ -37127,6 +36091,9 @@
       <c r="D774" t="s">
         <v>46</v>
       </c>
+      <c r="AK774">
+        <v>1</v>
+      </c>
       <c r="AN774">
         <v>1</v>
       </c>
@@ -37144,16 +36111,10 @@
       <c r="D775" t="s">
         <v>49</v>
       </c>
-      <c r="E775">
-        <v>1</v>
-      </c>
-      <c r="G775">
-        <v>1</v>
-      </c>
-      <c r="N775">
-        <v>1</v>
-      </c>
-      <c r="O775">
+      <c r="F775">
+        <v>1</v>
+      </c>
+      <c r="M775">
         <v>1</v>
       </c>
     </row>
@@ -37170,19 +36131,13 @@
       <c r="D776" t="s">
         <v>52</v>
       </c>
-      <c r="E776">
-        <v>1</v>
-      </c>
-      <c r="L776">
-        <v>1</v>
-      </c>
-      <c r="W776">
-        <v>1</v>
-      </c>
-      <c r="Y776">
-        <v>1</v>
-      </c>
-      <c r="AI776">
+      <c r="K776">
+        <v>1</v>
+      </c>
+      <c r="V776">
+        <v>1</v>
+      </c>
+      <c r="AF776">
         <v>1</v>
       </c>
     </row>
@@ -37227,10 +36182,7 @@
       <c r="D779" t="s">
         <v>46</v>
       </c>
-      <c r="W779">
-        <v>1</v>
-      </c>
-      <c r="Y779">
+      <c r="V779">
         <v>1</v>
       </c>
     </row>
@@ -37247,10 +36199,7 @@
       <c r="D780" t="s">
         <v>49</v>
       </c>
-      <c r="W780">
-        <v>1</v>
-      </c>
-      <c r="AA780">
+      <c r="X780">
         <v>1</v>
       </c>
     </row>
@@ -37270,7 +36219,7 @@
       <c r="E781">
         <v>1</v>
       </c>
-      <c r="F781">
+      <c r="AK781">
         <v>1</v>
       </c>
       <c r="AN781">
@@ -37318,6 +36267,9 @@
       <c r="D784" t="s">
         <v>46</v>
       </c>
+      <c r="AK784">
+        <v>1</v>
+      </c>
       <c r="AN784">
         <v>1</v>
       </c>
@@ -37335,10 +36287,7 @@
       <c r="D785" t="s">
         <v>49</v>
       </c>
-      <c r="E785">
-        <v>1</v>
-      </c>
-      <c r="H785">
+      <c r="G785">
         <v>1</v>
       </c>
     </row>
@@ -37355,7 +36304,7 @@
       <c r="D786" t="s">
         <v>52</v>
       </c>
-      <c r="AH786">
+      <c r="AE786">
         <v>1</v>
       </c>
     </row>
@@ -37400,6 +36349,9 @@
       <c r="D789" t="s">
         <v>46</v>
       </c>
+      <c r="M789">
+        <v>1</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="s">
@@ -37414,10 +36366,13 @@
       <c r="D790" t="s">
         <v>49</v>
       </c>
-      <c r="AI790">
-        <v>1</v>
-      </c>
-      <c r="AJ790">
+      <c r="J790">
+        <v>1</v>
+      </c>
+      <c r="AF790">
+        <v>1</v>
+      </c>
+      <c r="AG790">
         <v>1</v>
       </c>
     </row>
@@ -37434,6 +36389,9 @@
       <c r="D791" t="s">
         <v>52</v>
       </c>
+      <c r="AJ791">
+        <v>1</v>
+      </c>
       <c r="AM791">
         <v>1</v>
       </c>
@@ -37468,9 +36426,6 @@
       <c r="E793">
         <v>1</v>
       </c>
-      <c r="F793">
-        <v>1</v>
-      </c>
     </row>
     <row r="794">
       <c r="A794" t="s">
@@ -37485,10 +36440,7 @@
       <c r="D794" t="s">
         <v>46</v>
       </c>
-      <c r="N794">
-        <v>1</v>
-      </c>
-      <c r="O794">
+      <c r="M794">
         <v>1</v>
       </c>
     </row>
@@ -37505,16 +36457,10 @@
       <c r="D795" t="s">
         <v>49</v>
       </c>
-      <c r="N795">
-        <v>1</v>
-      </c>
-      <c r="O795">
-        <v>1</v>
-      </c>
-      <c r="W795">
-        <v>1</v>
-      </c>
-      <c r="AA795">
+      <c r="M795">
+        <v>1</v>
+      </c>
+      <c r="X795">
         <v>1</v>
       </c>
     </row>
@@ -37532,15 +36478,12 @@
         <v>52</v>
       </c>
       <c r="E796">
-        <v>2</v>
-      </c>
-      <c r="F796">
-        <v>1</v>
-      </c>
-      <c r="K796">
-        <v>1</v>
-      </c>
-      <c r="AH796">
+        <v>1</v>
+      </c>
+      <c r="J796">
+        <v>1</v>
+      </c>
+      <c r="AE796">
         <v>1</v>
       </c>
     </row>
@@ -37574,9 +36517,6 @@
       <c r="E798">
         <v>1</v>
       </c>
-      <c r="F798">
-        <v>1</v>
-      </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
@@ -37591,6 +36531,9 @@
       <c r="D799" t="s">
         <v>46</v>
       </c>
+      <c r="AI799">
+        <v>1</v>
+      </c>
       <c r="AL799">
         <v>1</v>
       </c>
@@ -37625,9 +36568,6 @@
       <c r="E801">
         <v>1</v>
       </c>
-      <c r="F801">
-        <v>1</v>
-      </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
@@ -37659,13 +36599,7 @@
       <c r="E803">
         <v>1</v>
       </c>
-      <c r="F803">
-        <v>1</v>
-      </c>
-      <c r="W803">
-        <v>1</v>
-      </c>
-      <c r="Y803">
+      <c r="V803">
         <v>1</v>
       </c>
     </row>
@@ -37682,10 +36616,7 @@
       <c r="D804" t="s">
         <v>46</v>
       </c>
-      <c r="N804">
-        <v>1</v>
-      </c>
-      <c r="O804">
+      <c r="M804">
         <v>1</v>
       </c>
     </row>
@@ -37702,13 +36633,13 @@
       <c r="D805" t="s">
         <v>49</v>
       </c>
-      <c r="W805">
-        <v>2</v>
-      </c>
-      <c r="X805">
-        <v>1</v>
-      </c>
-      <c r="Y805">
+      <c r="U805">
+        <v>1</v>
+      </c>
+      <c r="V805">
+        <v>1</v>
+      </c>
+      <c r="AK805">
         <v>1</v>
       </c>
       <c r="AN805">
@@ -37729,12 +36660,9 @@
         <v>52</v>
       </c>
       <c r="E806">
-        <v>2</v>
-      </c>
-      <c r="F806">
-        <v>1</v>
-      </c>
-      <c r="K806">
+        <v>1</v>
+      </c>
+      <c r="J806">
         <v>1</v>
       </c>
     </row>
@@ -37782,9 +36710,6 @@
       <c r="E809">
         <v>1</v>
       </c>
-      <c r="F809">
-        <v>1</v>
-      </c>
     </row>
     <row r="810">
       <c r="A810" t="s">
@@ -37799,10 +36724,10 @@
       <c r="D810" t="s">
         <v>49</v>
       </c>
-      <c r="N810">
-        <v>1</v>
-      </c>
-      <c r="O810">
+      <c r="M810">
+        <v>1</v>
+      </c>
+      <c r="AK810">
         <v>1</v>
       </c>
       <c r="AN810">
@@ -37864,16 +36789,13 @@
       <c r="D814" t="s">
         <v>46</v>
       </c>
-      <c r="N814">
-        <v>1</v>
-      </c>
-      <c r="O814">
-        <v>1</v>
-      </c>
-      <c r="AI814">
-        <v>1</v>
-      </c>
-      <c r="AJ814">
+      <c r="M814">
+        <v>1</v>
+      </c>
+      <c r="AF814">
+        <v>1</v>
+      </c>
+      <c r="AG814">
         <v>1</v>
       </c>
     </row>
@@ -37890,10 +36812,10 @@
       <c r="D815" t="s">
         <v>49</v>
       </c>
-      <c r="W815">
-        <v>1</v>
-      </c>
-      <c r="Y815">
+      <c r="V815">
+        <v>1</v>
+      </c>
+      <c r="AK815">
         <v>1</v>
       </c>
       <c r="AN815">
@@ -37941,16 +36863,13 @@
       <c r="D818" t="s">
         <v>43</v>
       </c>
-      <c r="N818">
-        <v>1</v>
-      </c>
-      <c r="O818">
-        <v>1</v>
-      </c>
-      <c r="AI818">
-        <v>1</v>
-      </c>
-      <c r="AJ818">
+      <c r="M818">
+        <v>1</v>
+      </c>
+      <c r="AF818">
+        <v>1</v>
+      </c>
+      <c r="AG818">
         <v>1</v>
       </c>
     </row>
@@ -37967,13 +36886,10 @@
       <c r="D819" t="s">
         <v>46</v>
       </c>
-      <c r="W819">
-        <v>1</v>
-      </c>
-      <c r="AA819">
-        <v>1</v>
-      </c>
-      <c r="AH819">
+      <c r="X819">
+        <v>1</v>
+      </c>
+      <c r="AE819">
         <v>1</v>
       </c>
     </row>
@@ -37990,6 +36906,9 @@
       <c r="D820" t="s">
         <v>49</v>
       </c>
+      <c r="AK820">
+        <v>1</v>
+      </c>
       <c r="AN820">
         <v>1</v>
       </c>
@@ -38007,10 +36926,7 @@
       <c r="D821" t="s">
         <v>52</v>
       </c>
-      <c r="N821">
-        <v>1</v>
-      </c>
-      <c r="O821">
+      <c r="M821">
         <v>1</v>
       </c>
     </row>
@@ -38027,7 +36943,7 @@
       <c r="D822" t="s">
         <v>40</v>
       </c>
-      <c r="AH822">
+      <c r="AE822">
         <v>1</v>
       </c>
     </row>
@@ -38047,9 +36963,6 @@
       <c r="E823">
         <v>1</v>
       </c>
-      <c r="F823">
-        <v>1</v>
-      </c>
     </row>
     <row r="824">
       <c r="A824" t="s">
@@ -38065,12 +36978,9 @@
         <v>46</v>
       </c>
       <c r="E824">
-        <v>2</v>
-      </c>
-      <c r="F824">
-        <v>1</v>
-      </c>
-      <c r="K824">
+        <v>1</v>
+      </c>
+      <c r="J824">
         <v>1</v>
       </c>
     </row>
@@ -38090,9 +37000,6 @@
       <c r="W825">
         <v>1</v>
       </c>
-      <c r="Z825">
-        <v>1</v>
-      </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
@@ -38110,9 +37017,6 @@
       <c r="W826">
         <v>1</v>
       </c>
-      <c r="Z826">
-        <v>1</v>
-      </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
@@ -38142,24 +37046,18 @@
         <v>43</v>
       </c>
       <c r="E828">
-        <v>2</v>
-      </c>
-      <c r="F828">
-        <v>1</v>
-      </c>
-      <c r="K828">
-        <v>1</v>
-      </c>
-      <c r="N828">
-        <v>1</v>
-      </c>
-      <c r="O828">
-        <v>1</v>
-      </c>
-      <c r="AI828">
-        <v>1</v>
-      </c>
-      <c r="AJ828">
+        <v>1</v>
+      </c>
+      <c r="J828">
+        <v>1</v>
+      </c>
+      <c r="M828">
+        <v>1</v>
+      </c>
+      <c r="AF828">
+        <v>1</v>
+      </c>
+      <c r="AG828">
         <v>1</v>
       </c>
     </row>
@@ -38191,18 +37089,12 @@
         <v>49</v>
       </c>
       <c r="E830">
-        <v>2</v>
-      </c>
-      <c r="F830">
-        <v>1</v>
-      </c>
-      <c r="K830">
+        <v>1</v>
+      </c>
+      <c r="J830">
         <v>1</v>
       </c>
       <c r="W830">
-        <v>1</v>
-      </c>
-      <c r="Z830">
         <v>1</v>
       </c>
     </row>
@@ -38222,13 +37114,10 @@
       <c r="E831">
         <v>1</v>
       </c>
-      <c r="F831">
-        <v>1</v>
-      </c>
-      <c r="N831">
-        <v>1</v>
-      </c>
-      <c r="O831">
+      <c r="M831">
+        <v>1</v>
+      </c>
+      <c r="AK831">
         <v>1</v>
       </c>
       <c r="AN831">
@@ -38290,10 +37179,7 @@
       <c r="D835" t="s">
         <v>49</v>
       </c>
-      <c r="N835">
-        <v>1</v>
-      </c>
-      <c r="O835">
+      <c r="M835">
         <v>1</v>
       </c>
     </row>
@@ -38310,13 +37196,10 @@
       <c r="D836" t="s">
         <v>52</v>
       </c>
-      <c r="W836">
-        <v>1</v>
-      </c>
-      <c r="AA836">
-        <v>1</v>
-      </c>
-      <c r="AH836">
+      <c r="X836">
+        <v>1</v>
+      </c>
+      <c r="AE836">
         <v>1</v>
       </c>
     </row>
@@ -38333,7 +37216,7 @@
       <c r="D837" t="s">
         <v>40</v>
       </c>
-      <c r="AF837">
+      <c r="AC837">
         <v>1</v>
       </c>
     </row>
@@ -38364,16 +37247,13 @@
       <c r="D839" t="s">
         <v>46</v>
       </c>
-      <c r="N839">
-        <v>1</v>
-      </c>
-      <c r="O839">
-        <v>1</v>
-      </c>
-      <c r="AI839">
-        <v>1</v>
-      </c>
-      <c r="AJ839">
+      <c r="M839">
+        <v>1</v>
+      </c>
+      <c r="AF839">
+        <v>1</v>
+      </c>
+      <c r="AG839">
         <v>1</v>
       </c>
     </row>
@@ -38390,10 +37270,7 @@
       <c r="D840" t="s">
         <v>49</v>
       </c>
-      <c r="W840">
-        <v>1</v>
-      </c>
-      <c r="Y840">
+      <c r="V840">
         <v>1</v>
       </c>
     </row>
@@ -38410,6 +37287,9 @@
       <c r="D841" t="s">
         <v>52</v>
       </c>
+      <c r="AK841">
+        <v>1</v>
+      </c>
       <c r="AN841">
         <v>1</v>
       </c>
@@ -38441,10 +37321,10 @@
       <c r="D843" t="s">
         <v>43</v>
       </c>
-      <c r="AI843">
-        <v>1</v>
-      </c>
-      <c r="AJ843">
+      <c r="AF843">
+        <v>1</v>
+      </c>
+      <c r="AG843">
         <v>1</v>
       </c>
     </row>
@@ -38464,13 +37344,7 @@
       <c r="E844">
         <v>1</v>
       </c>
-      <c r="F844">
-        <v>1</v>
-      </c>
-      <c r="W844">
-        <v>1</v>
-      </c>
-      <c r="X844">
+      <c r="U844">
         <v>1</v>
       </c>
     </row>
@@ -38487,10 +37361,7 @@
       <c r="D845" t="s">
         <v>49</v>
       </c>
-      <c r="N845">
-        <v>1</v>
-      </c>
-      <c r="O845">
+      <c r="M845">
         <v>1</v>
       </c>
     </row>
@@ -38535,16 +37406,13 @@
       <c r="D848" t="s">
         <v>43</v>
       </c>
-      <c r="E848">
-        <v>1</v>
-      </c>
-      <c r="K848">
-        <v>1</v>
-      </c>
-      <c r="AI848">
-        <v>1</v>
-      </c>
-      <c r="AJ848">
+      <c r="J848">
+        <v>1</v>
+      </c>
+      <c r="AF848">
+        <v>1</v>
+      </c>
+      <c r="AG848">
         <v>1</v>
       </c>
     </row>
@@ -38575,10 +37443,10 @@
       <c r="D850" t="s">
         <v>49</v>
       </c>
-      <c r="N850">
-        <v>1</v>
-      </c>
-      <c r="O850">
+      <c r="M850">
+        <v>1</v>
+      </c>
+      <c r="AK850">
         <v>1</v>
       </c>
       <c r="AN850">
@@ -38598,7 +37466,7 @@
       <c r="D851" t="s">
         <v>52</v>
       </c>
-      <c r="AH851">
+      <c r="AE851">
         <v>1</v>
       </c>
     </row>
@@ -38629,10 +37497,10 @@
       <c r="D853" t="s">
         <v>43</v>
       </c>
-      <c r="AI853">
-        <v>1</v>
-      </c>
-      <c r="AJ853">
+      <c r="AF853">
+        <v>1</v>
+      </c>
+      <c r="AG853">
         <v>1</v>
       </c>
     </row>
@@ -38649,6 +37517,9 @@
       <c r="D854" t="s">
         <v>46</v>
       </c>
+      <c r="AK854">
+        <v>1</v>
+      </c>
       <c r="AN854">
         <v>1</v>
       </c>
@@ -38666,25 +37537,19 @@
       <c r="D855" t="s">
         <v>49</v>
       </c>
-      <c r="E855">
-        <v>1</v>
-      </c>
-      <c r="I855">
-        <v>1</v>
-      </c>
-      <c r="N855">
-        <v>2</v>
-      </c>
-      <c r="O855">
-        <v>1</v>
-      </c>
-      <c r="U855">
-        <v>1</v>
-      </c>
-      <c r="AI855">
-        <v>1</v>
-      </c>
-      <c r="AJ855">
+      <c r="H855">
+        <v>1</v>
+      </c>
+      <c r="M855">
+        <v>1</v>
+      </c>
+      <c r="S855">
+        <v>1</v>
+      </c>
+      <c r="AF855">
+        <v>1</v>
+      </c>
+      <c r="AG855">
         <v>1</v>
       </c>
     </row>
@@ -38743,7 +37608,10 @@
       <c r="D859" t="s">
         <v>46</v>
       </c>
-      <c r="AE859">
+      <c r="AB859">
+        <v>1</v>
+      </c>
+      <c r="AJ859">
         <v>1</v>
       </c>
       <c r="AM859">
@@ -38763,16 +37631,10 @@
       <c r="D860" t="s">
         <v>49</v>
       </c>
-      <c r="E860">
-        <v>1</v>
-      </c>
-      <c r="H860">
-        <v>1</v>
-      </c>
-      <c r="N860">
-        <v>1</v>
-      </c>
-      <c r="O860">
+      <c r="G860">
+        <v>1</v>
+      </c>
+      <c r="M860">
         <v>1</v>
       </c>
     </row>
@@ -38790,9 +37652,6 @@
         <v>52</v>
       </c>
       <c r="E861">
-        <v>1</v>
-      </c>
-      <c r="F861">
         <v>1</v>
       </c>
     </row>

--- a/docs/LoL/LolSpells.xlsx
+++ b/docs/LoL/LolSpells.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Spells" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ValueOnly" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spells!$A$1:$AG$861</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spells!$A$1:$AK$861</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spells!$A$1:$AK$861</definedName>
   </definedNames>
   <calcPr/>
@@ -15399,6 +15399,9 @@
       <c r="M496">
         <v>1</v>
       </c>
+      <c r="AA496">
+        <v>1</v>
+      </c>
       <c r="AE496">
         <v>1</v>
       </c>
@@ -15593,6 +15596,9 @@
       <c r="D506" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AA506">
+        <v>1</v>
+      </c>
       <c r="AC506">
         <v>1</v>
       </c>
@@ -16069,6 +16075,9 @@
       <c r="X531">
         <v>1</v>
       </c>
+      <c r="AA531">
+        <v>1</v>
+      </c>
       <c r="AE531">
         <v>1</v>
       </c>
@@ -16694,6 +16703,9 @@
       <c r="D566" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AA566">
+        <v>1</v>
+      </c>
       <c r="AE566">
         <v>1</v>
       </c>
@@ -17179,6 +17191,9 @@
       <c r="D593" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AA593">
+        <v>1</v>
+      </c>
     </row>
     <row r="594" ht="14.25">
       <c r="A594" s="1" t="s">
@@ -17233,6 +17248,9 @@
       <c r="M596">
         <v>1</v>
       </c>
+      <c r="AA596">
+        <v>1</v>
+      </c>
       <c r="AE596">
         <v>1</v>
       </c>
@@ -17318,6 +17336,9 @@
       <c r="D601" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AA601">
+        <v>1</v>
+      </c>
     </row>
     <row r="602" ht="14.25">
       <c r="A602" s="1" t="s">
@@ -18332,6 +18353,9 @@
       <c r="D659" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="AA659">
+        <v>1</v>
+      </c>
     </row>
     <row r="660" ht="14.25">
       <c r="A660" s="1" t="s">
@@ -19134,6 +19158,9 @@
       <c r="D706" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AA706">
+        <v>1</v>
+      </c>
     </row>
     <row r="707" ht="14.25">
       <c r="A707" s="1" t="s">
@@ -19914,6 +19941,9 @@
       <c r="D752" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="AA752">
+        <v>1</v>
+      </c>
       <c r="AB752">
         <v>1</v>
       </c>
@@ -20000,6 +20030,9 @@
       <c r="M756">
         <v>1</v>
       </c>
+      <c r="AA756">
+        <v>1</v>
+      </c>
       <c r="AB756">
         <v>1</v>
       </c>
@@ -20772,6 +20805,9 @@
       <c r="E801">
         <v>1</v>
       </c>
+      <c r="AA801">
+        <v>1</v>
+      </c>
     </row>
     <row r="802" ht="14.25">
       <c r="A802" s="1" t="s">
@@ -20866,6 +20902,9 @@
       <c r="J806">
         <v>1</v>
       </c>
+      <c r="AA806">
+        <v>1</v>
+      </c>
     </row>
     <row r="807" ht="14.25">
       <c r="A807" s="1" t="s">
@@ -21354,6 +21393,9 @@
       <c r="D834" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="AA834">
+        <v>1</v>
+      </c>
     </row>
     <row r="835" ht="14.25">
       <c r="A835" s="1" t="s">
@@ -21388,6 +21430,9 @@
       <c r="X836">
         <v>1</v>
       </c>
+      <c r="AA836">
+        <v>1</v>
+      </c>
       <c r="AE836">
         <v>1</v>
       </c>
@@ -21745,6 +21790,9 @@
       </c>
       <c r="D856" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="AA856">
+        <v>1</v>
       </c>
     </row>
     <row r="857" ht="14.25">
@@ -21844,7 +21892,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{2D3AF7C2-61F6-46F2-88EA-0E4DD36D8AB7}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{A11194EB-D37D-44C8-BE7E-2B6451B75385}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -31035,6 +31083,9 @@
       <c r="M496">
         <v>1</v>
       </c>
+      <c r="AA496">
+        <v>1</v>
+      </c>
       <c r="AE496">
         <v>1</v>
       </c>
@@ -31235,6 +31286,9 @@
       <c r="D506" t="s">
         <v>52</v>
       </c>
+      <c r="AA506">
+        <v>1</v>
+      </c>
       <c r="AC506">
         <v>1</v>
       </c>
@@ -31726,6 +31780,9 @@
       <c r="X531">
         <v>1</v>
       </c>
+      <c r="AA531">
+        <v>1</v>
+      </c>
       <c r="AE531">
         <v>1</v>
       </c>
@@ -32375,6 +32432,9 @@
       <c r="D566" t="s">
         <v>52</v>
       </c>
+      <c r="AA566">
+        <v>1</v>
+      </c>
       <c r="AE566">
         <v>1</v>
       </c>
@@ -32876,6 +32936,9 @@
       <c r="D593" t="s">
         <v>43</v>
       </c>
+      <c r="AA593">
+        <v>1</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
@@ -32930,6 +32993,9 @@
       <c r="M596">
         <v>1</v>
       </c>
+      <c r="AA596">
+        <v>1</v>
+      </c>
       <c r="AE596">
         <v>1</v>
       </c>
@@ -33015,6 +33081,9 @@
       <c r="D601" t="s">
         <v>52</v>
       </c>
+      <c r="AA601">
+        <v>1</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="s">
@@ -34064,6 +34133,9 @@
       <c r="D659" t="s">
         <v>46</v>
       </c>
+      <c r="AA659">
+        <v>1</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="s">
@@ -34887,6 +34959,9 @@
       <c r="D706" t="s">
         <v>52</v>
       </c>
+      <c r="AA706">
+        <v>1</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="s">
@@ -35678,6 +35753,9 @@
       <c r="D752" t="s">
         <v>40</v>
       </c>
+      <c r="AA752">
+        <v>1</v>
+      </c>
       <c r="AB752">
         <v>1</v>
       </c>
@@ -35770,6 +35848,9 @@
       <c r="M756">
         <v>1</v>
       </c>
+      <c r="AA756">
+        <v>1</v>
+      </c>
       <c r="AB756">
         <v>1</v>
       </c>
@@ -36568,6 +36649,9 @@
       <c r="E801">
         <v>1</v>
       </c>
+      <c r="AA801">
+        <v>1</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
@@ -36665,6 +36749,9 @@
       <c r="J806">
         <v>1</v>
       </c>
+      <c r="AA806">
+        <v>1</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
@@ -37165,6 +37252,9 @@
       <c r="D834" t="s">
         <v>46</v>
       </c>
+      <c r="AA834">
+        <v>1</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
@@ -37199,6 +37289,9 @@
       <c r="X836">
         <v>1</v>
       </c>
+      <c r="AA836">
+        <v>1</v>
+      </c>
       <c r="AE836">
         <v>1</v>
       </c>
@@ -37565,6 +37658,9 @@
       </c>
       <c r="D856" t="s">
         <v>52</v>
+      </c>
+      <c r="AA856">
+        <v>1</v>
       </c>
     </row>
     <row r="857">

--- a/docs/LoL/LolSpells.xlsx
+++ b/docs/LoL/LolSpells.xlsx
@@ -18353,6 +18353,9 @@
       <c r="D659" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E659">
+        <v>1</v>
+      </c>
       <c r="AA659">
         <v>1</v>
       </c>
@@ -18369,9 +18372,6 @@
       </c>
       <c r="D660" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E660">
-        <v>1</v>
       </c>
     </row>
     <row r="661" ht="14.25">
@@ -21892,7 +21892,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{A11194EB-D37D-44C8-BE7E-2B6451B75385}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{200A5F15-C610-4BCE-93E0-5543B1504791}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -34133,6 +34133,9 @@
       <c r="D659" t="s">
         <v>46</v>
       </c>
+      <c r="E659">
+        <v>1</v>
+      </c>
       <c r="AA659">
         <v>1</v>
       </c>
@@ -34149,9 +34152,6 @@
       </c>
       <c r="D660" t="s">
         <v>49</v>
-      </c>
-      <c r="E660">
-        <v>1</v>
       </c>
     </row>
     <row r="661">

--- a/docs/LoL/LolSpells.xlsx
+++ b/docs/LoL/LolSpells.xlsx
@@ -21892,7 +21892,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{200A5F15-C610-4BCE-93E0-5543B1504791}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{BFB7A082-F5FA-4991-8CF6-52143E9AFB40}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>

--- a/docs/LoL/LolSpells.xlsx
+++ b/docs/LoL/LolSpells.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1925" uniqueCount="1925">
   <si>
     <t>Champions</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Sleep</t>
   </si>
   <si>
-    <t>Statis</t>
+    <t>Stasis</t>
   </si>
   <si>
     <t>Stun</t>
@@ -5793,6 +5793,9 @@
   </si>
   <si>
     <t>Stranglethorns</t>
+  </si>
+  <si>
+    <t>PointAndClick</t>
   </si>
 </sst>
 </file>
@@ -5865,7 +5868,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -5876,6 +5879,9 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6353,7 +6359,7 @@
   <cols>
     <col bestFit="1" min="1" max="1" width="14.8515625"/>
     <col customWidth="1" min="2" max="2" width="30.8515625"/>
-    <col bestFit="1" min="3" max="3" width="33.7109375"/>
+    <col customWidth="1" min="3" max="3" width="9.140625"/>
     <col bestFit="1" min="4" max="4" width="17.8515625"/>
     <col customWidth="1" min="5" max="5" outlineLevel="1" width="10.57421875"/>
     <col customWidth="1" min="6" max="6" outlineLevel="1" width="40.00390625"/>
@@ -6410,7 +6416,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -6422,80 +6428,83 @@
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AB1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AC1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AD1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AE1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="8" t="s">
+      <c r="AF1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="8" t="s">
+      <c r="AG1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="8" t="s">
+      <c r="AH1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="8" t="s">
+      <c r="AI1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="8" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="8" t="s">
+      <c r="AK1" s="9" t="s">
         <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -6511,11 +6520,11 @@
       <c r="D2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -6579,9 +6588,9 @@
       <c r="W5">
         <v>1</v>
       </c>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -6687,9 +6696,9 @@
       <c r="W11">
         <v>1</v>
       </c>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
       <c r="AB11">
         <v>1</v>
       </c>
@@ -6764,13 +6773,13 @@
       <c r="U15">
         <v>1</v>
       </c>
-      <c r="V15" s="9">
-        <v>1</v>
-      </c>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
+      <c r="V15" s="10">
+        <v>1</v>
+      </c>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
       <c r="AF15">
         <v>1</v>
       </c>
@@ -6797,9 +6806,12 @@
       <c r="X16">
         <v>1</v>
       </c>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
       <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
         <v>1</v>
       </c>
     </row>
@@ -6896,6 +6908,9 @@
       <c r="AG21">
         <v>1</v>
       </c>
+      <c r="AL21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="1" t="s">
@@ -6953,8 +6968,11 @@
       <c r="X24">
         <v>1</v>
       </c>
-      <c r="Y24" s="9"/>
-      <c r="Z24" s="9"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+      <c r="AL24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="1" t="s">
@@ -7108,11 +7126,11 @@
       <c r="U33">
         <v>1</v>
       </c>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
       <c r="AF33">
         <v>1</v>
       </c>
@@ -7226,6 +7244,9 @@
       <c r="D40" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL40">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="1" t="s">
@@ -7274,6 +7295,9 @@
       <c r="D43" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" ht="14.25">
       <c r="A44" s="1" t="s">
@@ -7674,13 +7698,13 @@
       <c r="U66">
         <v>1</v>
       </c>
-      <c r="V66" s="9">
-        <v>1</v>
-      </c>
-      <c r="W66" s="9"/>
-      <c r="X66" s="9"/>
-      <c r="Y66" s="9"/>
-      <c r="Z66" s="9"/>
+      <c r="V66" s="10">
+        <v>1</v>
+      </c>
+      <c r="W66" s="10"/>
+      <c r="X66" s="10"/>
+      <c r="Y66" s="10"/>
+      <c r="Z66" s="10"/>
       <c r="AK66">
         <v>1</v>
       </c>
@@ -7749,8 +7773,8 @@
       <c r="X70">
         <v>1</v>
       </c>
-      <c r="Y70" s="9"/>
-      <c r="Z70" s="9"/>
+      <c r="Y70" s="10"/>
+      <c r="Z70" s="10"/>
     </row>
     <row r="71" ht="14.25">
       <c r="A71" s="1" t="s">
@@ -7851,11 +7875,11 @@
       <c r="U75">
         <v>1</v>
       </c>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
+      <c r="V75" s="10"/>
+      <c r="W75" s="10"/>
+      <c r="X75" s="10"/>
+      <c r="Y75" s="10"/>
+      <c r="Z75" s="10"/>
     </row>
     <row r="76" ht="14.25">
       <c r="A76" s="1" t="s">
@@ -7964,8 +7988,8 @@
       <c r="X81">
         <v>1</v>
       </c>
-      <c r="Y81" s="9"/>
-      <c r="Z81" s="9"/>
+      <c r="Y81" s="10"/>
+      <c r="Z81" s="10"/>
       <c r="AB81">
         <v>1</v>
       </c>
@@ -8128,6 +8152,9 @@
       <c r="D90" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" ht="14.25">
       <c r="A91" s="1" t="s">
@@ -8145,6 +8172,9 @@
       <c r="M91">
         <v>1</v>
       </c>
+      <c r="AL91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" ht="14.25">
       <c r="A92" s="1" t="s">
@@ -8202,8 +8232,11 @@
       <c r="X94">
         <v>1</v>
       </c>
-      <c r="Y94" s="9"/>
-      <c r="Z94" s="9"/>
+      <c r="Y94" s="10"/>
+      <c r="Z94" s="10"/>
+      <c r="AL94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" ht="14.25">
       <c r="A95" s="1" t="s">
@@ -8275,7 +8308,10 @@
       <c r="Y98">
         <v>1</v>
       </c>
-      <c r="Z98" s="9"/>
+      <c r="Z98" s="10"/>
+      <c r="AL98">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" ht="14.25">
       <c r="A99" s="1" t="s">
@@ -8293,9 +8329,9 @@
       <c r="W99">
         <v>1</v>
       </c>
-      <c r="X99" s="9"/>
-      <c r="Y99" s="9"/>
-      <c r="Z99" s="9"/>
+      <c r="X99" s="10"/>
+      <c r="Y99" s="10"/>
+      <c r="Z99" s="10"/>
       <c r="AD99">
         <v>1</v>
       </c>
@@ -8342,11 +8378,11 @@
       <c r="U101">
         <v>1</v>
       </c>
-      <c r="V101" s="9"/>
-      <c r="W101" s="9"/>
-      <c r="X101" s="9"/>
-      <c r="Y101" s="9"/>
-      <c r="Z101" s="9"/>
+      <c r="V101" s="10"/>
+      <c r="W101" s="10"/>
+      <c r="X101" s="10"/>
+      <c r="Y101" s="10"/>
+      <c r="Z101" s="10"/>
       <c r="AF101">
         <v>1</v>
       </c>
@@ -8441,6 +8477,9 @@
       <c r="AF106">
         <v>1</v>
       </c>
+      <c r="AL106">
+        <v>1</v>
+      </c>
     </row>
     <row r="107" ht="14.25">
       <c r="A107" s="1" t="s">
@@ -8512,9 +8551,9 @@
       <c r="V110">
         <v>1</v>
       </c>
-      <c r="X110" s="9"/>
-      <c r="Y110" s="9"/>
-      <c r="Z110" s="9">
+      <c r="X110" s="10"/>
+      <c r="Y110" s="10"/>
+      <c r="Z110" s="10">
         <v>1</v>
       </c>
       <c r="AF110">
@@ -8540,8 +8579,11 @@
       <c r="Y111">
         <v>1</v>
       </c>
-      <c r="Z111" s="9"/>
+      <c r="Z111" s="10"/>
       <c r="AE111">
+        <v>1</v>
+      </c>
+      <c r="AL111">
         <v>1</v>
       </c>
     </row>
@@ -8612,6 +8654,9 @@
       <c r="D115" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL115">
+        <v>1</v>
+      </c>
     </row>
     <row r="116" ht="14.25">
       <c r="A116" s="1" t="s">
@@ -8714,6 +8759,9 @@
       <c r="D121" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AL121">
+        <v>1</v>
+      </c>
     </row>
     <row r="122" ht="14.25">
       <c r="A122" s="1" t="s">
@@ -8759,9 +8807,9 @@
       <c r="W124">
         <v>1</v>
       </c>
-      <c r="X124" s="9"/>
-      <c r="Y124" s="9"/>
-      <c r="Z124" s="9"/>
+      <c r="X124" s="10"/>
+      <c r="Y124" s="10"/>
+      <c r="Z124" s="10"/>
     </row>
     <row r="125" ht="14.25">
       <c r="A125" s="1" t="s">
@@ -8878,6 +8926,9 @@
       <c r="D131" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AL131">
+        <v>1</v>
+      </c>
     </row>
     <row r="132" ht="14.25">
       <c r="A132" s="1" t="s">
@@ -8937,8 +8988,11 @@
       <c r="X135">
         <v>1</v>
       </c>
-      <c r="Y135" s="9"/>
-      <c r="Z135" s="9"/>
+      <c r="Y135" s="10"/>
+      <c r="Z135" s="10"/>
+      <c r="AL135">
+        <v>1</v>
+      </c>
     </row>
     <row r="136" ht="14.25">
       <c r="A136" s="1" t="s">
@@ -9226,11 +9280,11 @@
       <c r="U151">
         <v>1</v>
       </c>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
+      <c r="V151" s="10"/>
+      <c r="W151" s="10"/>
+      <c r="X151" s="10"/>
+      <c r="Y151" s="10"/>
+      <c r="Z151" s="10"/>
       <c r="AE151">
         <v>1</v>
       </c>
@@ -9268,7 +9322,10 @@
       <c r="Y153">
         <v>1</v>
       </c>
-      <c r="Z153" s="9"/>
+      <c r="Z153" s="10"/>
+      <c r="AL153">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" ht="14.25">
       <c r="A154" s="1" t="s">
@@ -9318,6 +9375,9 @@
       <c r="AG155">
         <v>1</v>
       </c>
+      <c r="AL155">
+        <v>1</v>
+      </c>
     </row>
     <row r="156" ht="14.25">
       <c r="A156" s="1" t="s">
@@ -9389,6 +9449,9 @@
       <c r="M159">
         <v>1</v>
       </c>
+      <c r="AL159">
+        <v>1</v>
+      </c>
     </row>
     <row r="160" ht="14.25">
       <c r="A160" s="1" t="s">
@@ -9406,8 +9469,11 @@
       <c r="Y160">
         <v>1</v>
       </c>
-      <c r="Z160" s="9"/>
+      <c r="Z160" s="10"/>
       <c r="AK160">
+        <v>1</v>
+      </c>
+      <c r="AL160">
         <v>1</v>
       </c>
     </row>
@@ -9546,6 +9612,9 @@
       <c r="M168">
         <v>1</v>
       </c>
+      <c r="AL168">
+        <v>1</v>
+      </c>
     </row>
     <row r="169" ht="14.25">
       <c r="A169" s="1" t="s">
@@ -9628,9 +9697,9 @@
       <c r="W173">
         <v>1</v>
       </c>
-      <c r="X173" s="9"/>
-      <c r="Y173" s="9"/>
-      <c r="Z173" s="9"/>
+      <c r="X173" s="10"/>
+      <c r="Y173" s="10"/>
+      <c r="Z173" s="10"/>
     </row>
     <row r="174" ht="14.25">
       <c r="A174" s="1" t="s">
@@ -9694,6 +9763,9 @@
       <c r="AK176">
         <v>1</v>
       </c>
+      <c r="AL176">
+        <v>1</v>
+      </c>
     </row>
     <row r="177" ht="14.25">
       <c r="A177" s="1" t="s">
@@ -9725,8 +9797,11 @@
       <c r="X178">
         <v>1</v>
       </c>
-      <c r="Y178" s="9"/>
-      <c r="Z178" s="9"/>
+      <c r="Y178" s="10"/>
+      <c r="Z178" s="10"/>
+      <c r="AL178">
+        <v>1</v>
+      </c>
     </row>
     <row r="179" ht="14.25">
       <c r="A179" s="1" t="s">
@@ -9761,9 +9836,9 @@
       <c r="W180">
         <v>1</v>
       </c>
-      <c r="X180" s="9"/>
-      <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
+      <c r="X180" s="10"/>
+      <c r="Y180" s="10"/>
+      <c r="Z180" s="10"/>
       <c r="AE180">
         <v>1</v>
       </c>
@@ -9881,9 +9956,12 @@
       <c r="X186">
         <v>1</v>
       </c>
-      <c r="Y186" s="9"/>
-      <c r="Z186" s="9"/>
+      <c r="Y186" s="10"/>
+      <c r="Z186" s="10"/>
       <c r="AE186">
+        <v>1</v>
+      </c>
+      <c r="AL186">
         <v>1</v>
       </c>
     </row>
@@ -9917,6 +9995,9 @@
       <c r="D188" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL188">
+        <v>1</v>
+      </c>
     </row>
     <row r="189" ht="14.25">
       <c r="A189" s="1" t="s">
@@ -10044,6 +10125,9 @@
       <c r="AD196">
         <v>1</v>
       </c>
+      <c r="AL196">
+        <v>1</v>
+      </c>
     </row>
     <row r="197" ht="14.25">
       <c r="A197" s="1" t="s">
@@ -10209,9 +10293,9 @@
       <c r="W205">
         <v>1</v>
       </c>
-      <c r="X205" s="9"/>
-      <c r="Y205" s="9"/>
-      <c r="Z205" s="9"/>
+      <c r="X205" s="10"/>
+      <c r="Y205" s="10"/>
+      <c r="Z205" s="10"/>
       <c r="AF205">
         <v>1</v>
       </c>
@@ -10470,7 +10554,7 @@
       <c r="Y220">
         <v>1</v>
       </c>
-      <c r="Z220" s="9"/>
+      <c r="Z220" s="10"/>
     </row>
     <row r="221" ht="14.25">
       <c r="A221" s="1" t="s">
@@ -10739,7 +10823,10 @@
       <c r="Y234">
         <v>1</v>
       </c>
-      <c r="Z234" s="9"/>
+      <c r="Z234" s="10"/>
+      <c r="AL234">
+        <v>1</v>
+      </c>
     </row>
     <row r="235" ht="14.25">
       <c r="A235" s="1" t="s">
@@ -10808,8 +10895,11 @@
       <c r="X238">
         <v>1</v>
       </c>
-      <c r="Y238" s="9"/>
-      <c r="Z238" s="9"/>
+      <c r="Y238" s="10"/>
+      <c r="Z238" s="10"/>
+      <c r="AL238">
+        <v>1</v>
+      </c>
     </row>
     <row r="239" ht="14.25">
       <c r="A239" s="1" t="s">
@@ -10895,11 +10985,11 @@
       <c r="U243">
         <v>1</v>
       </c>
-      <c r="V243" s="9"/>
-      <c r="W243" s="9"/>
-      <c r="X243" s="9"/>
-      <c r="Y243" s="9"/>
-      <c r="Z243" s="9"/>
+      <c r="V243" s="10"/>
+      <c r="W243" s="10"/>
+      <c r="X243" s="10"/>
+      <c r="Y243" s="10"/>
+      <c r="Z243" s="10"/>
       <c r="AF243">
         <v>1</v>
       </c>
@@ -10940,6 +11030,9 @@
       <c r="M245">
         <v>1</v>
       </c>
+      <c r="AL245">
+        <v>1</v>
+      </c>
     </row>
     <row r="246" ht="14.25">
       <c r="A246" s="1" t="s">
@@ -11011,6 +11104,9 @@
       <c r="AK249">
         <v>1</v>
       </c>
+      <c r="AL249">
+        <v>1</v>
+      </c>
     </row>
     <row r="250" ht="14.25">
       <c r="A250" s="1" t="s">
@@ -11025,6 +11121,9 @@
       <c r="D250" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL250">
+        <v>1</v>
+      </c>
     </row>
     <row r="251" ht="14.25">
       <c r="A251" s="1" t="s">
@@ -11076,11 +11175,11 @@
       <c r="U253">
         <v>1</v>
       </c>
-      <c r="V253" s="9"/>
-      <c r="W253" s="9"/>
-      <c r="X253" s="9"/>
-      <c r="Y253" s="9"/>
-      <c r="Z253" s="9"/>
+      <c r="V253" s="10"/>
+      <c r="W253" s="10"/>
+      <c r="X253" s="10"/>
+      <c r="Y253" s="10"/>
+      <c r="Z253" s="10"/>
     </row>
     <row r="254" ht="14.25">
       <c r="A254" s="1" t="s">
@@ -11132,6 +11231,9 @@
       <c r="X256">
         <v>1</v>
       </c>
+      <c r="AL256">
+        <v>1</v>
+      </c>
     </row>
     <row r="257" ht="14.25">
       <c r="A257" s="1" t="s">
@@ -11163,6 +11265,9 @@
       <c r="X258">
         <v>1</v>
       </c>
+      <c r="AL258">
+        <v>1</v>
+      </c>
     </row>
     <row r="259" ht="14.25">
       <c r="A259" s="1" t="s">
@@ -11254,6 +11359,9 @@
       <c r="AG263">
         <v>1</v>
       </c>
+      <c r="AL263">
+        <v>1</v>
+      </c>
     </row>
     <row r="264" ht="14.25">
       <c r="A264" s="1" t="s">
@@ -11291,6 +11399,9 @@
       <c r="AK265">
         <v>1</v>
       </c>
+      <c r="AL265">
+        <v>1</v>
+      </c>
     </row>
     <row r="266" ht="14.25">
       <c r="A266" s="1" t="s">
@@ -11342,6 +11453,9 @@
       <c r="D268" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL268">
+        <v>1</v>
+      </c>
     </row>
     <row r="269" ht="14.25">
       <c r="A269" s="1" t="s">
@@ -11602,6 +11716,9 @@
       <c r="AE281">
         <v>1</v>
       </c>
+      <c r="AL281">
+        <v>1</v>
+      </c>
     </row>
     <row r="282" ht="14.25">
       <c r="A282" s="1" t="s">
@@ -11775,13 +11892,13 @@
       <c r="U291">
         <v>1</v>
       </c>
-      <c r="V291" s="9"/>
-      <c r="W291" s="9">
-        <v>1</v>
-      </c>
-      <c r="X291" s="9"/>
-      <c r="Y291" s="9"/>
-      <c r="Z291" s="9"/>
+      <c r="V291" s="10"/>
+      <c r="W291" s="10">
+        <v>1</v>
+      </c>
+      <c r="X291" s="10"/>
+      <c r="Y291" s="10"/>
+      <c r="Z291" s="10"/>
       <c r="AE291">
         <v>1</v>
       </c>
@@ -11839,6 +11956,9 @@
       <c r="G294">
         <v>1</v>
       </c>
+      <c r="AL294">
+        <v>1</v>
+      </c>
     </row>
     <row r="295" ht="14.25">
       <c r="A295" s="1" t="s">
@@ -11977,6 +12097,9 @@
       <c r="D303" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL303">
+        <v>1</v>
+      </c>
     </row>
     <row r="304" ht="14.25">
       <c r="A304" s="1" t="s">
@@ -12056,6 +12179,9 @@
       <c r="D308" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL308">
+        <v>1</v>
+      </c>
     </row>
     <row r="309" ht="14.25">
       <c r="A309" s="1" t="s">
@@ -12090,6 +12216,9 @@
       <c r="AA310">
         <v>1</v>
       </c>
+      <c r="AL310">
+        <v>1</v>
+      </c>
     </row>
     <row r="311" ht="14.25">
       <c r="A311" s="1" t="s">
@@ -12161,6 +12290,9 @@
       <c r="AK314">
         <v>1</v>
       </c>
+      <c r="AL314">
+        <v>1</v>
+      </c>
     </row>
     <row r="315" ht="14.25">
       <c r="A315" s="1" t="s">
@@ -12195,6 +12327,9 @@
       <c r="AE316">
         <v>1</v>
       </c>
+      <c r="AL316">
+        <v>1</v>
+      </c>
     </row>
     <row r="317" ht="14.25">
       <c r="A317" s="1" t="s">
@@ -12226,9 +12361,9 @@
       <c r="W318">
         <v>1</v>
       </c>
-      <c r="X318" s="9"/>
-      <c r="Y318" s="9"/>
-      <c r="Z318" s="9"/>
+      <c r="X318" s="10"/>
+      <c r="Y318" s="10"/>
+      <c r="Z318" s="10"/>
     </row>
     <row r="319" ht="14.25">
       <c r="A319" s="1" t="s">
@@ -12286,6 +12421,9 @@
       <c r="AE321">
         <v>1</v>
       </c>
+      <c r="AL321">
+        <v>1</v>
+      </c>
     </row>
     <row r="322" ht="14.25">
       <c r="A322" s="1" t="s">
@@ -12399,6 +12537,9 @@
       <c r="D328" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL328">
+        <v>1</v>
+      </c>
     </row>
     <row r="329" ht="14.25">
       <c r="A329" s="1" t="s">
@@ -12527,6 +12668,9 @@
       <c r="AD335">
         <v>1</v>
       </c>
+      <c r="AL335">
+        <v>1</v>
+      </c>
     </row>
     <row r="336" ht="14.25">
       <c r="A336" s="1" t="s">
@@ -12624,11 +12768,11 @@
       <c r="U340">
         <v>1</v>
       </c>
-      <c r="V340" s="9"/>
-      <c r="W340" s="9"/>
-      <c r="X340" s="9"/>
-      <c r="Y340" s="9"/>
-      <c r="Z340" s="9"/>
+      <c r="V340" s="10"/>
+      <c r="W340" s="10"/>
+      <c r="X340" s="10"/>
+      <c r="Y340" s="10"/>
+      <c r="Z340" s="10"/>
       <c r="AK340">
         <v>1</v>
       </c>
@@ -12652,11 +12796,11 @@
       <c r="U341">
         <v>1</v>
       </c>
-      <c r="V341" s="9"/>
-      <c r="W341" s="9"/>
-      <c r="X341" s="9"/>
-      <c r="Y341" s="9"/>
-      <c r="Z341" s="9"/>
+      <c r="V341" s="10"/>
+      <c r="W341" s="10"/>
+      <c r="X341" s="10"/>
+      <c r="Y341" s="10"/>
+      <c r="Z341" s="10"/>
       <c r="AF341">
         <v>1</v>
       </c>
@@ -12776,6 +12920,9 @@
       <c r="D348" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL348">
+        <v>1</v>
+      </c>
     </row>
     <row r="349" ht="14.25">
       <c r="A349" s="1" t="s">
@@ -12854,6 +13001,9 @@
       <c r="AG351">
         <v>1</v>
       </c>
+      <c r="AL351">
+        <v>1</v>
+      </c>
     </row>
     <row r="352" ht="14.25">
       <c r="A352" s="1" t="s">
@@ -12885,11 +13035,11 @@
       <c r="U353">
         <v>1</v>
       </c>
-      <c r="V353" s="9"/>
-      <c r="W353" s="9"/>
-      <c r="X353" s="9"/>
-      <c r="Y353" s="9"/>
-      <c r="Z353" s="9"/>
+      <c r="V353" s="10"/>
+      <c r="W353" s="10"/>
+      <c r="X353" s="10"/>
+      <c r="Y353" s="10"/>
+      <c r="Z353" s="10"/>
       <c r="AD353">
         <v>1</v>
       </c>
@@ -12916,6 +13066,9 @@
       <c r="X354">
         <v>1</v>
       </c>
+      <c r="AL354">
+        <v>1</v>
+      </c>
     </row>
     <row r="355" ht="14.25">
       <c r="A355" s="1" t="s">
@@ -12953,6 +13106,9 @@
       <c r="G356">
         <v>1</v>
       </c>
+      <c r="AL356">
+        <v>1</v>
+      </c>
     </row>
     <row r="357" ht="14.25">
       <c r="A357" s="1" t="s">
@@ -13018,11 +13174,11 @@
       <c r="U360">
         <v>1</v>
       </c>
-      <c r="V360" s="9"/>
-      <c r="W360" s="9"/>
-      <c r="X360" s="9"/>
-      <c r="Y360" s="9"/>
-      <c r="Z360" s="9"/>
+      <c r="V360" s="10"/>
+      <c r="W360" s="10"/>
+      <c r="X360" s="10"/>
+      <c r="Y360" s="10"/>
+      <c r="Z360" s="10"/>
     </row>
     <row r="361" ht="14.25">
       <c r="A361" s="1" t="s">
@@ -13231,6 +13387,9 @@
       <c r="AE371">
         <v>1</v>
       </c>
+      <c r="AL371">
+        <v>1</v>
+      </c>
     </row>
     <row r="372" ht="14.25">
       <c r="A372" s="1" t="s">
@@ -13259,6 +13418,9 @@
       <c r="D373" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL373">
+        <v>1</v>
+      </c>
     </row>
     <row r="374" ht="14.25">
       <c r="A374" s="1" t="s">
@@ -13299,9 +13461,9 @@
       <c r="W375">
         <v>1</v>
       </c>
-      <c r="X375" s="9"/>
-      <c r="Y375" s="9"/>
-      <c r="Z375" s="9"/>
+      <c r="X375" s="10"/>
+      <c r="Y375" s="10"/>
+      <c r="Z375" s="10"/>
     </row>
     <row r="376" ht="14.25">
       <c r="A376" s="1" t="s">
@@ -13373,6 +13535,9 @@
       <c r="AK379">
         <v>1</v>
       </c>
+      <c r="AL379">
+        <v>1</v>
+      </c>
     </row>
     <row r="380" ht="14.25">
       <c r="A380" s="1" t="s">
@@ -13387,6 +13552,9 @@
       <c r="D380" s="1" t="s">
         <v>869</v>
       </c>
+      <c r="AL380">
+        <v>1</v>
+      </c>
     </row>
     <row r="381" ht="14.25">
       <c r="A381" s="1" t="s">
@@ -13407,6 +13575,9 @@
       <c r="M381">
         <v>1</v>
       </c>
+      <c r="AL381">
+        <v>1</v>
+      </c>
     </row>
     <row r="382" ht="14.25">
       <c r="A382" s="1" t="s">
@@ -13523,6 +13694,9 @@
       <c r="AK388">
         <v>1</v>
       </c>
+      <c r="AL388">
+        <v>1</v>
+      </c>
     </row>
     <row r="389" ht="14.25">
       <c r="A389" s="1" t="s">
@@ -13633,6 +13807,9 @@
       <c r="D395" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL395">
+        <v>1</v>
+      </c>
     </row>
     <row r="396" ht="14.25">
       <c r="A396" s="1" t="s">
@@ -13650,6 +13827,9 @@
       <c r="K396">
         <v>1</v>
       </c>
+      <c r="AL396">
+        <v>1</v>
+      </c>
     </row>
     <row r="397" ht="14.25">
       <c r="A397" s="1" t="s">
@@ -13707,6 +13887,9 @@
       <c r="AE399">
         <v>1</v>
       </c>
+      <c r="AL399">
+        <v>1</v>
+      </c>
     </row>
     <row r="400" ht="14.25">
       <c r="A400" s="1" t="s">
@@ -13778,6 +13961,9 @@
       <c r="AE403">
         <v>1</v>
       </c>
+      <c r="AL403">
+        <v>1</v>
+      </c>
     </row>
     <row r="404" ht="14.25">
       <c r="A404" s="1" t="s">
@@ -14012,6 +14198,9 @@
       <c r="AK415">
         <v>1</v>
       </c>
+      <c r="AL415">
+        <v>1</v>
+      </c>
     </row>
     <row r="416" ht="14.25">
       <c r="A416" s="1" t="s">
@@ -14054,6 +14243,9 @@
       <c r="D418" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL418">
+        <v>1</v>
+      </c>
     </row>
     <row r="419" ht="14.25">
       <c r="A419" s="1" t="s">
@@ -14181,6 +14373,9 @@
       <c r="M426">
         <v>1</v>
       </c>
+      <c r="AL426">
+        <v>1</v>
+      </c>
     </row>
     <row r="427" ht="14.25">
       <c r="A427" s="1" t="s">
@@ -14246,6 +14441,9 @@
       <c r="D430" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL430">
+        <v>1</v>
+      </c>
     </row>
     <row r="431" ht="14.25">
       <c r="A431" s="1" t="s">
@@ -14357,6 +14555,9 @@
       <c r="AB436">
         <v>1</v>
       </c>
+      <c r="AL436">
+        <v>1</v>
+      </c>
     </row>
     <row r="437" ht="14.25">
       <c r="A437" s="1" t="s">
@@ -14408,6 +14609,9 @@
       <c r="D439" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="AL439">
+        <v>1</v>
+      </c>
     </row>
     <row r="440" ht="14.25">
       <c r="A440" s="1" t="s">
@@ -14425,6 +14629,9 @@
       <c r="M440">
         <v>1</v>
       </c>
+      <c r="AL440">
+        <v>1</v>
+      </c>
     </row>
     <row r="441" ht="14.25">
       <c r="A441" s="1" t="s">
@@ -14493,6 +14700,9 @@
       <c r="N444">
         <v>1</v>
       </c>
+      <c r="AL444">
+        <v>1</v>
+      </c>
     </row>
     <row r="445" ht="14.25">
       <c r="A445" s="1" t="s">
@@ -14561,11 +14771,11 @@
       <c r="U448">
         <v>1</v>
       </c>
-      <c r="V448" s="9"/>
-      <c r="W448" s="9"/>
-      <c r="X448" s="9"/>
-      <c r="Y448" s="9"/>
-      <c r="Z448" s="9">
+      <c r="V448" s="10"/>
+      <c r="W448" s="10"/>
+      <c r="X448" s="10"/>
+      <c r="Y448" s="10"/>
+      <c r="Z448" s="10">
         <v>1</v>
       </c>
       <c r="AF448">
@@ -14625,6 +14835,9 @@
       <c r="J451">
         <v>1</v>
       </c>
+      <c r="AL451">
+        <v>1</v>
+      </c>
     </row>
     <row r="452" ht="14.25">
       <c r="A452" s="1" t="s">
@@ -14857,6 +15070,9 @@
       <c r="AJ465">
         <v>1</v>
       </c>
+      <c r="AL465">
+        <v>1</v>
+      </c>
     </row>
     <row r="466" ht="14.25">
       <c r="A466" s="1" t="s">
@@ -14942,6 +15158,9 @@
       <c r="AK470">
         <v>1</v>
       </c>
+      <c r="AL470">
+        <v>1</v>
+      </c>
     </row>
     <row r="471" ht="14.25">
       <c r="A471" s="1" t="s">
@@ -14962,6 +15181,9 @@
       <c r="X471">
         <v>1</v>
       </c>
+      <c r="AL471">
+        <v>1</v>
+      </c>
     </row>
     <row r="472" ht="14.25">
       <c r="A472" s="1" t="s">
@@ -14993,6 +15215,9 @@
       <c r="D473" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AL473">
+        <v>1</v>
+      </c>
     </row>
     <row r="474" ht="14.25">
       <c r="A474" s="1" t="s">
@@ -15121,6 +15346,9 @@
       <c r="D480" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL480">
+        <v>1</v>
+      </c>
     </row>
     <row r="481" ht="14.25">
       <c r="A481" s="1" t="s">
@@ -15362,6 +15590,9 @@
       <c r="X494">
         <v>1</v>
       </c>
+      <c r="AL494">
+        <v>1</v>
+      </c>
     </row>
     <row r="495" ht="14.25">
       <c r="A495" s="1" t="s">
@@ -15485,6 +15716,9 @@
       <c r="X500">
         <v>1</v>
       </c>
+      <c r="AL500">
+        <v>1</v>
+      </c>
     </row>
     <row r="501" ht="14.25">
       <c r="A501" s="1" t="s">
@@ -15679,6 +15913,9 @@
       <c r="X510">
         <v>1</v>
       </c>
+      <c r="AL510">
+        <v>1</v>
+      </c>
     </row>
     <row r="511" ht="14.25">
       <c r="A511" s="1" t="s">
@@ -15776,6 +16013,9 @@
       <c r="X515">
         <v>1</v>
       </c>
+      <c r="AL515">
+        <v>1</v>
+      </c>
     </row>
     <row r="516" ht="14.25">
       <c r="A516" s="1" t="s">
@@ -15864,6 +16104,9 @@
       <c r="X520">
         <v>1</v>
       </c>
+      <c r="AL520">
+        <v>1</v>
+      </c>
     </row>
     <row r="521" ht="14.25">
       <c r="A521" s="1" t="s">
@@ -15961,6 +16204,9 @@
       <c r="F525">
         <v>1</v>
       </c>
+      <c r="AL525">
+        <v>1</v>
+      </c>
     </row>
     <row r="526" ht="14.25">
       <c r="A526" s="1" t="s">
@@ -16058,6 +16304,9 @@
       <c r="V530">
         <v>1</v>
       </c>
+      <c r="AL530">
+        <v>1</v>
+      </c>
     </row>
     <row r="531" ht="14.25">
       <c r="A531" s="1" t="s">
@@ -16081,6 +16330,9 @@
       <c r="AE531">
         <v>1</v>
       </c>
+      <c r="AL531">
+        <v>1</v>
+      </c>
     </row>
     <row r="532" ht="14.25">
       <c r="A532" s="1" t="s">
@@ -16238,6 +16490,9 @@
       <c r="AK539">
         <v>1</v>
       </c>
+      <c r="AL539">
+        <v>1</v>
+      </c>
     </row>
     <row r="540" ht="14.25">
       <c r="A540" s="1" t="s">
@@ -16337,9 +16592,9 @@
       <c r="W545">
         <v>1</v>
       </c>
-      <c r="X545" s="9"/>
-      <c r="Y545" s="9"/>
-      <c r="Z545" s="9"/>
+      <c r="X545" s="10"/>
+      <c r="Y545" s="10"/>
+      <c r="Z545" s="10"/>
     </row>
     <row r="546" ht="14.25">
       <c r="A546" s="1" t="s">
@@ -16675,6 +16930,9 @@
       <c r="M564">
         <v>1</v>
       </c>
+      <c r="AL564">
+        <v>1</v>
+      </c>
     </row>
     <row r="565" ht="14.25">
       <c r="A565" s="1" t="s">
@@ -16729,7 +16987,7 @@
       <c r="Y567">
         <v>1</v>
       </c>
-      <c r="Z567" s="9"/>
+      <c r="Z567" s="10"/>
       <c r="AK567">
         <v>1</v>
       </c>
@@ -16790,6 +17048,9 @@
       <c r="AB570">
         <v>1</v>
       </c>
+      <c r="AL570">
+        <v>1</v>
+      </c>
     </row>
     <row r="571" ht="14.25">
       <c r="A571" s="1" t="s">
@@ -16929,6 +17190,9 @@
       <c r="M578">
         <v>1</v>
       </c>
+      <c r="AL578">
+        <v>1</v>
+      </c>
     </row>
     <row r="579" ht="14.25">
       <c r="A579" s="1" t="s">
@@ -17162,7 +17426,10 @@
       <c r="Y591">
         <v>1</v>
       </c>
-      <c r="Z591" s="9"/>
+      <c r="Z591" s="10"/>
+      <c r="AL591">
+        <v>1</v>
+      </c>
     </row>
     <row r="592" ht="14.25">
       <c r="A592" s="1" t="s">
@@ -17228,6 +17495,9 @@
       <c r="M595">
         <v>1</v>
       </c>
+      <c r="AL595">
+        <v>1</v>
+      </c>
     </row>
     <row r="596" ht="14.25">
       <c r="A596" s="1" t="s">
@@ -17495,6 +17765,9 @@
       <c r="G610">
         <v>1</v>
       </c>
+      <c r="AL610">
+        <v>1</v>
+      </c>
     </row>
     <row r="611" ht="14.25">
       <c r="A611" s="1" t="s">
@@ -17813,6 +18086,9 @@
       <c r="AC628">
         <v>1</v>
       </c>
+      <c r="AL628">
+        <v>1</v>
+      </c>
     </row>
     <row r="629" ht="14.25">
       <c r="A629" s="1" t="s">
@@ -17994,6 +18270,9 @@
       <c r="AK639">
         <v>1</v>
       </c>
+      <c r="AL639">
+        <v>1</v>
+      </c>
     </row>
     <row r="640" ht="14.25">
       <c r="A640" s="1" t="s">
@@ -18164,7 +18443,10 @@
       <c r="Y649">
         <v>1</v>
       </c>
-      <c r="Z649" s="9"/>
+      <c r="Z649" s="10"/>
+      <c r="AL649">
+        <v>1</v>
+      </c>
     </row>
     <row r="650" ht="14.25">
       <c r="A650" s="1" t="s">
@@ -18211,6 +18493,9 @@
       <c r="D651" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AL651">
+        <v>1</v>
+      </c>
     </row>
     <row r="652" ht="14.25">
       <c r="A652" s="1" t="s">
@@ -18299,6 +18584,9 @@
       <c r="AC656">
         <v>1</v>
       </c>
+      <c r="AL656">
+        <v>1</v>
+      </c>
     </row>
     <row r="657" ht="14.25">
       <c r="A657" s="1" t="s">
@@ -18396,6 +18684,9 @@
       <c r="AK661">
         <v>1</v>
       </c>
+      <c r="AL661">
+        <v>1</v>
+      </c>
     </row>
     <row r="662" ht="14.25">
       <c r="A662" s="1" t="s">
@@ -18524,6 +18815,9 @@
       <c r="X668">
         <v>1</v>
       </c>
+      <c r="AL668">
+        <v>1</v>
+      </c>
     </row>
     <row r="669" ht="14.25">
       <c r="A669" s="1" t="s">
@@ -18688,6 +18982,9 @@
       <c r="AH678">
         <v>1</v>
       </c>
+      <c r="AL678">
+        <v>1</v>
+      </c>
     </row>
     <row r="679" ht="14.25">
       <c r="A679" s="1" t="s">
@@ -18904,6 +19201,9 @@
       <c r="D690" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL690">
+        <v>1</v>
+      </c>
     </row>
     <row r="691" ht="14.25">
       <c r="A691" s="1" t="s">
@@ -18924,6 +19224,9 @@
       <c r="J691">
         <v>1</v>
       </c>
+      <c r="AL691">
+        <v>1</v>
+      </c>
     </row>
     <row r="692" ht="14.25">
       <c r="A692" s="1" t="s">
@@ -18955,6 +19258,9 @@
       <c r="M693">
         <v>1</v>
       </c>
+      <c r="AL693">
+        <v>1</v>
+      </c>
     </row>
     <row r="694" ht="14.25">
       <c r="A694" s="1" t="s">
@@ -19006,6 +19312,9 @@
       <c r="D696" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AL696">
+        <v>1</v>
+      </c>
     </row>
     <row r="697" ht="14.25">
       <c r="A697" s="1" t="s">
@@ -19299,7 +19608,7 @@
       <c r="Y715">
         <v>1</v>
       </c>
-      <c r="Z715" s="9"/>
+      <c r="Z715" s="10"/>
       <c r="AK715">
         <v>1</v>
       </c>
@@ -19527,9 +19836,9 @@
       <c r="W728">
         <v>1</v>
       </c>
-      <c r="X728" s="9"/>
-      <c r="Y728" s="9"/>
-      <c r="Z728" s="9"/>
+      <c r="X728" s="10"/>
+      <c r="Y728" s="10"/>
+      <c r="Z728" s="10"/>
     </row>
     <row r="729" ht="14.25">
       <c r="A729" s="1" t="s">
@@ -19564,6 +19873,9 @@
       <c r="J730">
         <v>1</v>
       </c>
+      <c r="AL730">
+        <v>1</v>
+      </c>
     </row>
     <row r="731" ht="14.25">
       <c r="A731" s="1" t="s">
@@ -19657,6 +19969,9 @@
       <c r="D736" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="AL736">
+        <v>1</v>
+      </c>
     </row>
     <row r="737" ht="14.25">
       <c r="A737" s="1" t="s">
@@ -19927,6 +20242,9 @@
       <c r="X751">
         <v>1</v>
       </c>
+      <c r="AL751">
+        <v>1</v>
+      </c>
     </row>
     <row r="752" ht="14.25">
       <c r="A752" s="1" t="s">
@@ -20070,6 +20388,9 @@
       <c r="AK758">
         <v>1</v>
       </c>
+      <c r="AL758">
+        <v>1</v>
+      </c>
     </row>
     <row r="759" ht="14.25">
       <c r="A759" s="1" t="s">
@@ -20149,6 +20470,9 @@
       <c r="AK763">
         <v>1</v>
       </c>
+      <c r="AL763">
+        <v>1</v>
+      </c>
     </row>
     <row r="764" ht="14.25">
       <c r="A764" s="1" t="s">
@@ -20243,7 +20567,7 @@
       <c r="Y768">
         <v>1</v>
       </c>
-      <c r="Z768" s="9"/>
+      <c r="Z768" s="10"/>
       <c r="AK768">
         <v>1</v>
       </c>
@@ -20329,6 +20653,9 @@
       <c r="U773">
         <v>1</v>
       </c>
+      <c r="AL773">
+        <v>1</v>
+      </c>
     </row>
     <row r="774" ht="14.25">
       <c r="A774" s="1" t="s">
@@ -20451,6 +20778,9 @@
       <c r="X780">
         <v>1</v>
       </c>
+      <c r="AL780">
+        <v>1</v>
+      </c>
     </row>
     <row r="781" ht="14.25">
       <c r="A781" s="1" t="s">
@@ -20703,6 +21033,9 @@
       <c r="X795">
         <v>1</v>
       </c>
+      <c r="AL795">
+        <v>1</v>
+      </c>
     </row>
     <row r="796" ht="14.25">
       <c r="A796" s="1" t="s">
@@ -20788,6 +21121,9 @@
       <c r="D800" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AL800">
+        <v>1</v>
+      </c>
     </row>
     <row r="801" ht="14.25">
       <c r="A801" s="1" t="s">
@@ -20806,6 +21142,9 @@
         <v>1</v>
       </c>
       <c r="AA801">
+        <v>1</v>
+      </c>
+      <c r="AL801">
         <v>1</v>
       </c>
     </row>
@@ -21892,7 +22231,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{BFB7A082-F5FA-4991-8CF6-52143E9AFB40}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{CEDFFD89-F270-4544-9B10-43ACFF9CC3C0}" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -22024,13 +22363,16 @@
         <v>36</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>1924</v>
       </c>
     </row>
     <row r="2">
@@ -22338,6 +22680,9 @@
       <c r="AD16">
         <v>1</v>
       </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -22441,6 +22786,9 @@
       <c r="AG21">
         <v>1</v>
       </c>
+      <c r="AL21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -22498,6 +22846,9 @@
       <c r="X24">
         <v>1</v>
       </c>
+      <c r="AL24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
@@ -22532,9 +22883,6 @@
       <c r="AI26">
         <v>1</v>
       </c>
-      <c r="AL26">
-        <v>1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
@@ -22770,6 +23118,9 @@
       <c r="D40" t="s">
         <v>49</v>
       </c>
+      <c r="AL40">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
@@ -22818,6 +23169,9 @@
       <c r="D43" t="s">
         <v>43</v>
       </c>
+      <c r="AL43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
@@ -23689,6 +24043,9 @@
       <c r="D90" t="s">
         <v>49</v>
       </c>
+      <c r="AL90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
@@ -23706,6 +24063,9 @@
       <c r="M91">
         <v>1</v>
       </c>
+      <c r="AL91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
@@ -23763,6 +24123,9 @@
       <c r="X94">
         <v>1</v>
       </c>
+      <c r="AL94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
@@ -23837,6 +24200,9 @@
       <c r="Y98">
         <v>1</v>
       </c>
+      <c r="AL98">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
@@ -24000,6 +24366,9 @@
       <c r="AF106">
         <v>1</v>
       </c>
+      <c r="AL106">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
@@ -24103,6 +24472,9 @@
       <c r="AE111">
         <v>1</v>
       </c>
+      <c r="AL111">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
@@ -24177,6 +24549,9 @@
       <c r="D115" t="s">
         <v>49</v>
       </c>
+      <c r="AL115">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
@@ -24279,6 +24654,9 @@
       <c r="D121" t="s">
         <v>52</v>
       </c>
+      <c r="AL121">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
@@ -24443,6 +24821,9 @@
       <c r="D131" t="s">
         <v>52</v>
       </c>
+      <c r="AL131">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
@@ -24502,6 +24883,9 @@
       <c r="X135">
         <v>1</v>
       </c>
+      <c r="AL135">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
@@ -24838,6 +25222,9 @@
       <c r="Y153">
         <v>1</v>
       </c>
+      <c r="AL153">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
@@ -24887,6 +25274,9 @@
       <c r="AG155">
         <v>1</v>
       </c>
+      <c r="AL155">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
@@ -24961,6 +25351,9 @@
       <c r="M159">
         <v>1</v>
       </c>
+      <c r="AL159">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
@@ -24981,6 +25374,9 @@
       <c r="AK160">
         <v>1</v>
       </c>
+      <c r="AL160">
+        <v>1</v>
+      </c>
       <c r="AN160">
         <v>1</v>
       </c>
@@ -25120,6 +25516,9 @@
       <c r="M168">
         <v>1</v>
       </c>
+      <c r="AL168">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
@@ -25268,6 +25667,9 @@
       <c r="AK176">
         <v>1</v>
       </c>
+      <c r="AL176">
+        <v>1</v>
+      </c>
       <c r="AN176">
         <v>1</v>
       </c>
@@ -25302,6 +25704,9 @@
       <c r="X178">
         <v>1</v>
       </c>
+      <c r="AL178">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
@@ -25456,6 +25861,9 @@
       <c r="AE186">
         <v>1</v>
       </c>
+      <c r="AL186">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
@@ -25490,6 +25898,9 @@
       <c r="D188" t="s">
         <v>43</v>
       </c>
+      <c r="AL188">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
@@ -25620,6 +26031,9 @@
       <c r="AD196">
         <v>1</v>
       </c>
+      <c r="AL196">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
@@ -26329,6 +26743,9 @@
       <c r="Y234">
         <v>1</v>
       </c>
+      <c r="AL234">
+        <v>1</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
@@ -26397,6 +26814,9 @@
       <c r="X238">
         <v>1</v>
       </c>
+      <c r="AL238">
+        <v>1</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
@@ -26525,6 +26945,9 @@
       <c r="M245">
         <v>1</v>
       </c>
+      <c r="AL245">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
@@ -26599,6 +27022,9 @@
       <c r="AK249">
         <v>1</v>
       </c>
+      <c r="AL249">
+        <v>1</v>
+      </c>
       <c r="AN249">
         <v>1</v>
       </c>
@@ -26616,6 +27042,9 @@
       <c r="D250" t="s">
         <v>49</v>
       </c>
+      <c r="AL250">
+        <v>1</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
@@ -26718,6 +27147,9 @@
       <c r="X256">
         <v>1</v>
       </c>
+      <c r="AL256">
+        <v>1</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
@@ -26749,6 +27181,9 @@
       <c r="X258">
         <v>1</v>
       </c>
+      <c r="AL258">
+        <v>1</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
@@ -26843,6 +27278,9 @@
       <c r="AG263">
         <v>1</v>
       </c>
+      <c r="AL263">
+        <v>1</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
@@ -26880,6 +27318,9 @@
       <c r="AK265">
         <v>1</v>
       </c>
+      <c r="AL265">
+        <v>1</v>
+      </c>
       <c r="AN265">
         <v>1</v>
       </c>
@@ -26940,6 +27381,9 @@
       <c r="D268" t="s">
         <v>43</v>
       </c>
+      <c r="AL268">
+        <v>1</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
@@ -27206,6 +27650,9 @@
       <c r="AE281">
         <v>1</v>
       </c>
+      <c r="AL281">
+        <v>1</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
@@ -27445,6 +27892,9 @@
       <c r="G294">
         <v>1</v>
       </c>
+      <c r="AL294">
+        <v>1</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
@@ -27586,6 +28036,9 @@
       <c r="D303" t="s">
         <v>43</v>
       </c>
+      <c r="AL303">
+        <v>1</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
@@ -27665,6 +28118,9 @@
       <c r="D308" t="s">
         <v>43</v>
       </c>
+      <c r="AL308">
+        <v>1</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
@@ -27702,6 +28158,9 @@
       <c r="AA310">
         <v>1</v>
       </c>
+      <c r="AL310">
+        <v>1</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
@@ -27776,6 +28235,9 @@
       <c r="AK314">
         <v>1</v>
       </c>
+      <c r="AL314">
+        <v>1</v>
+      </c>
       <c r="AN314">
         <v>1</v>
       </c>
@@ -27813,6 +28275,9 @@
       <c r="AE316">
         <v>1</v>
       </c>
+      <c r="AL316">
+        <v>1</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
@@ -27901,6 +28366,9 @@
       <c r="AE321">
         <v>1</v>
       </c>
+      <c r="AL321">
+        <v>1</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
@@ -28017,6 +28485,9 @@
       <c r="D328" t="s">
         <v>43</v>
       </c>
+      <c r="AL328">
+        <v>1</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
@@ -28148,6 +28619,9 @@
       <c r="AD335">
         <v>1</v>
       </c>
+      <c r="AL335">
+        <v>1</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
@@ -28399,6 +28873,9 @@
       <c r="D348" t="s">
         <v>43</v>
       </c>
+      <c r="AL348">
+        <v>1</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
@@ -28477,6 +28954,9 @@
       <c r="AG351">
         <v>1</v>
       </c>
+      <c r="AL351">
+        <v>1</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
@@ -28534,6 +29014,9 @@
       <c r="X354">
         <v>1</v>
       </c>
+      <c r="AL354">
+        <v>1</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="s">
@@ -28571,6 +29054,9 @@
       <c r="G356">
         <v>1</v>
       </c>
+      <c r="AL356">
+        <v>1</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="s">
@@ -28847,6 +29333,9 @@
       <c r="AE371">
         <v>1</v>
       </c>
+      <c r="AL371">
+        <v>1</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
@@ -28875,6 +29364,9 @@
       <c r="D373" t="s">
         <v>43</v>
       </c>
+      <c r="AL373">
+        <v>1</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="s">
@@ -28989,6 +29481,9 @@
       <c r="AK379">
         <v>1</v>
       </c>
+      <c r="AL379">
+        <v>1</v>
+      </c>
       <c r="AN379">
         <v>1</v>
       </c>
@@ -29006,6 +29501,9 @@
       <c r="D380" t="s">
         <v>869</v>
       </c>
+      <c r="AL380">
+        <v>1</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="s">
@@ -29026,6 +29524,9 @@
       <c r="M381">
         <v>1</v>
       </c>
+      <c r="AL381">
+        <v>1</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="s">
@@ -29142,6 +29643,9 @@
       <c r="AK388">
         <v>1</v>
       </c>
+      <c r="AL388">
+        <v>1</v>
+      </c>
       <c r="AN388">
         <v>1</v>
       </c>
@@ -29255,6 +29759,9 @@
       <c r="D395" t="s">
         <v>49</v>
       </c>
+      <c r="AL395">
+        <v>1</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="s">
@@ -29272,6 +29779,9 @@
       <c r="K396">
         <v>1</v>
       </c>
+      <c r="AL396">
+        <v>1</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="s">
@@ -29329,6 +29839,9 @@
       <c r="AE399">
         <v>1</v>
       </c>
+      <c r="AL399">
+        <v>1</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="s">
@@ -29403,6 +29916,9 @@
       <c r="AE403">
         <v>1</v>
       </c>
+      <c r="AL403">
+        <v>1</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="s">
@@ -29532,9 +30048,6 @@
       <c r="AK409">
         <v>1</v>
       </c>
-      <c r="AL409">
-        <v>1</v>
-      </c>
       <c r="AN409">
         <v>1</v>
       </c>
@@ -29646,6 +30159,9 @@
       <c r="AK415">
         <v>1</v>
       </c>
+      <c r="AL415">
+        <v>1</v>
+      </c>
       <c r="AM415">
         <v>1</v>
       </c>
@@ -29694,6 +30210,9 @@
       <c r="D418" t="s">
         <v>43</v>
       </c>
+      <c r="AL418">
+        <v>1</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
@@ -29827,6 +30346,9 @@
       <c r="M426">
         <v>1</v>
       </c>
+      <c r="AL426">
+        <v>1</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="s">
@@ -29892,6 +30414,9 @@
       <c r="D430" t="s">
         <v>49</v>
       </c>
+      <c r="AL430">
+        <v>1</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
@@ -30009,6 +30534,9 @@
       <c r="AB436">
         <v>1</v>
       </c>
+      <c r="AL436">
+        <v>1</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="s">
@@ -30063,6 +30591,9 @@
       <c r="D439" t="s">
         <v>46</v>
       </c>
+      <c r="AL439">
+        <v>1</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
@@ -30080,6 +30611,9 @@
       <c r="M440">
         <v>1</v>
       </c>
+      <c r="AL440">
+        <v>1</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="s">
@@ -30148,6 +30682,9 @@
       <c r="N444">
         <v>1</v>
       </c>
+      <c r="AL444">
+        <v>1</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
@@ -30276,6 +30813,9 @@
       <c r="J451">
         <v>1</v>
       </c>
+      <c r="AL451">
+        <v>1</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="s">
@@ -30517,6 +31057,9 @@
       <c r="AJ465">
         <v>1</v>
       </c>
+      <c r="AL465">
+        <v>1</v>
+      </c>
       <c r="AM465">
         <v>1</v>
       </c>
@@ -30605,6 +31148,9 @@
       <c r="AK470">
         <v>1</v>
       </c>
+      <c r="AL470">
+        <v>1</v>
+      </c>
       <c r="AN470">
         <v>1</v>
       </c>
@@ -30628,6 +31174,9 @@
       <c r="X471">
         <v>1</v>
       </c>
+      <c r="AL471">
+        <v>1</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="s">
@@ -30662,6 +31211,9 @@
       <c r="D473" t="s">
         <v>43</v>
       </c>
+      <c r="AL473">
+        <v>1</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="s">
@@ -30796,6 +31348,9 @@
       <c r="D480" t="s">
         <v>49</v>
       </c>
+      <c r="AL480">
+        <v>1</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="s">
@@ -31043,6 +31598,9 @@
       <c r="X494">
         <v>1</v>
       </c>
+      <c r="AL494">
+        <v>1</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="s">
@@ -31172,6 +31730,9 @@
       <c r="X500">
         <v>1</v>
       </c>
+      <c r="AL500">
+        <v>1</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
@@ -31372,6 +31933,9 @@
       <c r="X510">
         <v>1</v>
       </c>
+      <c r="AL510">
+        <v>1</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
@@ -31472,6 +32036,9 @@
       <c r="X515">
         <v>1</v>
       </c>
+      <c r="AL515">
+        <v>1</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="s">
@@ -31563,6 +32130,9 @@
       <c r="X520">
         <v>1</v>
       </c>
+      <c r="AL520">
+        <v>1</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
@@ -31663,6 +32233,9 @@
       <c r="F525">
         <v>1</v>
       </c>
+      <c r="AL525">
+        <v>1</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="s">
@@ -31763,6 +32336,9 @@
       <c r="V530">
         <v>1</v>
       </c>
+      <c r="AL530">
+        <v>1</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="s">
@@ -31786,6 +32362,9 @@
       <c r="AE531">
         <v>1</v>
       </c>
+      <c r="AL531">
+        <v>1</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="s">
@@ -31949,6 +32528,9 @@
       <c r="AK539">
         <v>1</v>
       </c>
+      <c r="AL539">
+        <v>1</v>
+      </c>
       <c r="AN539">
         <v>1</v>
       </c>
@@ -32404,6 +32986,9 @@
       <c r="M564">
         <v>1</v>
       </c>
+      <c r="AL564">
+        <v>1</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="s">
@@ -32501,9 +33086,6 @@
       <c r="AI569">
         <v>1</v>
       </c>
-      <c r="AL569">
-        <v>1</v>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="s">
@@ -32524,6 +33106,9 @@
       <c r="AB570">
         <v>1</v>
       </c>
+      <c r="AL570">
+        <v>1</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
@@ -32666,6 +33251,9 @@
       <c r="M578">
         <v>1</v>
       </c>
+      <c r="AL578">
+        <v>1</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
@@ -32908,6 +33496,9 @@
       <c r="Y591">
         <v>1</v>
       </c>
+      <c r="AL591">
+        <v>1</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
@@ -32973,6 +33564,9 @@
       <c r="M595">
         <v>1</v>
       </c>
+      <c r="AL595">
+        <v>1</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="s">
@@ -33246,6 +33840,9 @@
       <c r="G610">
         <v>1</v>
       </c>
+      <c r="AL610">
+        <v>1</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
@@ -33579,6 +34176,9 @@
       <c r="AC628">
         <v>1</v>
       </c>
+      <c r="AL628">
+        <v>1</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="s">
@@ -33769,6 +34369,9 @@
       <c r="AK639">
         <v>1</v>
       </c>
+      <c r="AL639">
+        <v>1</v>
+      </c>
       <c r="AN639">
         <v>1</v>
       </c>
@@ -33942,6 +34545,9 @@
       <c r="Y649">
         <v>1</v>
       </c>
+      <c r="AL649">
+        <v>1</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="s">
@@ -33988,6 +34594,9 @@
       <c r="D651" t="s">
         <v>52</v>
       </c>
+      <c r="AL651">
+        <v>1</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="s">
@@ -34079,6 +34688,9 @@
       <c r="AC656">
         <v>1</v>
       </c>
+      <c r="AL656">
+        <v>1</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="s">
@@ -34176,6 +34788,9 @@
       <c r="AK661">
         <v>1</v>
       </c>
+      <c r="AL661">
+        <v>1</v>
+      </c>
       <c r="AN661">
         <v>1</v>
       </c>
@@ -34310,6 +34925,9 @@
       <c r="X668">
         <v>1</v>
       </c>
+      <c r="AL668">
+        <v>1</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="s">
@@ -34480,6 +35098,9 @@
       <c r="AH678">
         <v>1</v>
       </c>
+      <c r="AL678">
+        <v>1</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="s">
@@ -34702,6 +35323,9 @@
       <c r="D690" t="s">
         <v>49</v>
       </c>
+      <c r="AL690">
+        <v>1</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="s">
@@ -34722,6 +35346,9 @@
       <c r="J691">
         <v>1</v>
       </c>
+      <c r="AL691">
+        <v>1</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="s">
@@ -34753,6 +35380,9 @@
       <c r="M693">
         <v>1</v>
       </c>
+      <c r="AL693">
+        <v>1</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="s">
@@ -34807,6 +35437,9 @@
       <c r="D696" t="s">
         <v>52</v>
       </c>
+      <c r="AL696">
+        <v>1</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="s">
@@ -35370,6 +36003,9 @@
       <c r="J730">
         <v>1</v>
       </c>
+      <c r="AL730">
+        <v>1</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
@@ -35463,6 +36099,9 @@
       <c r="D736" t="s">
         <v>52</v>
       </c>
+      <c r="AL736">
+        <v>1</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="s">
@@ -35739,6 +36378,9 @@
       <c r="X751">
         <v>1</v>
       </c>
+      <c r="AL751">
+        <v>1</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
@@ -35888,6 +36530,9 @@
       <c r="AK758">
         <v>1</v>
       </c>
+      <c r="AL758">
+        <v>1</v>
+      </c>
       <c r="AN758">
         <v>1</v>
       </c>
@@ -35970,6 +36615,9 @@
       <c r="AK763">
         <v>1</v>
       </c>
+      <c r="AL763">
+        <v>1</v>
+      </c>
       <c r="AN763">
         <v>1</v>
       </c>
@@ -36158,6 +36806,9 @@
       <c r="U773">
         <v>1</v>
       </c>
+      <c r="AL773">
+        <v>1</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="s">
@@ -36283,6 +36934,9 @@
       <c r="X780">
         <v>1</v>
       </c>
+      <c r="AL780">
+        <v>1</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="s">
@@ -36544,6 +37198,9 @@
       <c r="X795">
         <v>1</v>
       </c>
+      <c r="AL795">
+        <v>1</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
@@ -36615,9 +37272,6 @@
       <c r="AI799">
         <v>1</v>
       </c>
-      <c r="AL799">
-        <v>1</v>
-      </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
@@ -36632,6 +37286,9 @@
       <c r="D800" t="s">
         <v>49</v>
       </c>
+      <c r="AL800">
+        <v>1</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="s">
@@ -36650,6 +37307,9 @@
         <v>1</v>
       </c>
       <c r="AA801">
+        <v>1</v>
+      </c>
+      <c r="AL801">
         <v>1</v>
       </c>
     </row>
